--- a/data/leagues/The Girl's Room 💞🏈 2026.xlsx
+++ b/data/leagues/The Girl's Room 💞🏈 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="106">
   <si>
     <t>Tush Push Director 🍑</t>
   </si>
@@ -61,10 +61,13 @@
     <t xml:space="preserve">michelle’s boy toys </t>
   </si>
   <si>
-    <t>1-0-0</t>
-  </si>
-  <si>
-    <t>0-1-0</t>
+    <t>2-0-0</t>
+  </si>
+  <si>
+    <t>1-1-0</t>
+  </si>
+  <si>
+    <t>0-2-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -130,6 +133,9 @@
     <t>Week_2</t>
   </si>
   <si>
+    <t>Week_3</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -151,42 +157,42 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Bianca Magsino</t>
+  </si>
+  <si>
+    <t>Hannah Miller</t>
+  </si>
+  <si>
+    <t>Michelle Nocitra</t>
+  </si>
+  <si>
+    <t>Malini Ragoopath</t>
+  </si>
+  <si>
+    <t>Kiana McIntosh</t>
+  </si>
+  <si>
+    <t>nidhi shah</t>
+  </si>
+  <si>
+    <t>Sumita Gangwani</t>
+  </si>
+  <si>
+    <t>Amanda Pasquale</t>
+  </si>
+  <si>
     <t>Emily Carey</t>
   </si>
   <si>
-    <t>Malini Ragoopath</t>
-  </si>
-  <si>
-    <t>Amanda Pasquale</t>
-  </si>
-  <si>
-    <t>Bianca Magsino</t>
-  </si>
-  <si>
-    <t>Michelle Nocitra</t>
-  </si>
-  <si>
-    <t>Kiana McIntosh</t>
-  </si>
-  <si>
     <t>Hillary Dale</t>
   </si>
   <si>
     <t>Allie Kardon</t>
   </si>
   <si>
-    <t>nidhi shah</t>
-  </si>
-  <si>
     <t>Grace Stockbower</t>
   </si>
   <si>
-    <t>Hannah Miller</t>
-  </si>
-  <si>
-    <t>Sumita Gangwani</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -211,69 +217,66 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>1-0</t>
-  </si>
-  <si>
-    <t>0-1</t>
-  </si>
-  <si>
-    <t>12.0-2.9-0.1</t>
-  </si>
-  <si>
-    <t>10.9-4.0-0.1</t>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>0-2</t>
   </si>
   <si>
     <t>10.4-4.5-0.1</t>
   </si>
   <si>
-    <t>10.3-4.6-0.1</t>
+    <t>9.9-5.0-0.1</t>
   </si>
   <si>
     <t>8.7-6.2-0.1</t>
   </si>
   <si>
-    <t>8.1-6.7-0.1</t>
-  </si>
-  <si>
-    <t>6.8-8.1-0.1</t>
-  </si>
-  <si>
-    <t>6.7-8.2-0.1</t>
-  </si>
-  <si>
-    <t>4.9-10.0-0.1</t>
-  </si>
-  <si>
-    <t>5.1-9.7-0.1</t>
-  </si>
-  <si>
-    <t>4.2-10.7-0.1</t>
-  </si>
-  <si>
-    <t>1.2-13.7-0.1</t>
-  </si>
-  <si>
-    <t>13-2</t>
+    <t>7.5-7.3-0.1</t>
+  </si>
+  <si>
+    <t>7.3-7.6-0.1</t>
+  </si>
+  <si>
+    <t>7.2-7.6-0.2</t>
+  </si>
+  <si>
+    <t>7.1-7.8-0.1</t>
+  </si>
+  <si>
+    <t>7.0-7.9-0.1</t>
+  </si>
+  <si>
+    <t>4.9-9.9-0.2</t>
+  </si>
+  <si>
+    <t>3.5-11.4-0.1</t>
   </si>
   <si>
     <t>11-4</t>
   </si>
   <si>
+    <t>10-5</t>
+  </si>
+  <si>
+    <t>9-6</t>
+  </si>
+  <si>
+    <t>7-8</t>
+  </si>
+  <si>
     <t>8-7</t>
   </si>
   <si>
-    <t>6-9</t>
-  </si>
-  <si>
     <t>5-10</t>
   </si>
   <si>
     <t>4-11</t>
   </si>
   <si>
-    <t>1-14</t>
-  </si>
-  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -283,7 +286,40 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↑7</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↓8</t>
+  </si>
+  <si>
+    <t>↓6</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↓10</t>
+  </si>
+  <si>
     <t>Week 1</t>
+  </si>
+  <si>
+    <t>Week 2</t>
   </si>
   <si>
     <t>Week</t>
@@ -714,7 +750,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -729,10 +765,10 @@
         <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2" t="s">
         <v>12</v>
@@ -749,40 +785,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -790,31 +826,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
         <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4" t="s">
         <v>12</v>
@@ -823,7 +859,7 @@
         <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -896,7 +932,7 @@
         <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K6" t="s">
         <v>13</v>
@@ -919,7 +955,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -937,7 +973,7 @@
         <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K7" t="s">
         <v>12</v>
@@ -954,40 +990,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
         <v>13</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K8" t="s">
         <v>12</v>
       </c>
       <c r="L8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1001,7 +1037,7 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -1010,16 +1046,16 @@
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
         <v>13</v>
       </c>
       <c r="I9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K9" t="s">
         <v>12</v>
@@ -1028,7 +1064,7 @@
         <v>13</v>
       </c>
       <c r="M9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1042,25 +1078,25 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
         <v>13</v>
       </c>
       <c r="I10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K10" t="s">
         <v>13</v>
@@ -1069,7 +1105,7 @@
         <v>13</v>
       </c>
       <c r="M10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1077,31 +1113,31 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
         <v>13</v>
       </c>
       <c r="I11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K11" t="s">
         <v>12</v>
@@ -1110,7 +1146,7 @@
         <v>12</v>
       </c>
       <c r="M11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1118,40 +1154,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
         <v>13</v>
       </c>
       <c r="I12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1159,31 +1195,31 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
       </c>
       <c r="I13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K13" t="s">
         <v>13</v>
@@ -1192,7 +1228,7 @@
         <v>13</v>
       </c>
       <c r="M13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1202,30 +1238,56 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:8">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>93</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1240,13 +1302,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1254,13 +1316,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>0.08333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1268,10 +1330,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -1285,7 +1347,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>0.25</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1296,13 +1358,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>0.3333333333333333</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1313,7 +1375,7 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>0.3333333333333333</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -1324,10 +1386,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -1338,13 +1400,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1352,13 +1414,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>0.6666666666666666</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1366,10 +1428,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>0.6666666666666666</v>
+        <v>1.25</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -1380,10 +1442,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.75</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
@@ -1394,13 +1456,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>0.8333333333333334</v>
+        <v>1.5</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1408,10 +1470,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>0.9166666666666666</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
@@ -1429,16 +1491,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1446,13 +1508,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -1463,16 +1525,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>0.9166666666666666</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="D3">
-        <v>-0.08333333333333337</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1480,16 +1542,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>0.8333333333333334</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="D4">
-        <v>-0.1666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1500,10 +1562,10 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>0.75</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="D5">
-        <v>-0.25</v>
+        <v>-0.9166666666666667</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -1514,16 +1576,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>0.5833333333333334</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="D6">
-        <v>-0.4166666666666666</v>
+        <v>0.08333333333333326</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1531,13 +1593,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>0.5833333333333334</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="D7">
-        <v>0.5833333333333334</v>
+        <v>0.08333333333333326</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -1551,13 +1613,13 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>0.4166666666666667</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>-0.5833333333333333</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1565,13 +1627,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0.4166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D9">
-        <v>0.4166666666666667</v>
+        <v>-0.1666666666666666</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -1582,13 +1644,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>0.25</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D10">
-        <v>0.25</v>
+        <v>-0.1666666666666666</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
@@ -1599,13 +1661,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>0.1666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D11">
-        <v>0.1666666666666667</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -1619,13 +1681,13 @@
         <v>8</v>
       </c>
       <c r="C12">
-        <v>0.08333333333333333</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D12">
-        <v>0.08333333333333333</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1636,13 +1698,13 @@
         <v>11</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1657,486 +1719,486 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>55.6</v>
+        <v>37.8</v>
       </c>
       <c r="C2">
-        <v>21.9</v>
+        <v>23</v>
       </c>
       <c r="D2">
-        <v>12.1</v>
+        <v>15.6</v>
       </c>
       <c r="E2">
-        <v>6.8</v>
+        <v>11.1</v>
       </c>
       <c r="F2">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="H2">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>96.40000000000001</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>19.2</v>
+        <v>35.1</v>
       </c>
       <c r="C3">
-        <v>27.1</v>
+        <v>24.4</v>
       </c>
       <c r="D3">
-        <v>22.8</v>
+        <v>13.9</v>
       </c>
       <c r="E3">
-        <v>15.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>6.7</v>
       </c>
       <c r="G3">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="H3">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="I3">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
-        <v>85</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>11.2</v>
+        <v>10.5</v>
       </c>
       <c r="C4">
-        <v>21.3</v>
+        <v>16.4</v>
       </c>
       <c r="D4">
-        <v>23.1</v>
+        <v>16.4</v>
       </c>
       <c r="E4">
-        <v>21.4</v>
+        <v>13.6</v>
       </c>
       <c r="F4">
-        <v>13.7</v>
+        <v>10.8</v>
       </c>
       <c r="G4">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H4">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="I4">
+        <v>6.3</v>
+      </c>
+      <c r="J4">
+        <v>4.5</v>
+      </c>
+      <c r="K4">
+        <v>3.6</v>
+      </c>
+      <c r="L4">
+        <v>0.7</v>
+      </c>
+      <c r="M4">
         <v>0.4</v>
       </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0.2</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
       <c r="N4">
-        <v>77</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>11.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C5">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="D5">
-        <v>21.9</v>
+        <v>14.9</v>
       </c>
       <c r="E5">
-        <v>21.3</v>
+        <v>14.1</v>
       </c>
       <c r="F5">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="G5">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="H5">
-        <v>3.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
       <c r="J5">
+        <v>6.7</v>
+      </c>
+      <c r="K5">
+        <v>3.3</v>
+      </c>
+      <c r="L5">
+        <v>1.9</v>
+      </c>
+      <c r="M5">
         <v>0.3</v>
       </c>
-      <c r="K5">
-        <v>0.1</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
       <c r="N5">
-        <v>74</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="C6">
         <v>5.7</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="E6">
-        <v>16.1</v>
+        <v>9.6</v>
       </c>
       <c r="F6">
-        <v>22.3</v>
+        <v>12.8</v>
       </c>
       <c r="G6">
-        <v>20.2</v>
+        <v>11.6</v>
       </c>
       <c r="H6">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="I6">
-        <v>6.4</v>
+        <v>11.6</v>
       </c>
       <c r="J6">
-        <v>2.3</v>
+        <v>10.9</v>
       </c>
       <c r="K6">
-        <v>1.8</v>
+        <v>8.4</v>
       </c>
       <c r="L6">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="N6">
-        <v>34.4</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="C7">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="D7">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="E7">
-        <v>11.2</v>
+        <v>7.9</v>
       </c>
       <c r="F7">
-        <v>20.9</v>
+        <v>10.2</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>10.8</v>
       </c>
       <c r="H7">
-        <v>16.3</v>
+        <v>13</v>
       </c>
       <c r="I7">
-        <v>8.1</v>
+        <v>11.6</v>
       </c>
       <c r="J7">
-        <v>4.4</v>
+        <v>11.7</v>
       </c>
       <c r="K7">
-        <v>2.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L7">
-        <v>0.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N7">
-        <v>22.3</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="C8">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="E8">
-        <v>2.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F8">
-        <v>7.2</v>
+        <v>9.9</v>
       </c>
       <c r="G8">
-        <v>15.7</v>
+        <v>11.7</v>
       </c>
       <c r="H8">
-        <v>23.8</v>
+        <v>13.9</v>
       </c>
       <c r="I8">
-        <v>23.3</v>
+        <v>13.1</v>
       </c>
       <c r="J8">
-        <v>13.9</v>
+        <v>12.4</v>
       </c>
       <c r="K8">
-        <v>7</v>
+        <v>10.8</v>
       </c>
       <c r="L8">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="M8">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="N8">
-        <v>5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="D9">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="E9">
-        <v>3.6</v>
+        <v>8.4</v>
       </c>
       <c r="F9">
-        <v>7.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G9">
-        <v>13.6</v>
+        <v>11.7</v>
       </c>
       <c r="H9">
-        <v>19.2</v>
+        <v>11</v>
       </c>
       <c r="I9">
-        <v>23.4</v>
+        <v>11</v>
       </c>
       <c r="J9">
-        <v>17.6</v>
+        <v>12.8</v>
       </c>
       <c r="K9">
-        <v>9.4</v>
+        <v>12.6</v>
       </c>
       <c r="L9">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="M9">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="N9">
-        <v>4.8</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="D10">
-        <v>0.2</v>
+        <v>5.9</v>
       </c>
       <c r="E10">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="F10">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="G10">
-        <v>2.4</v>
+        <v>13.5</v>
       </c>
       <c r="H10">
-        <v>6.4</v>
+        <v>12.8</v>
       </c>
       <c r="I10">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="J10">
-        <v>23.5</v>
+        <v>13.6</v>
       </c>
       <c r="K10">
-        <v>24.7</v>
+        <v>11</v>
       </c>
       <c r="L10">
-        <v>26.4</v>
+        <v>4.9</v>
       </c>
       <c r="M10">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="N10">
-        <v>0.7</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="D11">
-        <v>0.1</v>
+        <v>5.5</v>
       </c>
       <c r="E11">
-        <v>0.3</v>
+        <v>7.8</v>
       </c>
       <c r="F11">
-        <v>1.1</v>
+        <v>9.1</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H11">
-        <v>10.8</v>
+        <v>11.4</v>
       </c>
       <c r="I11">
-        <v>15.1</v>
+        <v>13.9</v>
       </c>
       <c r="J11">
-        <v>20.7</v>
+        <v>12.2</v>
       </c>
       <c r="K11">
-        <v>27.2</v>
+        <v>13.7</v>
       </c>
       <c r="L11">
-        <v>19.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M11">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="N11">
-        <v>0.4</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2147,40 +2209,40 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F12">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="G12">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="H12">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="I12">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J12">
-        <v>17.1</v>
+        <v>10.2</v>
       </c>
       <c r="K12">
-        <v>26.7</v>
+        <v>19.3</v>
       </c>
       <c r="L12">
-        <v>39.1</v>
+        <v>35.9</v>
       </c>
       <c r="M12">
-        <v>3.6</v>
+        <v>16.9</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2197,34 +2259,34 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J13">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="K13">
-        <v>0.7</v>
+        <v>6.9</v>
       </c>
       <c r="L13">
-        <v>5.9</v>
+        <v>17.8</v>
       </c>
       <c r="M13">
-        <v>93.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2234,139 +2296,175 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>35</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="C2">
+        <v>89.3</v>
+      </c>
+      <c r="D2">
+        <v>85.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>3.6</v>
+      </c>
+      <c r="C3">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="D3">
+        <v>81.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>96.39999999999999</v>
-      </c>
-      <c r="C2">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3">
-        <v>86.7</v>
-      </c>
-      <c r="C3">
-        <v>84.8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
+      <c r="B4">
+        <v>95.39999999999999</v>
+      </c>
+      <c r="C4">
+        <v>55.3</v>
+      </c>
+      <c r="D4">
+        <v>53.40000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
-        <v>77.5</v>
-      </c>
-      <c r="C4">
-        <v>77.10000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
+      <c r="B5">
+        <v>78</v>
+      </c>
+      <c r="C5">
+        <v>46.1</v>
+      </c>
+      <c r="D5">
+        <v>52.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.6</v>
+      </c>
+      <c r="C6">
+        <v>26.6</v>
+      </c>
+      <c r="D6">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B5">
-        <v>76.5</v>
-      </c>
-      <c r="C5">
-        <v>72.89999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
+      <c r="B7">
+        <v>74</v>
+      </c>
+      <c r="C7">
+        <v>22.2</v>
+      </c>
+      <c r="D7">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>0.4</v>
+      </c>
+      <c r="C8">
+        <v>20.8</v>
+      </c>
+      <c r="D8">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>21.8</v>
+      </c>
+      <c r="C9">
+        <v>19.5</v>
+      </c>
+      <c r="D9">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>6.800000000000001</v>
+      </c>
+      <c r="C10">
+        <v>16.6</v>
+      </c>
+      <c r="D10">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>31.2</v>
-      </c>
-      <c r="C6">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>19.1</v>
-      </c>
-      <c r="C7">
-        <v>28.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>7.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>4.7</v>
-      </c>
-      <c r="C9">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10">
-        <v>0.2</v>
-      </c>
-      <c r="C10">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B11">
-        <v>0.2</v>
+        <v>30.7</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>16.9</v>
+      </c>
+      <c r="D11">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>1.6</v>
+      </c>
+      <c r="D12">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -2374,6 +2472,9 @@
         <v>0</v>
       </c>
       <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
         <v>0</v>
       </c>
     </row>
@@ -2389,28 +2490,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2418,28 +2519,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>103.82</v>
+        <v>109.02</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
       </c>
       <c r="F2">
-        <v>121.82</v>
+        <v>114.79</v>
       </c>
       <c r="G2">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2447,28 +2548,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3">
-        <v>111.5</v>
+        <v>109.55</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>119.89</v>
+        <v>113.79</v>
       </c>
       <c r="G3">
-        <v>0.429</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2476,28 +2577,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4">
-        <v>99.66</v>
+        <v>84.23</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>122.72</v>
+        <v>118.02</v>
       </c>
       <c r="G4">
-        <v>0.571</v>
+        <v>0.577</v>
       </c>
       <c r="H4">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I4">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2505,28 +2606,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5">
-        <v>128.56</v>
+        <v>112.23</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>122.31</v>
+        <v>114.63</v>
       </c>
       <c r="G5">
-        <v>0.571</v>
+        <v>0.538</v>
       </c>
       <c r="H5">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I5">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2534,28 +2635,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>63.94</v>
+        <v>110.48</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
       </c>
       <c r="F6">
-        <v>124.49</v>
+        <v>113.66</v>
       </c>
       <c r="G6">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="H6">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2563,28 +2664,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>137.2</v>
+        <v>113.16</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
       </c>
       <c r="F7">
-        <v>117.24</v>
+        <v>110.87</v>
       </c>
       <c r="G7">
-        <v>0.429</v>
+        <v>0.385</v>
       </c>
       <c r="H7">
         <v>0.2</v>
       </c>
       <c r="I7">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2592,28 +2693,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>103.96</v>
+        <v>128.05</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>118.4</v>
+        <v>114.58</v>
       </c>
       <c r="G8">
-        <v>0.5</v>
+        <v>0.462</v>
       </c>
       <c r="H8">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2621,28 +2722,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>113.96</v>
+        <v>105.43</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9">
-        <v>114.78</v>
+        <v>115.27</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.577</v>
       </c>
       <c r="H9">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2650,28 +2751,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10">
-        <v>135.64</v>
+        <v>114.19</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>112.43</v>
+        <v>113.3</v>
       </c>
       <c r="G10">
-        <v>0.429</v>
+        <v>0.5</v>
       </c>
       <c r="H10">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="I10">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2679,28 +2780,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D11">
-        <v>150.66</v>
+        <v>111.82</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>114.2</v>
+        <v>113.59</v>
       </c>
       <c r="G11">
-        <v>0.429</v>
+        <v>0.5</v>
       </c>
       <c r="H11">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="I11">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2708,28 +2809,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D12">
-        <v>128.76</v>
+        <v>140.59</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
       </c>
       <c r="F12">
-        <v>117.24</v>
+        <v>110.5</v>
       </c>
       <c r="G12">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="H12">
         <v>-0.7</v>
       </c>
       <c r="I12">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2737,28 +2838,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D13">
-        <v>139.8</v>
+        <v>126.04</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13">
-        <v>111.93</v>
+        <v>111.78</v>
       </c>
       <c r="G13">
-        <v>0.429</v>
+        <v>0.462</v>
       </c>
       <c r="H13">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="I13">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2773,286 +2874,286 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>150.66</v>
+        <v>128.05</v>
       </c>
       <c r="E2">
-        <v>150.66</v>
+        <v>256.1</v>
       </c>
       <c r="F2">
-        <v>96.39999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D3">
-        <v>139.8</v>
+        <v>140.59</v>
       </c>
       <c r="E3">
-        <v>139.8</v>
+        <v>281.18</v>
       </c>
       <c r="F3">
-        <v>85</v>
+        <v>82.69999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D4">
-        <v>135.64</v>
+        <v>126.04</v>
       </c>
       <c r="E4">
-        <v>135.64</v>
+        <v>252.08</v>
       </c>
       <c r="F4">
-        <v>77</v>
+        <v>56.89999999999999</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>137.2</v>
+        <v>113.16</v>
       </c>
       <c r="E5">
-        <v>137.2</v>
+        <v>226.32</v>
       </c>
       <c r="F5">
-        <v>74</v>
+        <v>50.3</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>128.56</v>
+        <v>114.19</v>
       </c>
       <c r="E6">
-        <v>128.56</v>
+        <v>228.38</v>
       </c>
       <c r="F6">
-        <v>34.4</v>
+        <v>26.1</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>128.76</v>
+        <v>110.48</v>
       </c>
       <c r="E7">
-        <v>128.76</v>
+        <v>220.96</v>
       </c>
       <c r="F7">
-        <v>22.3</v>
+        <v>21.3</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>113.96</v>
+        <v>111.82</v>
       </c>
       <c r="E8">
-        <v>113.96</v>
+        <v>223.64</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>20.5</v>
       </c>
       <c r="G8">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="H8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>111.5</v>
+        <v>109.55</v>
       </c>
       <c r="E9">
-        <v>111.5</v>
+        <v>219.1</v>
       </c>
       <c r="F9">
-        <v>4.8</v>
+        <v>18.5</v>
       </c>
       <c r="G9">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="H9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>103.82</v>
+        <v>112.23</v>
       </c>
       <c r="E10">
-        <v>103.82</v>
+        <v>224.46</v>
       </c>
       <c r="F10">
-        <v>0.7000000000000001</v>
+        <v>17.9</v>
       </c>
       <c r="G10">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="H10" t="s">
         <v>72</v>
@@ -3063,28 +3164,28 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
-        <v>103.96</v>
+        <v>109.02</v>
       </c>
       <c r="E11">
-        <v>103.96</v>
+        <v>218.04</v>
       </c>
       <c r="F11">
-        <v>0.4</v>
+        <v>17.1</v>
       </c>
       <c r="G11">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I11" t="s">
         <v>80</v>
@@ -3095,28 +3196,28 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>99.66</v>
+        <v>105.43</v>
       </c>
       <c r="E12">
-        <v>99.66</v>
+        <v>210.86</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="G12">
-        <v>3.6</v>
+        <v>16.9</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3124,28 +3225,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>63.94</v>
+        <v>84.22999999999999</v>
       </c>
       <c r="E13">
-        <v>63.94</v>
+        <v>168.46</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G13">
-        <v>93.2</v>
+        <v>68.60000000000001</v>
       </c>
       <c r="H13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -3160,19 +3261,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3183,16 +3284,16 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3200,10 +3301,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3">
         <v>6</v>
@@ -3211,8 +3312,8 @@
       <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="F3">
-        <v>0</v>
+      <c r="F3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3220,19 +3321,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3243,16 +3344,16 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
-      <c r="F5">
-        <v>0</v>
+      <c r="F5" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3260,19 +3361,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3280,19 +3381,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
       </c>
-      <c r="F7">
-        <v>0</v>
+      <c r="F7" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3300,19 +3401,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3320,19 +3421,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
       </c>
-      <c r="F9">
-        <v>0</v>
+      <c r="F9" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3340,19 +3441,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3360,19 +3461,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
       </c>
-      <c r="F11">
-        <v>0</v>
+      <c r="F11" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3380,19 +3481,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D12">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F12" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3400,10 +3501,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13">
         <v>-8</v>
@@ -3411,8 +3512,8 @@
       <c r="E13" t="s">
         <v>13</v>
       </c>
-      <c r="F13">
-        <v>0</v>
+      <c r="F13" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3422,18 +3523,21 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3441,32 +3545,41 @@
         <v>8</v>
       </c>
       <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="C3">
         <v>6</v>
       </c>
-      <c r="B3">
+      <c r="D3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>-1</v>
+      </c>
+      <c r="C4">
         <v>6</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -3474,95 +3587,122 @@
         <v>1</v>
       </c>
       <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>-1</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>-2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>-2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>-6</v>
+      </c>
+      <c r="C9">
+        <v>-2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
+      <c r="C10">
+        <v>-6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>-1</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>-1</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>-2</v>
-      </c>
       <c r="C11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>-7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="C12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>-7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
         <v>-8</v>
       </c>
-      <c r="C13">
-        <v>0</v>
+      <c r="D13" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/The Girl's Room 💞🏈 2026.xlsx
+++ b/data/leagues/The Girl's Room 💞🏈 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="107">
   <si>
     <t>Tush Push Director 🍑</t>
   </si>
@@ -226,34 +226,40 @@
     <t>0-2</t>
   </si>
   <si>
-    <t>10.4-4.5-0.1</t>
-  </si>
-  <si>
-    <t>9.9-5.0-0.1</t>
-  </si>
-  <si>
-    <t>8.7-6.2-0.1</t>
-  </si>
-  <si>
-    <t>7.5-7.3-0.1</t>
-  </si>
-  <si>
-    <t>7.3-7.6-0.1</t>
+    <t>10.4-4.4-0.1</t>
+  </si>
+  <si>
+    <t>9.8-5.1-0.1</t>
+  </si>
+  <si>
+    <t>8.8-6.2-0.1</t>
+  </si>
+  <si>
+    <t>8.6-6.3-0.1</t>
+  </si>
+  <si>
+    <t>7.6-7.2-0.1</t>
+  </si>
+  <si>
+    <t>7.2-7.7-0.1</t>
   </si>
   <si>
     <t>7.2-7.6-0.2</t>
   </si>
   <si>
+    <t>7.1-7.7-0.2</t>
+  </si>
+  <si>
     <t>7.1-7.8-0.1</t>
   </si>
   <si>
     <t>7.0-7.9-0.1</t>
   </si>
   <si>
-    <t>4.9-9.9-0.2</t>
-  </si>
-  <si>
-    <t>3.5-11.4-0.1</t>
+    <t>5.0-9.8-0.1</t>
+  </si>
+  <si>
+    <t>3.4-11.5-0.1</t>
   </si>
   <si>
     <t>11-4</t>
@@ -268,13 +274,10 @@
     <t>7-8</t>
   </si>
   <si>
-    <t>8-7</t>
-  </si>
-  <si>
     <t>5-10</t>
   </si>
   <si>
-    <t>4-11</t>
+    <t>3-12</t>
   </si>
   <si>
     <t>Owners</t>
@@ -1243,25 +1246,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1766,43 +1769,43 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>37.8</v>
+        <v>39.1</v>
       </c>
       <c r="C2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2">
-        <v>15.6</v>
+        <v>16.3</v>
       </c>
       <c r="E2">
-        <v>11.1</v>
+        <v>7.9</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="G2">
         <v>3.4</v>
       </c>
       <c r="H2">
+        <v>2.6</v>
+      </c>
+      <c r="I2">
         <v>1.4</v>
       </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
       <c r="J2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>87.5</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1810,43 +1813,43 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>35.1</v>
+        <v>33.3</v>
       </c>
       <c r="C3">
-        <v>24.4</v>
+        <v>22.7</v>
       </c>
       <c r="D3">
-        <v>13.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3">
-        <v>9.300000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="F3">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="G3">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="H3">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L3">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1854,43 +1857,43 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="C4">
-        <v>16.4</v>
+        <v>15.9</v>
       </c>
       <c r="D4">
-        <v>16.4</v>
+        <v>15.9</v>
       </c>
       <c r="E4">
-        <v>13.6</v>
+        <v>16.3</v>
       </c>
       <c r="F4">
-        <v>10.8</v>
+        <v>11.9</v>
       </c>
       <c r="G4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="J4">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="M4">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="N4">
-        <v>56.9</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1898,43 +1901,43 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="C5">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="D5">
-        <v>14.9</v>
+        <v>13.7</v>
       </c>
       <c r="E5">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>11.1</v>
+        <v>12.8</v>
       </c>
       <c r="G5">
-        <v>8.9</v>
+        <v>11.5</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="J5">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="K5">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="L5">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="M5">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="N5">
-        <v>50.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1942,43 +1945,43 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="C6">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="D6">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="E6">
-        <v>9.6</v>
+        <v>12.3</v>
       </c>
       <c r="F6">
-        <v>12.8</v>
+        <v>11.7</v>
       </c>
       <c r="G6">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="H6">
-        <v>12.8</v>
+        <v>10.1</v>
       </c>
       <c r="I6">
-        <v>11.6</v>
+        <v>11.1</v>
       </c>
       <c r="J6">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="K6">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="L6">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>26.1</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1986,43 +1989,43 @@
         <v>1</v>
       </c>
       <c r="B7">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="C7">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="E7">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="G7">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="I7">
         <v>11.6</v>
       </c>
       <c r="J7">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="K7">
-        <v>9.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="L7">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N7">
-        <v>21.3</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -2033,128 +2036,128 @@
         <v>1.5</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="D8">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="E8">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="F8">
         <v>9.9</v>
       </c>
       <c r="G8">
-        <v>11.7</v>
+        <v>12.6</v>
       </c>
       <c r="H8">
-        <v>13.9</v>
+        <v>15.2</v>
       </c>
       <c r="I8">
+        <v>13.7</v>
+      </c>
+      <c r="J8">
         <v>13.1</v>
       </c>
-      <c r="J8">
-        <v>12.4</v>
-      </c>
       <c r="K8">
-        <v>10.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L8">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>20.5</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>1.5</v>
+      </c>
+      <c r="C9">
+        <v>2.8</v>
+      </c>
+      <c r="D9">
         <v>6</v>
       </c>
-      <c r="B9">
-        <v>1.1</v>
-      </c>
-      <c r="C9">
-        <v>2.9</v>
-      </c>
-      <c r="D9">
-        <v>6.1</v>
-      </c>
       <c r="E9">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F9">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="G9">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="H9">
-        <v>11</v>
+        <v>14.3</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>13.3</v>
       </c>
       <c r="J9">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="K9">
-        <v>12.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L9">
-        <v>10.5</v>
+        <v>6.3</v>
       </c>
       <c r="M9">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="N9">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="C10">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="D10">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="E10">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="F10">
-        <v>11.9</v>
+        <v>10.7</v>
       </c>
       <c r="G10">
-        <v>13.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H10">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="I10">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="J10">
-        <v>13.6</v>
+        <v>11.6</v>
       </c>
       <c r="K10">
-        <v>11</v>
+        <v>14.2</v>
       </c>
       <c r="L10">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="M10">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="N10">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2162,43 +2165,43 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="C11">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="D11">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="E11">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="F11">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G11">
-        <v>9.699999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="H11">
-        <v>11.4</v>
+        <v>12.9</v>
       </c>
       <c r="I11">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="J11">
-        <v>12.2</v>
+        <v>12.9</v>
       </c>
       <c r="K11">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="L11">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="M11">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="N11">
-        <v>17.1</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2209,40 +2212,40 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D12">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E12">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F12">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="G12">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="H12">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="I12">
         <v>7.8</v>
       </c>
       <c r="J12">
-        <v>10.2</v>
+        <v>13.3</v>
       </c>
       <c r="K12">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="L12">
-        <v>35.9</v>
+        <v>32.7</v>
       </c>
       <c r="M12">
-        <v>16.9</v>
+        <v>16.6</v>
       </c>
       <c r="N12">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2253,37 +2256,37 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>0.5</v>
       </c>
-      <c r="G13">
-        <v>0.6</v>
-      </c>
       <c r="H13">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I13">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J13">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="K13">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="L13">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="M13">
-        <v>68.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="N13">
         <v>0.1</v>
@@ -2315,13 +2318,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>88.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C2">
-        <v>89.3</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D2">
-        <v>85.5</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2329,13 +2332,13 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="C3">
-        <v>85.09999999999999</v>
+        <v>84.39999999999999</v>
       </c>
       <c r="D3">
-        <v>81.3</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2343,13 +2346,13 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>95.39999999999999</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="C4">
-        <v>55.3</v>
+        <v>60.4</v>
       </c>
       <c r="D4">
-        <v>53.40000000000001</v>
+        <v>53.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2357,13 +2360,13 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>78</v>
+        <v>78.60000000000001</v>
       </c>
       <c r="C5">
-        <v>46.1</v>
+        <v>47.8</v>
       </c>
       <c r="D5">
-        <v>52.6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2371,13 +2374,13 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="C6">
-        <v>26.6</v>
+        <v>28.1</v>
       </c>
       <c r="D6">
-        <v>30.2</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2385,13 +2388,13 @@
         <v>1</v>
       </c>
       <c r="B7">
-        <v>74</v>
+        <v>74.7</v>
       </c>
       <c r="C7">
-        <v>22.2</v>
+        <v>21.8</v>
       </c>
       <c r="D7">
-        <v>22.8</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2399,27 +2402,27 @@
         <v>5</v>
       </c>
       <c r="B8">
-        <v>0.4</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="C8">
-        <v>20.8</v>
+        <v>18.3</v>
       </c>
       <c r="D8">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>21.8</v>
+        <v>31.3</v>
       </c>
       <c r="C9">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="D9">
-        <v>19.6</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2427,27 +2430,27 @@
         <v>7</v>
       </c>
       <c r="B10">
-        <v>6.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>16.6</v>
+        <v>16.9</v>
       </c>
       <c r="D10">
-        <v>18.2</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B11">
-        <v>30.7</v>
+        <v>20.7</v>
       </c>
       <c r="C11">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
       <c r="D11">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2458,10 +2461,10 @@
         <v>0.1</v>
       </c>
       <c r="C12">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2475,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -2918,7 +2921,7 @@
         <v>256.1</v>
       </c>
       <c r="F2">
-        <v>87.5</v>
+        <v>87.3</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2927,7 +2930,7 @@
         <v>67</v>
       </c>
       <c r="I2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2947,7 +2950,7 @@
         <v>281.18</v>
       </c>
       <c r="F3">
-        <v>82.69999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2956,7 +2959,7 @@
         <v>68</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2976,16 +2979,16 @@
         <v>252.08</v>
       </c>
       <c r="F4">
-        <v>56.89999999999999</v>
+        <v>58.2</v>
       </c>
       <c r="G4">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H4" t="s">
         <v>69</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3005,16 +3008,16 @@
         <v>226.32</v>
       </c>
       <c r="F5">
-        <v>50.3</v>
+        <v>47.4</v>
       </c>
       <c r="G5">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3034,16 +3037,16 @@
         <v>228.38</v>
       </c>
       <c r="F6">
-        <v>26.1</v>
+        <v>30.5</v>
       </c>
       <c r="G6">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3063,16 +3066,16 @@
         <v>220.96</v>
       </c>
       <c r="F7">
-        <v>21.3</v>
+        <v>22.2</v>
       </c>
       <c r="G7">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3092,21 +3095,21 @@
         <v>223.64</v>
       </c>
       <c r="F8">
-        <v>20.5</v>
+        <v>18.8</v>
       </c>
       <c r="G8">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>65</v>
@@ -3115,27 +3118,27 @@
         <v>0.5</v>
       </c>
       <c r="D9">
-        <v>109.55</v>
+        <v>112.23</v>
       </c>
       <c r="E9">
-        <v>219.1</v>
+        <v>224.46</v>
       </c>
       <c r="F9">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="G9">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="H9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
         <v>65</v>
@@ -3144,22 +3147,22 @@
         <v>0.5</v>
       </c>
       <c r="D10">
-        <v>112.23</v>
+        <v>109.55</v>
       </c>
       <c r="E10">
-        <v>224.46</v>
+        <v>219.1</v>
       </c>
       <c r="F10">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="G10">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3179,16 +3182,16 @@
         <v>218.04</v>
       </c>
       <c r="F11">
-        <v>17.1</v>
+        <v>15.6</v>
       </c>
       <c r="G11">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="H11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3208,16 +3211,16 @@
         <v>210.86</v>
       </c>
       <c r="F12">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="G12">
-        <v>16.9</v>
+        <v>16.6</v>
       </c>
       <c r="H12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3240,13 +3243,13 @@
         <v>0.1</v>
       </c>
       <c r="G13">
-        <v>68.60000000000001</v>
+        <v>69.89999999999999</v>
       </c>
       <c r="H13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -3264,16 +3267,16 @@
         <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3293,7 +3296,7 @@
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3313,7 +3316,7 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3333,7 +3336,7 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3353,7 +3356,7 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3373,7 +3376,7 @@
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3393,7 +3396,7 @@
         <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3413,7 +3416,7 @@
         <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3433,7 +3436,7 @@
         <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3453,7 +3456,7 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3473,7 +3476,7 @@
         <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3493,7 +3496,7 @@
         <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3513,7 +3516,7 @@
         <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3528,13 +3531,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3548,7 +3551,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3562,7 +3565,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3576,7 +3579,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3590,7 +3593,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3604,7 +3607,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3618,7 +3621,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3632,7 +3635,7 @@
         <v>-2</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3646,7 +3649,7 @@
         <v>-2</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3660,7 +3663,7 @@
         <v>-6</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3674,7 +3677,7 @@
         <v>-7</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3688,7 +3691,7 @@
         <v>-7</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3702,7 +3705,7 @@
         <v>-8</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/The Girl's Room 💞🏈 2026.xlsx
+++ b/data/leagues/The Girl's Room 💞🏈 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="108">
   <si>
     <t>Tush Push Director 🍑</t>
   </si>
@@ -55,19 +55,22 @@
     <t xml:space="preserve">Hurts so Good </t>
   </si>
   <si>
-    <t>Bianca</t>
+    <t>Rolling with the Homies</t>
   </si>
   <si>
     <t xml:space="preserve">michelle’s boy toys </t>
   </si>
   <si>
-    <t>2-0-0</t>
-  </si>
-  <si>
-    <t>1-1-0</t>
-  </si>
-  <si>
-    <t>0-2-0</t>
+    <t>2-1-0</t>
+  </si>
+  <si>
+    <t>1-2-0</t>
+  </si>
+  <si>
+    <t>3-0-0</t>
+  </si>
+  <si>
+    <t>0-3-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -136,6 +139,9 @@
     <t>Week_3</t>
   </si>
   <si>
+    <t>Week_4</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -157,42 +163,42 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Kiana McIntosh</t>
+  </si>
+  <si>
+    <t>Emily Carey</t>
+  </si>
+  <si>
+    <t>Amanda Pasquale</t>
+  </si>
+  <si>
+    <t>Michelle Nocitra</t>
+  </si>
+  <si>
+    <t>Sumita Gangwani</t>
+  </si>
+  <si>
+    <t>Hannah Miller</t>
+  </si>
+  <si>
+    <t>Allie Kardon</t>
+  </si>
+  <si>
+    <t>Malini Ragoopath</t>
+  </si>
+  <si>
+    <t>Grace Stockbower</t>
+  </si>
+  <si>
+    <t>nidhi shah</t>
+  </si>
+  <si>
+    <t>Hillary Dale</t>
+  </si>
+  <si>
     <t>Bianca Magsino</t>
   </si>
   <si>
-    <t>Hannah Miller</t>
-  </si>
-  <si>
-    <t>Michelle Nocitra</t>
-  </si>
-  <si>
-    <t>Malini Ragoopath</t>
-  </si>
-  <si>
-    <t>Kiana McIntosh</t>
-  </si>
-  <si>
-    <t>nidhi shah</t>
-  </si>
-  <si>
-    <t>Sumita Gangwani</t>
-  </si>
-  <si>
-    <t>Amanda Pasquale</t>
-  </si>
-  <si>
-    <t>Emily Carey</t>
-  </si>
-  <si>
-    <t>Hillary Dale</t>
-  </si>
-  <si>
-    <t>Allie Kardon</t>
-  </si>
-  <si>
-    <t>Grace Stockbower</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -217,52 +223,52 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>10.4-4.4-0.1</t>
-  </si>
-  <si>
-    <t>9.8-5.1-0.1</t>
-  </si>
-  <si>
-    <t>8.8-6.2-0.1</t>
-  </si>
-  <si>
-    <t>8.6-6.3-0.1</t>
-  </si>
-  <si>
-    <t>7.6-7.2-0.1</t>
-  </si>
-  <si>
-    <t>7.2-7.7-0.1</t>
-  </si>
-  <si>
-    <t>7.2-7.6-0.2</t>
-  </si>
-  <si>
-    <t>7.1-7.7-0.2</t>
-  </si>
-  <si>
-    <t>7.1-7.8-0.1</t>
-  </si>
-  <si>
-    <t>7.0-7.9-0.1</t>
-  </si>
-  <si>
-    <t>5.0-9.8-0.1</t>
-  </si>
-  <si>
-    <t>3.4-11.5-0.1</t>
-  </si>
-  <si>
-    <t>11-4</t>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>11.4-3.5-0.1</t>
+  </si>
+  <si>
+    <t>9.6-5.3-0.1</t>
+  </si>
+  <si>
+    <t>8.8-6.1-0.1</t>
+  </si>
+  <si>
+    <t>8.7-6.2-0.2</t>
+  </si>
+  <si>
+    <t>8.7-6.1-0.1</t>
+  </si>
+  <si>
+    <t>8.2-6.6-0.1</t>
+  </si>
+  <si>
+    <t>7.6-7.3-0.1</t>
+  </si>
+  <si>
+    <t>7.7-7.2-0.2</t>
+  </si>
+  <si>
+    <t>7.0-7.8-0.2</t>
+  </si>
+  <si>
+    <t>4.4-10.5-0.1</t>
+  </si>
+  <si>
+    <t>5.2-9.7-0.1</t>
+  </si>
+  <si>
+    <t>2.0-12.9-0.1</t>
+  </si>
+  <si>
+    <t>12-3</t>
   </si>
   <si>
     <t>10-5</t>
@@ -271,13 +277,16 @@
     <t>9-6</t>
   </si>
   <si>
+    <t>8-7</t>
+  </si>
+  <si>
     <t>7-8</t>
   </si>
   <si>
     <t>5-10</t>
   </si>
   <si>
-    <t>3-12</t>
+    <t>2-13</t>
   </si>
   <si>
     <t>Owners</t>
@@ -289,40 +298,34 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>↑2</t>
   </si>
   <si>
-    <t>↑6</t>
-  </si>
-  <si>
-    <t>↑7</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↑5</t>
-  </si>
-  <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↓8</t>
-  </si>
-  <si>
-    <t>↓6</t>
-  </si>
-  <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↓10</t>
+    <t>↓5</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
+    <t>↓7</t>
   </si>
   <si>
     <t>Week 1</t>
   </si>
   <si>
     <t>Week 2</t>
+  </si>
+  <si>
+    <t>Week 3</t>
   </si>
   <si>
     <t>Week</t>
@@ -756,16 +759,16 @@
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
@@ -777,7 +780,7 @@
         <v>12</v>
       </c>
       <c r="L2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M2" t="s">
         <v>12</v>
@@ -806,13 +809,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
         <v>13</v>
@@ -838,16 +841,16 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
         <v>13</v>
@@ -873,37 +876,37 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -914,34 +917,34 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6" t="s">
         <v>13</v>
       </c>
       <c r="L6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M6" t="s">
         <v>13</v>
@@ -958,13 +961,13 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -976,7 +979,7 @@
         <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
         <v>12</v>
@@ -993,40 +996,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" t="s">
-        <v>12</v>
-      </c>
       <c r="L8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1034,40 +1037,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" t="s">
         <v>14</v>
       </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" t="s">
-        <v>12</v>
-      </c>
       <c r="L9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1078,37 +1081,37 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1119,34 +1122,34 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" t="s">
         <v>14</v>
-      </c>
-      <c r="H11" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" t="s">
-        <v>12</v>
       </c>
       <c r="M11" t="s">
         <v>13</v>
@@ -1157,40 +1160,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1198,31 +1201,31 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K13" t="s">
         <v>13</v>
@@ -1231,7 +1234,7 @@
         <v>13</v>
       </c>
       <c r="M13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1241,30 +1244,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1272,25 +1275,103 @@
         <v>0</v>
       </c>
       <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>-4</v>
+      </c>
+      <c r="G2">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>2</v>
       </c>
-      <c r="F2">
+      <c r="F3">
         <v>10</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>8</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H3" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1305,13 +1386,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1319,13 +1400,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1333,10 +1414,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -1347,10 +1428,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>0.5833333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1361,13 +1442,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>0.9166666666666666</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1375,13 +1456,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0.9166666666666666</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1389,13 +1470,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1403,13 +1484,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1417,13 +1498,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>1.166666666666667</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1431,13 +1512,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>1.25</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1445,10 +1526,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>1.333333333333333</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
@@ -1459,13 +1540,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1473,13 +1554,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>1.583333333333333</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1494,16 +1575,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1511,13 +1592,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>1.666666666666667</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="D2">
-        <v>-0.3333333333333333</v>
+        <v>0.1666666666666665</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -1528,16 +1609,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>1.416666666666667</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>0.4166666666666667</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1545,16 +1626,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>1.333333333333333</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D4">
-        <v>0.3333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1562,13 +1643,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>1.083333333333333</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D5">
-        <v>-0.9166666666666667</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -1582,13 +1663,13 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>1.083333333333333</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D6">
-        <v>0.08333333333333326</v>
+        <v>-0.4166666666666667</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1596,16 +1677,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>1.083333333333333</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D7">
-        <v>0.08333333333333326</v>
+        <v>-0.4166666666666667</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1613,16 +1694,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>-0.4166666666666667</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1630,13 +1711,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>0.8333333333333334</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D9">
-        <v>-0.1666666666666666</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -1647,13 +1728,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>0.8333333333333334</v>
+        <v>1.25</v>
       </c>
       <c r="D10">
-        <v>-0.1666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
@@ -1664,13 +1745,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11">
-        <v>0.6666666666666666</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="D11">
-        <v>-0.3333333333333334</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -1681,16 +1762,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>0.5833333333333334</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D12">
-        <v>0.5833333333333334</v>
+        <v>-0.1666666666666666</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1701,13 +1782,13 @@
         <v>11</v>
       </c>
       <c r="C13">
-        <v>0.4166666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D13">
-        <v>0.4166666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1722,395 +1803,395 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>39.1</v>
+        <v>69.8</v>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>15.1</v>
       </c>
       <c r="D2">
-        <v>16.3</v>
+        <v>7.3</v>
       </c>
       <c r="E2">
-        <v>7.9</v>
+        <v>3.9</v>
       </c>
       <c r="F2">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="G2">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="H2">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="I2">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J2">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>87.3</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>33.3</v>
+        <v>11.8</v>
       </c>
       <c r="C3">
-        <v>22.7</v>
+        <v>26.6</v>
       </c>
       <c r="D3">
-        <v>15.6</v>
+        <v>20.3</v>
       </c>
       <c r="E3">
-        <v>11.2</v>
+        <v>14.1</v>
       </c>
       <c r="F3">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G3">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="I3">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="K3">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L3">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
-        <v>82.8</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>10.1</v>
+        <v>4.8</v>
       </c>
       <c r="C4">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="D4">
-        <v>15.9</v>
+        <v>17.7</v>
       </c>
       <c r="E4">
-        <v>16.3</v>
+        <v>14.2</v>
       </c>
       <c r="F4">
-        <v>11.9</v>
+        <v>13.9</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>12.7</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="L4">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="M4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>58.2</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="C5">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="D5">
-        <v>13.7</v>
+        <v>16.3</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="F5">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="G5">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>11</v>
       </c>
       <c r="I5">
-        <v>6.5</v>
+        <v>8.9</v>
       </c>
       <c r="J5">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="K5">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="L5">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="M5">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>47.4</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="C6">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>9.5</v>
+        <v>15.9</v>
       </c>
       <c r="E6">
-        <v>12.3</v>
+        <v>14.1</v>
       </c>
       <c r="F6">
-        <v>11.7</v>
+        <v>13.9</v>
       </c>
       <c r="G6">
-        <v>12.1</v>
+        <v>11.3</v>
       </c>
       <c r="H6">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="I6">
-        <v>11.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>6.9</v>
       </c>
       <c r="K6">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>30.5</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D7">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>13.6</v>
       </c>
       <c r="F7">
-        <v>10.4</v>
+        <v>14.8</v>
       </c>
       <c r="G7">
+        <v>13.8</v>
+      </c>
+      <c r="H7">
+        <v>12.1</v>
+      </c>
+      <c r="I7">
+        <v>12.6</v>
+      </c>
+      <c r="J7">
         <v>10</v>
       </c>
-      <c r="H7">
-        <v>9.9</v>
-      </c>
-      <c r="I7">
-        <v>11.6</v>
-      </c>
-      <c r="J7">
-        <v>11.9</v>
-      </c>
       <c r="K7">
-        <v>10.6</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="M7">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="N7">
-        <v>22.2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B8">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="C8">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="E8">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="F8">
-        <v>9.9</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>12.6</v>
+        <v>14.2</v>
       </c>
       <c r="H8">
+        <v>15.4</v>
+      </c>
+      <c r="I8">
+        <v>14.9</v>
+      </c>
+      <c r="J8">
         <v>15.2</v>
       </c>
-      <c r="I8">
-        <v>13.7</v>
-      </c>
-      <c r="J8">
-        <v>13.1</v>
-      </c>
       <c r="K8">
-        <v>9.699999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="L8">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="N8">
-        <v>18.8</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>1.2</v>
+      </c>
+      <c r="C9">
+        <v>3.6</v>
+      </c>
+      <c r="D9">
+        <v>5.3</v>
+      </c>
+      <c r="E9">
+        <v>8.5</v>
+      </c>
+      <c r="F9">
+        <v>11.1</v>
+      </c>
+      <c r="G9">
+        <v>13.5</v>
+      </c>
+      <c r="H9">
+        <v>16.8</v>
+      </c>
+      <c r="I9">
+        <v>17.2</v>
+      </c>
+      <c r="J9">
+        <v>14.3</v>
+      </c>
+      <c r="K9">
         <v>7</v>
       </c>
-      <c r="B9">
-        <v>1.5</v>
-      </c>
-      <c r="C9">
-        <v>2.8</v>
-      </c>
-      <c r="D9">
-        <v>6</v>
-      </c>
-      <c r="E9">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="F9">
-        <v>11.3</v>
-      </c>
-      <c r="G9">
-        <v>12.1</v>
-      </c>
-      <c r="H9">
-        <v>14.3</v>
-      </c>
-      <c r="I9">
-        <v>13.3</v>
-      </c>
-      <c r="J9">
-        <v>12.6</v>
-      </c>
-      <c r="K9">
-        <v>9.699999999999999</v>
-      </c>
       <c r="L9">
-        <v>6.3</v>
+        <v>1.3</v>
       </c>
       <c r="M9">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="N9">
         <v>18.6</v>
@@ -2118,134 +2199,134 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B10">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="C10">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="E10">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="F10">
-        <v>10.7</v>
+        <v>7.9</v>
       </c>
       <c r="G10">
-        <v>9.699999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="H10">
-        <v>11.6</v>
+        <v>14.5</v>
       </c>
       <c r="I10">
-        <v>13.8</v>
+        <v>17.2</v>
       </c>
       <c r="J10">
-        <v>11.6</v>
+        <v>19.3</v>
       </c>
       <c r="K10">
-        <v>14.2</v>
+        <v>11.7</v>
       </c>
       <c r="L10">
-        <v>8.6</v>
+        <v>4.3</v>
       </c>
       <c r="M10">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="N10">
-        <v>17.1</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B11">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="D11">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="F11">
-        <v>8.699999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="G11">
-        <v>11.4</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>12.9</v>
+        <v>1.7</v>
       </c>
       <c r="I11">
-        <v>11.8</v>
+        <v>4.3</v>
       </c>
       <c r="J11">
-        <v>12.9</v>
+        <v>6.3</v>
       </c>
       <c r="K11">
-        <v>14.6</v>
+        <v>22.3</v>
       </c>
       <c r="L11">
-        <v>9.5</v>
+        <v>52.4</v>
       </c>
       <c r="M11">
-        <v>2.6</v>
+        <v>11.1</v>
       </c>
       <c r="N11">
-        <v>15.6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C12">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
         <v>0.4</v>
       </c>
-      <c r="E12">
-        <v>0.7</v>
-      </c>
       <c r="F12">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G12">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="H12">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="I12">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="J12">
-        <v>13.3</v>
+        <v>16</v>
       </c>
       <c r="K12">
-        <v>19</v>
+        <v>41.9</v>
       </c>
       <c r="L12">
-        <v>32.7</v>
+        <v>23.9</v>
       </c>
       <c r="M12">
-        <v>16.6</v>
+        <v>3.2</v>
       </c>
       <c r="N12">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2256,7 +2337,7 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -2268,28 +2349,28 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="K13">
-        <v>6.5</v>
+        <v>1.9</v>
       </c>
       <c r="L13">
-        <v>17.3</v>
+        <v>12.6</v>
       </c>
       <c r="M13">
-        <v>69.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="N13">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2299,175 +2380,211 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>37</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>88.40000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="C2">
-        <v>89.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D2">
-        <v>88.40000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>97.3</v>
+      </c>
+      <c r="E2">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>3.8</v>
+        <v>16.1</v>
       </c>
       <c r="C3">
-        <v>84.39999999999999</v>
+        <v>12</v>
       </c>
       <c r="D3">
-        <v>85.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="E3">
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>2.5</v>
+      </c>
+      <c r="C4">
+        <v>12.2</v>
+      </c>
+      <c r="D4">
+        <v>47.09999999999999</v>
+      </c>
+      <c r="E4">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>93.30000000000001</v>
+      </c>
+      <c r="C5">
+        <v>93.60000000000001</v>
+      </c>
+      <c r="D5">
+        <v>47.8</v>
+      </c>
+      <c r="E5">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>24.9</v>
+      </c>
+      <c r="C6">
+        <v>7.9</v>
+      </c>
+      <c r="D6">
+        <v>46.1</v>
+      </c>
+      <c r="E6">
+        <v>49.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>82.89999999999999</v>
+      </c>
+      <c r="C7">
+        <v>48.9</v>
+      </c>
+      <c r="D7">
+        <v>29.4</v>
+      </c>
+      <c r="E7">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>95.19999999999999</v>
-      </c>
-      <c r="C4">
-        <v>60.4</v>
-      </c>
-      <c r="D4">
-        <v>53.90000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>78.60000000000001</v>
-      </c>
-      <c r="C5">
-        <v>47.8</v>
-      </c>
-      <c r="D5">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="B8">
+        <v>97.89999999999999</v>
+      </c>
+      <c r="C8">
+        <v>78.2</v>
+      </c>
+      <c r="D8">
+        <v>19.5</v>
+      </c>
+      <c r="E8">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>0.1</v>
-      </c>
-      <c r="C6">
-        <v>28.1</v>
-      </c>
-      <c r="D6">
-        <v>28.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>22.5</v>
+      </c>
+      <c r="D9">
+        <v>24.1</v>
+      </c>
+      <c r="E9">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0.8</v>
+      </c>
+      <c r="D10">
+        <v>13.9</v>
+      </c>
+      <c r="E10">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>13.9</v>
+      </c>
+      <c r="D11">
         <v>1</v>
       </c>
-      <c r="B7">
-        <v>74.7</v>
-      </c>
-      <c r="C7">
-        <v>21.8</v>
-      </c>
-      <c r="D7">
-        <v>23.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>0.7000000000000001</v>
-      </c>
-      <c r="C8">
-        <v>18.3</v>
-      </c>
-      <c r="D8">
-        <v>19.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>31.3</v>
-      </c>
-      <c r="C9">
-        <v>15</v>
-      </c>
-      <c r="D9">
-        <v>18.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>16.9</v>
-      </c>
-      <c r="D10">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11">
-        <v>20.7</v>
-      </c>
-      <c r="C11">
-        <v>16.4</v>
-      </c>
-      <c r="D11">
-        <v>15.6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B12">
-        <v>0.1</v>
+        <v>80.60000000000001</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>12.4</v>
       </c>
       <c r="D12">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>0.2</v>
+      </c>
+      <c r="E12">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -2478,7 +2595,10 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2493,28 +2613,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2522,28 +2642,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2">
-        <v>109.02</v>
+        <v>93.75</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
       </c>
       <c r="F2">
-        <v>114.79</v>
+        <v>114.43</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.528</v>
       </c>
       <c r="H2">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2551,28 +2671,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3">
-        <v>109.55</v>
+        <v>110.5</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>113.79</v>
+        <v>111.86</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>0.472</v>
       </c>
       <c r="H3">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2580,28 +2700,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4">
-        <v>84.23</v>
+        <v>113.65</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>118.02</v>
+        <v>112.74</v>
       </c>
       <c r="G4">
-        <v>0.577</v>
+        <v>0.5</v>
       </c>
       <c r="H4">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2609,28 +2729,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5">
-        <v>112.23</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>114.63</v>
+        <v>114.72</v>
       </c>
       <c r="G5">
-        <v>0.538</v>
+        <v>0.556</v>
       </c>
       <c r="H5">
         <v>0.3</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2638,28 +2758,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>110.48</v>
+        <v>119.25</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>113.66</v>
+        <v>114.04</v>
       </c>
       <c r="G6">
         <v>0.5</v>
       </c>
       <c r="H6">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2667,28 +2787,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7">
-        <v>113.16</v>
+        <v>124.23</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
       </c>
       <c r="F7">
-        <v>110.87</v>
+        <v>112.06</v>
       </c>
       <c r="G7">
-        <v>0.385</v>
+        <v>0.5</v>
       </c>
       <c r="H7">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2696,28 +2816,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8">
-        <v>128.05</v>
+        <v>137.47</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
       </c>
       <c r="F8">
-        <v>114.58</v>
+        <v>111.01</v>
       </c>
       <c r="G8">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2725,28 +2845,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9">
-        <v>105.43</v>
+        <v>118.67</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>115.27</v>
+        <v>112.99</v>
       </c>
       <c r="G9">
-        <v>0.577</v>
+        <v>0.5</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2754,19 +2874,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10">
-        <v>114.19</v>
+        <v>116.27</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
       </c>
       <c r="F10">
-        <v>113.3</v>
+        <v>112.3</v>
       </c>
       <c r="G10">
         <v>0.5</v>
@@ -2775,7 +2895,7 @@
         <v>-0.3</v>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2783,28 +2903,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11">
-        <v>111.82</v>
+        <v>111.87</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>113.59</v>
+        <v>110.33</v>
       </c>
       <c r="G11">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="H11">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2812,28 +2932,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D12">
-        <v>140.59</v>
+        <v>102.5</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
       </c>
       <c r="F12">
-        <v>110.5</v>
+        <v>113.19</v>
       </c>
       <c r="G12">
-        <v>0.5</v>
+        <v>0.528</v>
       </c>
       <c r="H12">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="I12">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2841,28 +2961,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D13">
-        <v>126.04</v>
+        <v>116.63</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>111.78</v>
+        <v>110.62</v>
       </c>
       <c r="G13">
-        <v>0.462</v>
+        <v>0.472</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="I13">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2877,350 +2997,350 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D2">
-        <v>128.05</v>
+        <v>137.4666666666667</v>
       </c>
       <c r="E2">
-        <v>256.1</v>
+        <v>412.4</v>
       </c>
       <c r="F2">
-        <v>87.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>140.59</v>
+        <v>124.2266666666667</v>
       </c>
       <c r="E3">
-        <v>281.18</v>
+        <v>372.68</v>
       </c>
       <c r="F3">
-        <v>82.8</v>
+        <v>72.8</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>126.04</v>
+        <v>118.6666666666667</v>
       </c>
       <c r="E4">
-        <v>252.08</v>
+        <v>356</v>
       </c>
       <c r="F4">
-        <v>58.2</v>
+        <v>51.9</v>
       </c>
       <c r="G4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>113.16</v>
+        <v>119.2466666666667</v>
       </c>
       <c r="E5">
-        <v>226.32</v>
+        <v>357.74</v>
       </c>
       <c r="F5">
-        <v>47.4</v>
+        <v>48.4</v>
       </c>
       <c r="G5">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D6">
-        <v>114.19</v>
+        <v>116.6266666666667</v>
       </c>
       <c r="E6">
-        <v>228.38</v>
+        <v>349.88</v>
       </c>
       <c r="F6">
-        <v>30.5</v>
+        <v>46.1</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D7">
-        <v>110.48</v>
+        <v>111.8666666666667</v>
       </c>
       <c r="E7">
-        <v>220.96</v>
+        <v>335.6</v>
       </c>
       <c r="F7">
-        <v>22.2</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8">
-        <v>111.82</v>
+        <v>116.2733333333333</v>
       </c>
       <c r="E8">
-        <v>223.64</v>
+        <v>348.82</v>
       </c>
       <c r="F8">
-        <v>18.8</v>
+        <v>20.7</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="H8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D9">
-        <v>112.23</v>
+        <v>110.5</v>
       </c>
       <c r="E9">
-        <v>224.46</v>
+        <v>331.5</v>
       </c>
       <c r="F9">
         <v>18.6</v>
       </c>
       <c r="G9">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="H9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D10">
-        <v>109.55</v>
+        <v>113.6466666666667</v>
       </c>
       <c r="E10">
-        <v>219.1</v>
+        <v>340.9400000000001</v>
       </c>
       <c r="F10">
-        <v>17.1</v>
+        <v>13.3</v>
       </c>
       <c r="G10">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D11">
-        <v>109.02</v>
+        <v>93.75333333333333</v>
       </c>
       <c r="E11">
-        <v>218.04</v>
+        <v>281.26</v>
       </c>
       <c r="F11">
-        <v>15.6</v>
+        <v>0.6</v>
       </c>
       <c r="G11">
-        <v>2.6</v>
+        <v>11.1</v>
       </c>
       <c r="H11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D12">
-        <v>105.43</v>
+        <v>102.5</v>
       </c>
       <c r="E12">
-        <v>210.86</v>
+        <v>307.5</v>
       </c>
       <c r="F12">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="G12">
-        <v>16.6</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3228,28 +3348,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>84.22999999999999</v>
+        <v>85.51333333333332</v>
       </c>
       <c r="E13">
-        <v>168.46</v>
+        <v>256.54</v>
       </c>
       <c r="F13">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>69.89999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="H13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -3264,19 +3384,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3287,16 +3407,16 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3304,19 +3424,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3324,10 +3444,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -3336,7 +3456,7 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3344,19 +3464,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3364,19 +3484,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3384,19 +3504,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3407,13 +3527,13 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D8">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
         <v>94</v>
@@ -3424,19 +3544,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
         <v>47</v>
       </c>
       <c r="D9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3444,19 +3564,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3464,19 +3584,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D11">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3487,13 +3607,13 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D12">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
         <v>96</v>
@@ -3507,10 +3627,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D13">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
@@ -3526,10 +3646,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
         <v>98</v>
       </c>
@@ -3537,10 +3657,13 @@
         <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>100</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3550,81 +3673,99 @@
       <c r="C2">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>-1</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="B4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B5">
+        <v>-1</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6">
         <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>-1</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>-6</v>
+      </c>
+      <c r="C7">
+        <v>-2</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>-2</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -3634,53 +3775,65 @@
       <c r="C8">
         <v>-2</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B9">
+        <v>-2</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>-3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>-7</v>
+      </c>
+      <c r="D10">
+        <v>-4</v>
+      </c>
+      <c r="E10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>-6</v>
       </c>
-      <c r="C9">
-        <v>-2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>-6</v>
-      </c>
-      <c r="D10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>-7</v>
-      </c>
-      <c r="D11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="D11">
+        <v>-5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -3690,11 +3843,14 @@
       <c r="C12">
         <v>-7</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12">
+        <v>-9</v>
+      </c>
+      <c r="E12" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
@@ -3704,7 +3860,10 @@
       <c r="C13">
         <v>-8</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13">
+        <v>-15</v>
+      </c>
+      <c r="E13" t="s">
         <v>97</v>
       </c>
     </row>

--- a/data/leagues/The Girl's Room 💞🏈 2026.xlsx
+++ b/data/leagues/The Girl's Room 💞🏈 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="112">
   <si>
     <t>Tush Push Director 🍑</t>
   </si>
@@ -61,16 +61,19 @@
     <t xml:space="preserve">michelle’s boy toys </t>
   </si>
   <si>
-    <t>2-1-0</t>
-  </si>
-  <si>
-    <t>1-2-0</t>
-  </si>
-  <si>
-    <t>3-0-0</t>
-  </si>
-  <si>
-    <t>0-3-0</t>
+    <t>3-1-0</t>
+  </si>
+  <si>
+    <t>2-2-0</t>
+  </si>
+  <si>
+    <t>1-3-0</t>
+  </si>
+  <si>
+    <t>0-4-0</t>
+  </si>
+  <si>
+    <t>4-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -142,6 +145,9 @@
     <t>Week_4</t>
   </si>
   <si>
+    <t>Week_5</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -163,42 +169,42 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Michelle Nocitra</t>
+  </si>
+  <si>
+    <t>Hannah Miller</t>
+  </si>
+  <si>
     <t>Kiana McIntosh</t>
   </si>
   <si>
+    <t>Malini Ragoopath</t>
+  </si>
+  <si>
+    <t>nidhi shah</t>
+  </si>
+  <si>
+    <t>Bianca Magsino</t>
+  </si>
+  <si>
     <t>Emily Carey</t>
   </si>
   <si>
+    <t>Sumita Gangwani</t>
+  </si>
+  <si>
+    <t>Allie Kardon</t>
+  </si>
+  <si>
     <t>Amanda Pasquale</t>
   </si>
   <si>
-    <t>Michelle Nocitra</t>
-  </si>
-  <si>
-    <t>Sumita Gangwani</t>
-  </si>
-  <si>
-    <t>Hannah Miller</t>
-  </si>
-  <si>
-    <t>Allie Kardon</t>
-  </si>
-  <si>
-    <t>Malini Ragoopath</t>
+    <t>Hillary Dale</t>
   </si>
   <si>
     <t>Grace Stockbower</t>
   </si>
   <si>
-    <t>nidhi shah</t>
-  </si>
-  <si>
-    <t>Hillary Dale</t>
-  </si>
-  <si>
-    <t>Bianca Magsino</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -223,52 +229,52 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>11.4-3.5-0.1</t>
-  </si>
-  <si>
-    <t>9.6-5.3-0.1</t>
-  </si>
-  <si>
-    <t>8.8-6.1-0.1</t>
-  </si>
-  <si>
-    <t>8.7-6.2-0.2</t>
-  </si>
-  <si>
-    <t>8.7-6.1-0.1</t>
-  </si>
-  <si>
-    <t>8.2-6.6-0.1</t>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>9.9-5.0-0.1</t>
+  </si>
+  <si>
+    <t>9.8-5.1-0.1</t>
+  </si>
+  <si>
+    <t>9.2-5.7-0.1</t>
+  </si>
+  <si>
+    <t>9.1-5.8-0.1</t>
+  </si>
+  <si>
+    <t>8.5-6.4-0.1</t>
+  </si>
+  <si>
+    <t>8.0-6.9-0.1</t>
+  </si>
+  <si>
+    <t>7.8-7.1-0.2</t>
   </si>
   <si>
     <t>7.6-7.3-0.1</t>
   </si>
   <si>
-    <t>7.7-7.2-0.2</t>
-  </si>
-  <si>
-    <t>7.0-7.8-0.2</t>
-  </si>
-  <si>
-    <t>4.4-10.5-0.1</t>
+    <t>6.4-8.4-0.1</t>
+  </si>
+  <si>
+    <t>6.4-8.5-0.1</t>
   </si>
   <si>
     <t>5.2-9.7-0.1</t>
   </si>
   <si>
-    <t>2.0-12.9-0.1</t>
-  </si>
-  <si>
-    <t>12-3</t>
+    <t>1.5-13.4-0.1</t>
   </si>
   <si>
     <t>10-5</t>
@@ -280,13 +286,13 @@
     <t>8-7</t>
   </si>
   <si>
-    <t>7-8</t>
+    <t>6-9</t>
   </si>
   <si>
     <t>5-10</t>
   </si>
   <si>
-    <t>2-13</t>
+    <t>1-14</t>
   </si>
   <si>
     <t>Owners</t>
@@ -298,27 +304,30 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
     <t>↑1</t>
   </si>
   <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↓5</t>
-  </si>
-  <si>
-    <t>↓2</t>
+    <t>↑5</t>
   </si>
   <si>
     <t>↓7</t>
   </si>
   <si>
+    <t>↑7</t>
+  </si>
+  <si>
+    <t>↓9</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -326,6 +335,9 @@
   </si>
   <si>
     <t>Week 3</t>
+  </si>
+  <si>
+    <t>Week 4</t>
   </si>
   <si>
     <t>Week</t>
@@ -753,19 +765,19 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>
@@ -780,10 +792,10 @@
         <v>12</v>
       </c>
       <c r="L2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -806,16 +818,16 @@
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K3" t="s">
         <v>13</v>
@@ -832,40 +844,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" t="s">
         <v>14</v>
       </c>
-      <c r="I4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" t="s">
-        <v>13</v>
-      </c>
       <c r="K4" t="s">
         <v>12</v>
       </c>
       <c r="L4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -873,40 +885,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
         <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
         <v>12</v>
       </c>
       <c r="K5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -935,10 +947,10 @@
         <v>12</v>
       </c>
       <c r="I6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" t="s">
         <v>14</v>
-      </c>
-      <c r="J6" t="s">
-        <v>15</v>
       </c>
       <c r="K6" t="s">
         <v>13</v>
@@ -955,22 +967,22 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
         <v>13</v>
@@ -979,16 +991,16 @@
         <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K7" t="s">
         <v>12</v>
       </c>
       <c r="L7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -996,40 +1008,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1037,19 +1049,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
         <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
@@ -1061,16 +1073,16 @@
         <v>12</v>
       </c>
       <c r="J9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1084,7 +1096,7 @@
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
@@ -1108,7 +1120,7 @@
         <v>12</v>
       </c>
       <c r="L10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M10" t="s">
         <v>15</v>
@@ -1122,7 +1134,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1143,13 +1155,13 @@
         <v>12</v>
       </c>
       <c r="J11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K11" t="s">
         <v>12</v>
       </c>
       <c r="L11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M11" t="s">
         <v>13</v>
@@ -1163,10 +1175,10 @@
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
@@ -1190,10 +1202,10 @@
         <v>12</v>
       </c>
       <c r="L12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1204,7 +1216,7 @@
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -1213,13 +1225,13 @@
         <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
@@ -1228,10 +1240,10 @@
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M13" t="s">
         <v>15</v>
@@ -1244,30 +1256,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1301,25 +1313,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>-8</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1327,25 +1339,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1353,25 +1365,103 @@
         <v>3</v>
       </c>
       <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
         <v>7</v>
       </c>
-      <c r="E5">
+      <c r="E7">
         <v>5</v>
       </c>
-      <c r="F5">
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="G5">
+      <c r="G7">
         <v>4</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H7" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1386,13 +1476,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1400,13 +1490,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1414,13 +1504,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1431,7 +1521,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1445,7 +1535,7 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>1.333333333333333</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -1459,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>1.583333333333333</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -1470,13 +1560,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>1.666666666666667</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1484,13 +1574,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>1.75</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1498,13 +1588,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>1.833333333333333</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1512,10 +1602,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>1.833333333333333</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1526,10 +1616,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>1.916666666666667</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
@@ -1540,13 +1630,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1554,13 +1644,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>2.083333333333333</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1575,16 +1665,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1592,13 +1682,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>2.166666666666667</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="D2">
-        <v>0.1666666666666665</v>
+        <v>-0.4166666666666665</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -1609,13 +1699,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-0.4166666666666665</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1626,16 +1716,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>1.833333333333333</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="D4">
-        <v>-0.1666666666666667</v>
+        <v>0.5833333333333335</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1643,13 +1733,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>1.833333333333333</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="D5">
-        <v>-0.1666666666666667</v>
+        <v>-0.5833333333333335</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -1660,16 +1750,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>1.583333333333333</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="D6">
-        <v>-0.4166666666666667</v>
+        <v>0.1666666666666665</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1677,13 +1767,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>1.583333333333333</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="D7">
-        <v>-0.4166666666666667</v>
+        <v>-0.9166666666666665</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -1694,16 +1784,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>1.583333333333333</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>-0.4166666666666667</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1711,13 +1801,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>1.583333333333333</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="D9">
-        <v>0.5833333333333333</v>
+        <v>-0.08333333333333326</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -1728,16 +1818,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>1.25</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="D10">
-        <v>0.25</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1745,13 +1835,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>1.166666666666667</v>
+        <v>1.75</v>
       </c>
       <c r="D11">
-        <v>0.1666666666666667</v>
+        <v>-0.25</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -1762,16 +1852,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>0.8333333333333334</v>
+        <v>1.5</v>
       </c>
       <c r="D12">
-        <v>-0.1666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1803,46 +1893,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1850,72 +1940,72 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>69.8</v>
+        <v>34.9</v>
       </c>
       <c r="C2">
-        <v>15.1</v>
+        <v>22.3</v>
       </c>
       <c r="D2">
-        <v>7.3</v>
+        <v>14.3</v>
       </c>
       <c r="E2">
-        <v>3.9</v>
+        <v>10.2</v>
       </c>
       <c r="F2">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="H2">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="I2">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J2">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>96.09999999999999</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3">
-        <v>11.8</v>
+        <v>27.2</v>
       </c>
       <c r="C3">
-        <v>26.6</v>
+        <v>20.2</v>
       </c>
       <c r="D3">
-        <v>20.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3">
-        <v>14.1</v>
+        <v>12.1</v>
       </c>
       <c r="F3">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="H3">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="I3">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J3">
         <v>1.9</v>
@@ -1924,321 +2014,321 @@
         <v>0.8</v>
       </c>
       <c r="L3">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
-        <v>72.8</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B4">
-        <v>4.8</v>
+        <v>13.8</v>
       </c>
       <c r="C4">
-        <v>15.2</v>
+        <v>13.9</v>
       </c>
       <c r="D4">
-        <v>17.7</v>
+        <v>14.3</v>
       </c>
       <c r="E4">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="F4">
-        <v>13.9</v>
+        <v>13.3</v>
       </c>
       <c r="G4">
-        <v>12.7</v>
+        <v>10.5</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="J4">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K4">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="L4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>51.9</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="C5">
-        <v>12.2</v>
+        <v>16.1</v>
       </c>
       <c r="D5">
-        <v>16.3</v>
+        <v>14.8</v>
       </c>
       <c r="E5">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>13.1</v>
+        <v>13.6</v>
       </c>
       <c r="G5">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
-        <v>8.9</v>
+        <v>6.6</v>
       </c>
       <c r="J5">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="K5">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="L5">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>48.4</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D6">
-        <v>15.9</v>
+        <v>10.3</v>
       </c>
       <c r="E6">
-        <v>14.1</v>
+        <v>15.1</v>
       </c>
       <c r="F6">
-        <v>13.9</v>
+        <v>13.3</v>
       </c>
       <c r="G6">
+        <v>13.7</v>
+      </c>
+      <c r="H6">
+        <v>12.5</v>
+      </c>
+      <c r="I6">
         <v>11.3</v>
       </c>
-      <c r="H6">
-        <v>10.6</v>
-      </c>
-      <c r="I6">
-        <v>8.699999999999999</v>
-      </c>
       <c r="J6">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="L6">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>46.1</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="C7">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="D7">
-        <v>7.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E7">
-        <v>13.6</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>14.8</v>
+        <v>12.3</v>
       </c>
       <c r="G7">
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="H7">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="I7">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="L7">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="M7">
         <v>0.1</v>
       </c>
       <c r="N7">
-        <v>31</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="C8">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="D8">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="E8">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>13.6</v>
       </c>
       <c r="G8">
-        <v>14.2</v>
+        <v>13.1</v>
       </c>
       <c r="H8">
-        <v>15.4</v>
+        <v>13.5</v>
       </c>
       <c r="I8">
-        <v>14.9</v>
+        <v>14.3</v>
       </c>
       <c r="J8">
-        <v>15.2</v>
+        <v>9.5</v>
       </c>
       <c r="K8">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L8">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="M8">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>20.7</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>2.8</v>
+      </c>
+      <c r="C9">
         <v>4</v>
       </c>
-      <c r="B9">
-        <v>1.2</v>
-      </c>
-      <c r="C9">
-        <v>3.6</v>
-      </c>
       <c r="D9">
-        <v>5.3</v>
+        <v>8.5</v>
       </c>
       <c r="E9">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F9">
-        <v>11.1</v>
+        <v>10.1</v>
       </c>
       <c r="G9">
-        <v>13.5</v>
+        <v>12.6</v>
       </c>
       <c r="H9">
-        <v>16.8</v>
+        <v>13</v>
       </c>
       <c r="I9">
-        <v>17.2</v>
+        <v>13.3</v>
       </c>
       <c r="J9">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="K9">
-        <v>7</v>
+        <v>8.9</v>
       </c>
       <c r="L9">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="M9">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>18.6</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B10">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="D10">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="E10">
-        <v>6.9</v>
+        <v>3.6</v>
       </c>
       <c r="F10">
-        <v>7.9</v>
+        <v>6.3</v>
       </c>
       <c r="G10">
-        <v>11.7</v>
+        <v>7.1</v>
       </c>
       <c r="H10">
-        <v>14.5</v>
+        <v>10.9</v>
       </c>
       <c r="I10">
-        <v>17.2</v>
+        <v>16.2</v>
       </c>
       <c r="J10">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="K10">
-        <v>11.7</v>
+        <v>18.2</v>
       </c>
       <c r="L10">
-        <v>4.3</v>
+        <v>14.1</v>
       </c>
       <c r="M10">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="N10">
-        <v>13.3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2246,43 +2336,43 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C11">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E11">
+        <v>2.6</v>
+      </c>
+      <c r="F11">
+        <v>2.9</v>
+      </c>
+      <c r="G11">
+        <v>6.8</v>
+      </c>
+      <c r="H11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I11">
+        <v>11.3</v>
+      </c>
+      <c r="J11">
+        <v>15.6</v>
+      </c>
+      <c r="K11">
+        <v>26</v>
+      </c>
+      <c r="L11">
+        <v>22.1</v>
+      </c>
+      <c r="M11">
         <v>0.4</v>
       </c>
-      <c r="F11">
-        <v>0.3</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>1.7</v>
-      </c>
-      <c r="I11">
-        <v>4.3</v>
-      </c>
-      <c r="J11">
-        <v>6.3</v>
-      </c>
-      <c r="K11">
-        <v>22.3</v>
-      </c>
-      <c r="L11">
-        <v>52.4</v>
-      </c>
-      <c r="M11">
-        <v>11.1</v>
-      </c>
       <c r="N11">
-        <v>0.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2290,43 +2380,43 @@
         <v>5</v>
       </c>
       <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0.3</v>
+      </c>
+      <c r="D12">
         <v>0.1</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
       <c r="E12">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F12">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="G12">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="H12">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="I12">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="J12">
-        <v>16</v>
+        <v>13.7</v>
       </c>
       <c r="K12">
-        <v>41.9</v>
+        <v>23.9</v>
       </c>
       <c r="L12">
-        <v>23.9</v>
+        <v>46.7</v>
       </c>
       <c r="M12">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="N12">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2358,16 +2448,16 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="L13">
-        <v>12.6</v>
+        <v>2.8</v>
       </c>
       <c r="M13">
-        <v>85.2</v>
+        <v>97</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2380,211 +2470,247 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>39</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="C2">
-        <v>97.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="D2">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="E2">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>84.7</v>
+      </c>
+      <c r="F2">
+        <v>84.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>0.1</v>
+      </c>
+      <c r="C3">
+        <v>21.5</v>
+      </c>
+      <c r="D3">
+        <v>23.7</v>
+      </c>
+      <c r="E3">
+        <v>77.60000000000001</v>
+      </c>
+      <c r="F3">
+        <v>74.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>92.60000000000001</v>
+      </c>
+      <c r="C4">
+        <v>93.30000000000001</v>
+      </c>
+      <c r="D4">
+        <v>47.7</v>
+      </c>
+      <c r="E4">
+        <v>53.3</v>
+      </c>
+      <c r="F4">
+        <v>56.99999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="C5">
+        <v>45.8</v>
+      </c>
+      <c r="D5">
+        <v>28.8</v>
+      </c>
+      <c r="E5">
+        <v>56.2</v>
+      </c>
+      <c r="F5">
+        <v>52.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>13.4</v>
+      </c>
+      <c r="D6">
+        <v>44.5</v>
+      </c>
+      <c r="E6">
+        <v>38.2</v>
+      </c>
+      <c r="F6">
+        <v>39.90000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>25</v>
+      </c>
+      <c r="C7">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="D7">
+        <v>48</v>
+      </c>
+      <c r="E7">
+        <v>32</v>
+      </c>
+      <c r="F7">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0.5</v>
+      </c>
+      <c r="D8">
+        <v>13.3</v>
+      </c>
+      <c r="E8">
+        <v>23.5</v>
+      </c>
+      <c r="F8">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
-        <v>16.1</v>
-      </c>
-      <c r="C3">
-        <v>12</v>
-      </c>
-      <c r="D3">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="E3">
+      <c r="B9">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>11.8</v>
+      </c>
+      <c r="D9">
         <v>74.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
-        <v>2.5</v>
-      </c>
-      <c r="C4">
-        <v>12.2</v>
-      </c>
-      <c r="D4">
-        <v>47.09999999999999</v>
-      </c>
-      <c r="E4">
-        <v>49.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5">
-        <v>93.30000000000001</v>
-      </c>
-      <c r="C5">
-        <v>93.60000000000001</v>
-      </c>
-      <c r="D5">
-        <v>47.8</v>
-      </c>
-      <c r="E5">
-        <v>49.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>24.9</v>
-      </c>
-      <c r="C6">
-        <v>7.9</v>
-      </c>
-      <c r="D6">
-        <v>46.1</v>
-      </c>
-      <c r="E6">
-        <v>49.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>82.89999999999999</v>
-      </c>
-      <c r="C7">
-        <v>48.9</v>
-      </c>
-      <c r="D7">
-        <v>29.4</v>
-      </c>
-      <c r="E7">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
+      <c r="E9">
+        <v>20.5</v>
+      </c>
+      <c r="F9">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B8">
-        <v>97.89999999999999</v>
-      </c>
-      <c r="C8">
-        <v>78.2</v>
-      </c>
-      <c r="D8">
-        <v>19.5</v>
-      </c>
-      <c r="E8">
-        <v>20.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>22.5</v>
-      </c>
-      <c r="D9">
-        <v>24.1</v>
-      </c>
-      <c r="E9">
-        <v>17.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="B10">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="C10">
-        <v>0.8</v>
+        <v>76.8</v>
       </c>
       <c r="D10">
-        <v>13.9</v>
+        <v>20.7</v>
       </c>
       <c r="E10">
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>8.5</v>
+      </c>
+      <c r="F10">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="C11">
+        <v>14.2</v>
+      </c>
+      <c r="D11">
+        <v>0.1</v>
+      </c>
+      <c r="E11">
+        <v>4.6</v>
+      </c>
+      <c r="F11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>13.9</v>
-      </c>
-      <c r="D11">
+      <c r="B12">
+        <v>0.2</v>
+      </c>
+      <c r="C12">
+        <v>15.8</v>
+      </c>
+      <c r="D12">
+        <v>0.5</v>
+      </c>
+      <c r="E12">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="F12">
         <v>1</v>
       </c>
-      <c r="E11">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12">
-        <v>80.60000000000001</v>
-      </c>
-      <c r="C12">
-        <v>12.4</v>
-      </c>
-      <c r="D12">
-        <v>0.2</v>
-      </c>
-      <c r="E12">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -2598,6 +2724,9 @@
         <v>0</v>
       </c>
       <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
         <v>0</v>
       </c>
     </row>
@@ -2613,28 +2742,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2642,28 +2771,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <v>93.75</v>
+        <v>85.2</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>114.43</v>
+        <v>116.46</v>
       </c>
       <c r="G2">
-        <v>0.528</v>
+        <v>0.545</v>
       </c>
       <c r="H2">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2671,28 +2800,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>110.5</v>
+        <v>114.99</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>111.86</v>
+        <v>113.75</v>
       </c>
       <c r="G3">
-        <v>0.472</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
         <v>0.8</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2700,28 +2829,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>113.65</v>
+        <v>105.3</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
       </c>
       <c r="F4">
-        <v>112.74</v>
+        <v>114.63</v>
       </c>
       <c r="G4">
         <v>0.5</v>
       </c>
       <c r="H4">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2729,28 +2858,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5">
+        <v>114.92</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>113.76</v>
+      </c>
+      <c r="G5">
+        <v>0.477</v>
+      </c>
+      <c r="H5">
+        <v>0.5</v>
+      </c>
+      <c r="I5">
         <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5">
-        <v>85.51000000000001</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5">
-        <v>114.72</v>
-      </c>
-      <c r="G5">
-        <v>0.556</v>
-      </c>
-      <c r="H5">
-        <v>0.3</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2758,28 +2887,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6">
-        <v>119.25</v>
+        <v>117.78</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
       </c>
       <c r="F6">
-        <v>114.04</v>
+        <v>113.5</v>
       </c>
       <c r="G6">
+        <v>0.477</v>
+      </c>
+      <c r="H6">
         <v>0.5</v>
       </c>
-      <c r="H6">
-        <v>0.1</v>
-      </c>
       <c r="I6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2787,28 +2916,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>124.23</v>
+        <v>117.27</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>112.06</v>
+        <v>113.54</v>
       </c>
       <c r="G7">
         <v>0.5</v>
       </c>
       <c r="H7">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2816,28 +2945,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D8">
-        <v>137.47</v>
+        <v>123.66</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
       </c>
       <c r="F8">
-        <v>111.01</v>
+        <v>112.96</v>
       </c>
       <c r="G8">
-        <v>0.5</v>
+        <v>0.477</v>
       </c>
       <c r="H8">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2845,28 +2974,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9">
-        <v>118.67</v>
+        <v>118.4</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9">
-        <v>112.99</v>
+        <v>113.44</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.477</v>
       </c>
       <c r="H9">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2874,28 +3003,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D10">
-        <v>116.27</v>
+        <v>132.06</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
       </c>
       <c r="F10">
-        <v>112.3</v>
+        <v>112.2</v>
       </c>
       <c r="G10">
         <v>0.5</v>
       </c>
       <c r="H10">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2903,28 +3032,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D11">
-        <v>111.87</v>
+        <v>116.47</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>110.33</v>
+        <v>113.62</v>
       </c>
       <c r="G11">
-        <v>0.444</v>
+        <v>0.5</v>
       </c>
       <c r="H11">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2935,25 +3064,25 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D12">
-        <v>102.5</v>
+        <v>105.77</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12">
-        <v>113.19</v>
+        <v>114.59</v>
       </c>
       <c r="G12">
-        <v>0.528</v>
+        <v>0.523</v>
       </c>
       <c r="H12">
         <v>-0.8</v>
       </c>
       <c r="I12">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2961,28 +3090,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D13">
-        <v>116.63</v>
+        <v>114.44</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13">
-        <v>110.62</v>
+        <v>113.8</v>
       </c>
       <c r="G13">
-        <v>0.472</v>
+        <v>0.523</v>
       </c>
       <c r="H13">
         <v>-0.9</v>
       </c>
       <c r="I13">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2997,31 +3126,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3029,260 +3158,260 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D2">
-        <v>137.4666666666667</v>
+        <v>132.055</v>
       </c>
       <c r="E2">
-        <v>412.4</v>
+        <v>528.22</v>
       </c>
       <c r="F2">
-        <v>96.09999999999999</v>
+        <v>81.69999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D3">
-        <v>124.2266666666667</v>
+        <v>123.655</v>
       </c>
       <c r="E3">
-        <v>372.68</v>
+        <v>494.62</v>
       </c>
       <c r="F3">
-        <v>72.8</v>
+        <v>76.2</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D4">
-        <v>118.6666666666667</v>
+        <v>118.4</v>
       </c>
       <c r="E4">
-        <v>356</v>
+        <v>473.6</v>
       </c>
       <c r="F4">
-        <v>51.9</v>
+        <v>56.39999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D5">
-        <v>119.2466666666667</v>
+        <v>117.78</v>
       </c>
       <c r="E5">
-        <v>357.74</v>
+        <v>471.12</v>
       </c>
       <c r="F5">
-        <v>48.4</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C6">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D6">
-        <v>116.6266666666667</v>
+        <v>114.92</v>
       </c>
       <c r="E6">
-        <v>349.88</v>
+        <v>459.68</v>
       </c>
       <c r="F6">
-        <v>46.1</v>
+        <v>38.1</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>111.8666666666667</v>
+        <v>117.27</v>
       </c>
       <c r="E7">
-        <v>335.6</v>
+        <v>469.08</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="G7">
         <v>0.1</v>
       </c>
       <c r="H7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>116.2733333333333</v>
+        <v>116.465</v>
       </c>
       <c r="E8">
-        <v>348.82</v>
+        <v>465.8600000000001</v>
       </c>
       <c r="F8">
-        <v>20.7</v>
+        <v>24.5</v>
       </c>
       <c r="G8">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C9">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>110.5</v>
+        <v>114.99</v>
       </c>
       <c r="E9">
-        <v>331.5</v>
+        <v>459.96</v>
       </c>
       <c r="F9">
-        <v>18.6</v>
+        <v>23.5</v>
       </c>
       <c r="G9">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C10">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D10">
-        <v>113.6466666666667</v>
+        <v>114.445</v>
       </c>
       <c r="E10">
-        <v>340.9400000000001</v>
+        <v>457.78</v>
       </c>
       <c r="F10">
-        <v>13.3</v>
+        <v>7.6</v>
       </c>
       <c r="G10">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3290,28 +3419,28 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
-        <v>93.75333333333333</v>
+        <v>105.3</v>
       </c>
       <c r="E11">
-        <v>281.26</v>
+        <v>421.2</v>
       </c>
       <c r="F11">
-        <v>0.6</v>
+        <v>5.7</v>
       </c>
       <c r="G11">
-        <v>11.1</v>
+        <v>0.4</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3319,28 +3448,28 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C12">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D12">
-        <v>102.5</v>
+        <v>105.765</v>
       </c>
       <c r="E12">
-        <v>307.5</v>
+        <v>423.06</v>
       </c>
       <c r="F12">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="G12">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="H12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3348,28 +3477,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>85.51333333333332</v>
+        <v>85.19999999999999</v>
       </c>
       <c r="E13">
-        <v>256.54</v>
+        <v>340.8</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>85.2</v>
+        <v>97</v>
       </c>
       <c r="H13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -3384,19 +3513,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3407,16 +3536,16 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3424,19 +3553,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3444,19 +3573,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3464,10 +3593,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -3476,7 +3605,7 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3484,19 +3613,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D6">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3504,19 +3633,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3524,19 +3653,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3544,19 +3673,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3564,19 +3693,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D10">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3584,19 +3713,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D11">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3604,7 +3733,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C12" t="s">
         <v>49</v>
@@ -3613,10 +3742,10 @@
         <v>-9</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3624,19 +3753,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -3646,24 +3775,27 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>104</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3676,195 +3808,231 @@
       <c r="D2">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>-1</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>4</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>7</v>
       </c>
-      <c r="E3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
+      <c r="E5">
         <v>6</v>
       </c>
-      <c r="D4">
+      <c r="F5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>-1</v>
+      </c>
+      <c r="C6">
         <v>6</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>-1</v>
-      </c>
-      <c r="C5">
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>-2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>-3</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>-7</v>
+      </c>
+      <c r="D8">
+        <v>-4</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>-6</v>
+      </c>
+      <c r="C9">
+        <v>-2</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>-6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>-6</v>
+      </c>
+      <c r="D10">
+        <v>-5</v>
+      </c>
+      <c r="E10">
+        <v>-6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>-8</v>
+      </c>
+      <c r="D11">
+        <v>-15</v>
+      </c>
+      <c r="E11">
+        <v>-8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5">
+      <c r="B12">
         <v>6</v>
       </c>
-      <c r="E5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>-6</v>
-      </c>
-      <c r="C7">
+      <c r="C12">
         <v>-2</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>-2</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9">
-        <v>-2</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>-3</v>
-      </c>
-      <c r="E9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>-9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>-8</v>
+      </c>
+      <c r="C13">
         <v>-7</v>
       </c>
-      <c r="D10">
-        <v>-4</v>
-      </c>
-      <c r="E10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>-6</v>
-      </c>
-      <c r="D11">
-        <v>-5</v>
-      </c>
-      <c r="E11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>-8</v>
-      </c>
-      <c r="C12">
-        <v>-7</v>
-      </c>
-      <c r="D12">
+      <c r="D13">
         <v>-9</v>
       </c>
-      <c r="E12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13">
-        <v>-8</v>
-      </c>
-      <c r="D13">
-        <v>-15</v>
-      </c>
-      <c r="E13" t="s">
-        <v>97</v>
+      <c r="E13">
+        <v>-12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/The Girl's Room 💞🏈 2026.xlsx
+++ b/data/leagues/The Girl's Room 💞🏈 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="116">
   <si>
     <t>Tush Push Director 🍑</t>
   </si>
@@ -61,19 +61,22 @@
     <t xml:space="preserve">michelle’s boy toys </t>
   </si>
   <si>
-    <t>3-1-0</t>
-  </si>
-  <si>
-    <t>2-2-0</t>
-  </si>
-  <si>
-    <t>1-3-0</t>
-  </si>
-  <si>
-    <t>0-4-0</t>
-  </si>
-  <si>
-    <t>4-0-0</t>
+    <t>3-2-0</t>
+  </si>
+  <si>
+    <t>2-3-0</t>
+  </si>
+  <si>
+    <t>4-1-0</t>
+  </si>
+  <si>
+    <t>0-5-0</t>
+  </si>
+  <si>
+    <t>5-0-0</t>
+  </si>
+  <si>
+    <t>1-4-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -148,6 +151,9 @@
     <t>Week_5</t>
   </si>
   <si>
+    <t>Week_6</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -169,42 +175,42 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Sumita Gangwani</t>
+  </si>
+  <si>
+    <t>Kiana McIntosh</t>
+  </si>
+  <si>
+    <t>Amanda Pasquale</t>
+  </si>
+  <si>
+    <t>nidhi shah</t>
+  </si>
+  <si>
+    <t>Grace Stockbower</t>
+  </si>
+  <si>
     <t>Michelle Nocitra</t>
   </si>
   <si>
+    <t>Allie Kardon</t>
+  </si>
+  <si>
+    <t>Malini Ragoopath</t>
+  </si>
+  <si>
+    <t>Hillary Dale</t>
+  </si>
+  <si>
+    <t>Bianca Magsino</t>
+  </si>
+  <si>
+    <t>Emily Carey</t>
+  </si>
+  <si>
     <t>Hannah Miller</t>
   </si>
   <si>
-    <t>Kiana McIntosh</t>
-  </si>
-  <si>
-    <t>Malini Ragoopath</t>
-  </si>
-  <si>
-    <t>nidhi shah</t>
-  </si>
-  <si>
-    <t>Bianca Magsino</t>
-  </si>
-  <si>
-    <t>Emily Carey</t>
-  </si>
-  <si>
-    <t>Sumita Gangwani</t>
-  </si>
-  <si>
-    <t>Allie Kardon</t>
-  </si>
-  <si>
-    <t>Amanda Pasquale</t>
-  </si>
-  <si>
-    <t>Hillary Dale</t>
-  </si>
-  <si>
-    <t>Grace Stockbower</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -229,54 +235,57 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>9.9-5.0-0.1</t>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>0-5</t>
+  </si>
+  <si>
+    <t>10.2-4.7-0.1</t>
   </si>
   <si>
     <t>9.8-5.1-0.1</t>
   </si>
   <si>
-    <t>9.2-5.7-0.1</t>
-  </si>
-  <si>
     <t>9.1-5.8-0.1</t>
   </si>
   <si>
-    <t>8.5-6.4-0.1</t>
-  </si>
-  <si>
-    <t>8.0-6.9-0.1</t>
-  </si>
-  <si>
-    <t>7.8-7.1-0.2</t>
-  </si>
-  <si>
-    <t>7.6-7.3-0.1</t>
-  </si>
-  <si>
-    <t>6.4-8.4-0.1</t>
-  </si>
-  <si>
-    <t>6.4-8.5-0.1</t>
-  </si>
-  <si>
-    <t>5.2-9.7-0.1</t>
+    <t>8.9-6.0-0.1</t>
+  </si>
+  <si>
+    <t>8.4-6.4-0.1</t>
+  </si>
+  <si>
+    <t>8.6-6.3-0.1</t>
+  </si>
+  <si>
+    <t>7.7-7.2-0.1</t>
+  </si>
+  <si>
+    <t>6.9-8.0-0.1</t>
+  </si>
+  <si>
+    <t>6.1-8.7-0.1</t>
+  </si>
+  <si>
+    <t>4.4-10.5-0.1</t>
   </si>
   <si>
     <t>1.5-13.4-0.1</t>
   </si>
   <si>
+    <t>11-4</t>
+  </si>
+  <si>
     <t>10-5</t>
   </si>
   <si>
@@ -289,7 +298,7 @@
     <t>6-9</t>
   </si>
   <si>
-    <t>5-10</t>
+    <t>4-11</t>
   </si>
   <si>
     <t>1-14</t>
@@ -304,28 +313,28 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↑5</t>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↓2</t>
   </si>
   <si>
     <t>↓7</t>
   </si>
   <si>
-    <t>↑7</t>
-  </si>
-  <si>
-    <t>↓9</t>
-  </si>
-  <si>
-    <t>↓3</t>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↑10</t>
+  </si>
+  <si>
+    <t>↓5</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -338,6 +347,9 @@
   </si>
   <si>
     <t>Week 4</t>
+  </si>
+  <si>
+    <t>Week 5</t>
   </si>
   <si>
     <t>Week</t>
@@ -765,16 +777,16 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -803,13 +815,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -818,22 +830,22 @@
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M3" t="s">
         <v>13</v>
@@ -844,40 +856,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" t="s">
         <v>14</v>
       </c>
-      <c r="K4" t="s">
-        <v>12</v>
-      </c>
       <c r="L4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -885,22 +897,22 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
         <v>12</v>
@@ -909,13 +921,13 @@
         <v>16</v>
       </c>
       <c r="J5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K5" t="s">
         <v>16</v>
       </c>
       <c r="L5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M5" t="s">
         <v>12</v>
@@ -926,22 +938,22 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
         <v>12</v>
@@ -950,13 +962,13 @@
         <v>16</v>
       </c>
       <c r="J6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" t="s">
         <v>14</v>
-      </c>
-      <c r="K6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L6" t="s">
-        <v>12</v>
       </c>
       <c r="M6" t="s">
         <v>13</v>
@@ -970,37 +982,37 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" t="s">
         <v>14</v>
       </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" t="s">
-        <v>12</v>
-      </c>
       <c r="L7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1008,40 +1020,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K8" t="s">
         <v>16</v>
       </c>
       <c r="L8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1049,13 +1061,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -1073,13 +1085,13 @@
         <v>12</v>
       </c>
       <c r="J9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K9" t="s">
         <v>16</v>
       </c>
       <c r="L9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M9" t="s">
         <v>13</v>
@@ -1096,7 +1108,7 @@
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
@@ -1131,13 +1143,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -1155,13 +1167,13 @@
         <v>12</v>
       </c>
       <c r="J11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" t="s">
         <v>14</v>
       </c>
-      <c r="K11" t="s">
-        <v>12</v>
-      </c>
       <c r="L11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M11" t="s">
         <v>13</v>
@@ -1172,22 +1184,22 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
         <v>14</v>
       </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
         <v>12</v>
@@ -1196,13 +1208,13 @@
         <v>12</v>
       </c>
       <c r="J12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M12" t="s">
         <v>13</v>
@@ -1216,7 +1228,7 @@
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -1240,10 +1252,10 @@
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M13" t="s">
         <v>15</v>
@@ -1256,30 +1268,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1313,22 +1325,22 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>-13</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>-8</v>
-      </c>
       <c r="G3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -1339,25 +1351,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="F4">
+        <v>-11</v>
+      </c>
+      <c r="G4">
         <v>10</v>
       </c>
-      <c r="G4">
-        <v>8</v>
-      </c>
       <c r="H4" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1365,25 +1377,25 @@
         <v>3</v>
       </c>
       <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
-      </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
         <v>9</v>
       </c>
-      <c r="G5">
-        <v>7</v>
-      </c>
       <c r="H5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1391,25 +1403,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1417,25 +1429,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
         <v>4</v>
-      </c>
-      <c r="H7" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1446,21 +1458,125 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8">
         <v>2</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>7</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>6</v>
+      </c>
+      <c r="H9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="E8">
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
+      </c>
+      <c r="H10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="F8">
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
         <v>8</v>
       </c>
-      <c r="G8">
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+      <c r="G12">
         <v>2</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H12" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1476,13 +1592,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1493,10 +1609,10 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>0.75</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1507,10 +1623,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1518,13 +1634,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>1.333333333333333</v>
+        <v>1.75</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1532,13 +1648,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>1.583333333333333</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1546,10 +1662,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>2.083333333333333</v>
+        <v>2.5</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -1560,13 +1676,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>2.083333333333333</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1574,13 +1690,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>2.166666666666667</v>
+        <v>2.75</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1588,13 +1704,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>2.416666666666667</v>
+        <v>2.75</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1602,10 +1718,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>2.416666666666667</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1619,7 +1735,7 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>2.583333333333333</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
@@ -1630,13 +1746,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>2.666666666666667</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1647,10 +1763,10 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>2.916666666666667</v>
+        <v>3.75</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1665,16 +1781,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1682,13 +1798,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2.583333333333333</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D2">
-        <v>-0.4166666666666665</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -1702,10 +1818,10 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>2.583333333333333</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D3">
-        <v>-0.4166666666666665</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1716,16 +1832,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>2.583333333333333</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D4">
-        <v>0.5833333333333335</v>
+        <v>-0.08333333333333348</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1736,13 +1852,13 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>2.416666666666667</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="D5">
-        <v>-0.5833333333333335</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1753,13 +1869,13 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>2.166666666666667</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="D6">
-        <v>0.1666666666666665</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1767,16 +1883,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>2.083333333333333</v>
+        <v>2.75</v>
       </c>
       <c r="D7">
-        <v>-0.9166666666666665</v>
+        <v>0.75</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1784,16 +1900,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1801,16 +1917,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>1.916666666666667</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="D9">
-        <v>-0.08333333333333326</v>
+        <v>-0.4166666666666665</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1818,16 +1934,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>1.833333333333333</v>
+        <v>2.25</v>
       </c>
       <c r="D10">
-        <v>0.8333333333333333</v>
+        <v>-0.75</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1835,13 +1951,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -1855,13 +1971,13 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="D12">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1872,10 +1988,10 @@
         <v>11</v>
       </c>
       <c r="C13">
-        <v>0.5833333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="D13">
-        <v>0.5833333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -1893,46 +2009,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1940,43 +2056,43 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>34.9</v>
+        <v>38.4</v>
       </c>
       <c r="C2">
-        <v>22.3</v>
+        <v>23.4</v>
       </c>
       <c r="D2">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="E2">
-        <v>10.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="G2">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="H2">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="I2">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J2">
         <v>0.9</v>
       </c>
       <c r="K2">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>81.7</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1984,87 +2100,87 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>27.2</v>
+        <v>29.2</v>
       </c>
       <c r="C3">
-        <v>20.2</v>
+        <v>21.1</v>
       </c>
       <c r="D3">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E3">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G3">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="I3">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J3">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="K3">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="L3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
-        <v>76.2</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>13.8</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>13.9</v>
+        <v>17</v>
       </c>
       <c r="D4">
-        <v>14.3</v>
+        <v>16.5</v>
       </c>
       <c r="E4">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="F4">
-        <v>13.3</v>
+        <v>12.5</v>
       </c>
       <c r="G4">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H4">
         <v>7.9</v>
       </c>
       <c r="I4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J4">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>56.4</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -2072,307 +2188,307 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>10.5</v>
+        <v>7.7</v>
       </c>
       <c r="C5">
-        <v>16.1</v>
+        <v>10.3</v>
       </c>
       <c r="D5">
-        <v>14.8</v>
+        <v>10.6</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>13.7</v>
       </c>
       <c r="F5">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>13.4</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>13.1</v>
       </c>
       <c r="I5">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="K5">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="L5">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>54.4</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="C6">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="D6">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="E6">
+        <v>14.5</v>
+      </c>
+      <c r="F6">
         <v>15.1</v>
       </c>
-      <c r="F6">
-        <v>13.3</v>
-      </c>
       <c r="G6">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="H6">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="I6">
         <v>11.3</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="K6">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>38.1</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="C7">
-        <v>6.9</v>
+        <v>8.4</v>
       </c>
       <c r="D7">
-        <v>9.800000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>13.6</v>
       </c>
       <c r="F7">
-        <v>12.3</v>
+        <v>15.2</v>
       </c>
       <c r="G7">
-        <v>12.8</v>
+        <v>14.7</v>
       </c>
       <c r="H7">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="I7">
-        <v>12.2</v>
+        <v>10.4</v>
       </c>
       <c r="J7">
-        <v>10.3</v>
+        <v>6.5</v>
       </c>
       <c r="K7">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="L7">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="M7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>30.8</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B8">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="C8">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="D8">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="E8">
+        <v>10.6</v>
+      </c>
+      <c r="F8">
+        <v>11.6</v>
+      </c>
+      <c r="G8">
+        <v>15.3</v>
+      </c>
+      <c r="H8">
+        <v>12.9</v>
+      </c>
+      <c r="I8">
+        <v>15.5</v>
+      </c>
+      <c r="J8">
         <v>9.1</v>
       </c>
-      <c r="F8">
-        <v>13.6</v>
-      </c>
-      <c r="G8">
-        <v>13.1</v>
-      </c>
-      <c r="H8">
-        <v>13.5</v>
-      </c>
-      <c r="I8">
-        <v>14.3</v>
-      </c>
-      <c r="J8">
-        <v>9.5</v>
-      </c>
       <c r="K8">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="L8">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8">
-        <v>24.5</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B9">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="D9">
-        <v>8.5</v>
+        <v>5.9</v>
       </c>
       <c r="E9">
+        <v>6.6</v>
+      </c>
+      <c r="F9">
+        <v>10.4</v>
+      </c>
+      <c r="G9">
+        <v>13.5</v>
+      </c>
+      <c r="H9">
+        <v>16.1</v>
+      </c>
+      <c r="I9">
+        <v>19</v>
+      </c>
+      <c r="J9">
+        <v>14.8</v>
+      </c>
+      <c r="K9">
         <v>8.199999999999999</v>
       </c>
-      <c r="F9">
-        <v>10.1</v>
-      </c>
-      <c r="G9">
-        <v>12.6</v>
-      </c>
-      <c r="H9">
-        <v>13</v>
-      </c>
-      <c r="I9">
-        <v>13.3</v>
-      </c>
-      <c r="J9">
-        <v>13.2</v>
-      </c>
-      <c r="K9">
-        <v>8.9</v>
-      </c>
       <c r="L9">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
-        <v>23.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10">
         <v>0.4</v>
       </c>
       <c r="C10">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="E10">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="F10">
-        <v>6.3</v>
+        <v>4.2</v>
       </c>
       <c r="G10">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="H10">
-        <v>10.9</v>
+        <v>13.3</v>
       </c>
       <c r="I10">
-        <v>16.2</v>
+        <v>12.9</v>
       </c>
       <c r="J10">
-        <v>19.2</v>
+        <v>22.2</v>
       </c>
       <c r="K10">
-        <v>18.2</v>
+        <v>24.4</v>
       </c>
       <c r="L10">
-        <v>14.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M10">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="N10">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B11">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="C11">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="D11">
+        <v>0.8</v>
+      </c>
+      <c r="E11">
         <v>1.5</v>
       </c>
-      <c r="E11">
-        <v>2.6</v>
-      </c>
       <c r="F11">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G11">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="H11">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="I11">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="J11">
-        <v>15.6</v>
+        <v>23.1</v>
       </c>
       <c r="K11">
-        <v>26</v>
+        <v>34.1</v>
       </c>
       <c r="L11">
-        <v>22.1</v>
+        <v>12.2</v>
       </c>
       <c r="M11">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="N11">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2383,40 +2499,40 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0.4</v>
+      </c>
+      <c r="G12">
         <v>0.1</v>
       </c>
-      <c r="E12">
-        <v>0.7</v>
-      </c>
-      <c r="F12">
-        <v>0.6</v>
-      </c>
-      <c r="G12">
-        <v>2.1</v>
-      </c>
       <c r="H12">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="I12">
-        <v>6.3</v>
+        <v>2.9</v>
       </c>
       <c r="J12">
-        <v>13.7</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>23.9</v>
+        <v>15.2</v>
       </c>
       <c r="L12">
-        <v>46.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="M12">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="N12">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2451,13 +2567,13 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="L13">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="M13">
-        <v>97</v>
+        <v>95.7</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2470,247 +2586,283 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>41</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="C2">
-        <v>98.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D2">
-        <v>98.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="E2">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="F2">
-        <v>84.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>85.7</v>
+      </c>
+      <c r="G2">
+        <v>87.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>21.5</v>
+        <v>23.7</v>
       </c>
       <c r="D3">
-        <v>23.7</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>77.60000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F3">
+        <v>79.80000000000001</v>
+      </c>
+      <c r="G3">
+        <v>80.30000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>16.4</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
         <v>74.2</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4">
-        <v>92.60000000000001</v>
-      </c>
-      <c r="C4">
-        <v>93.30000000000001</v>
-      </c>
-      <c r="D4">
-        <v>47.7</v>
-      </c>
       <c r="E4">
-        <v>53.3</v>
+        <v>22.1</v>
       </c>
       <c r="F4">
-        <v>56.99999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>59.3</v>
+      </c>
+      <c r="G4">
+        <v>64.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B5">
-        <v>81.59999999999999</v>
+        <v>82.39999999999999</v>
       </c>
       <c r="C5">
-        <v>45.8</v>
+        <v>45.4</v>
       </c>
       <c r="D5">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="E5">
-        <v>56.2</v>
+        <v>58.7</v>
       </c>
       <c r="F5">
-        <v>52.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>39.90000000000001</v>
+      </c>
+      <c r="G5">
+        <v>39.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>23.8</v>
+      </c>
+      <c r="C6">
+        <v>8.9</v>
+      </c>
+      <c r="D6">
+        <v>47.59999999999999</v>
+      </c>
+      <c r="E6">
+        <v>29.7</v>
+      </c>
+      <c r="F6">
+        <v>42.6</v>
+      </c>
+      <c r="G6">
+        <v>38.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
+      <c r="B7">
+        <v>3.1</v>
+      </c>
+      <c r="C7">
+        <v>14.5</v>
+      </c>
+      <c r="D7">
+        <v>46.40000000000001</v>
+      </c>
+      <c r="E7">
+        <v>37</v>
+      </c>
+      <c r="F7">
+        <v>33.8</v>
+      </c>
+      <c r="G7">
+        <v>37.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6">
-        <v>13.4</v>
-      </c>
-      <c r="D6">
-        <v>44.5</v>
-      </c>
-      <c r="E6">
-        <v>38.2</v>
-      </c>
-      <c r="F6">
-        <v>39.90000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>25</v>
-      </c>
-      <c r="C7">
-        <v>8.200000000000001</v>
-      </c>
-      <c r="D7">
-        <v>48</v>
-      </c>
-      <c r="E7">
-        <v>32</v>
-      </c>
-      <c r="F7">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
+      <c r="B8">
+        <v>98.3</v>
+      </c>
+      <c r="C8">
+        <v>76.2</v>
+      </c>
+      <c r="D8">
+        <v>21.7</v>
+      </c>
+      <c r="E8">
+        <v>7.399999999999999</v>
+      </c>
+      <c r="F8">
+        <v>32.8</v>
+      </c>
+      <c r="G8">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>91.5</v>
+      </c>
+      <c r="C9">
+        <v>93.10000000000001</v>
+      </c>
+      <c r="D9">
+        <v>46.40000000000001</v>
+      </c>
+      <c r="E9">
+        <v>50.8</v>
+      </c>
+      <c r="F9">
+        <v>17.2</v>
+      </c>
+      <c r="G9">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>82.39999999999999</v>
+      </c>
+      <c r="C10">
+        <v>12.4</v>
+      </c>
+      <c r="D10">
+        <v>0.1</v>
+      </c>
+      <c r="E10">
+        <v>4.9</v>
+      </c>
+      <c r="F10">
+        <v>5.600000000000001</v>
+      </c>
+      <c r="G10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0.5</v>
-      </c>
-      <c r="D8">
-        <v>13.3</v>
-      </c>
-      <c r="E8">
-        <v>23.5</v>
-      </c>
-      <c r="F8">
-        <v>24.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9">
-        <v>17</v>
-      </c>
-      <c r="C9">
-        <v>11.8</v>
-      </c>
-      <c r="D9">
-        <v>74.5</v>
-      </c>
-      <c r="E9">
-        <v>20.5</v>
-      </c>
-      <c r="F9">
-        <v>21.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>97.8</v>
-      </c>
-      <c r="C10">
-        <v>76.8</v>
-      </c>
-      <c r="D10">
-        <v>20.7</v>
-      </c>
-      <c r="E10">
-        <v>8.5</v>
-      </c>
-      <c r="F10">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="B11">
-        <v>82.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>14.2</v>
+        <v>0.8</v>
       </c>
       <c r="D11">
-        <v>0.1</v>
+        <v>14.7</v>
       </c>
       <c r="E11">
-        <v>4.6</v>
+        <v>27.5</v>
       </c>
       <c r="F11">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>3.1</v>
+      </c>
+      <c r="G11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B12">
+        <v>0.3</v>
+      </c>
+      <c r="C12">
+        <v>16.6</v>
+      </c>
+      <c r="D12">
+        <v>1.2</v>
+      </c>
+      <c r="E12">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="F12">
         <v>0.2</v>
       </c>
-      <c r="C12">
-        <v>15.8</v>
-      </c>
-      <c r="D12">
-        <v>0.5</v>
-      </c>
-      <c r="E12">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -2727,6 +2879,9 @@
         <v>0</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>0</v>
       </c>
     </row>
@@ -2742,28 +2897,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2771,28 +2926,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D2">
-        <v>85.2</v>
+        <v>113.82</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>116.46</v>
+        <v>116.54</v>
       </c>
       <c r="G2">
-        <v>0.545</v>
+        <v>0.46</v>
       </c>
       <c r="H2">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2800,28 +2955,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3">
-        <v>114.99</v>
+        <v>107.03</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>113.75</v>
+        <v>117.62</v>
       </c>
       <c r="G3">
         <v>0.5</v>
       </c>
       <c r="H3">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2829,28 +2984,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4">
-        <v>105.3</v>
+        <v>111.18</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
       </c>
       <c r="F4">
-        <v>114.63</v>
+        <v>117.62</v>
       </c>
       <c r="G4">
         <v>0.5</v>
       </c>
       <c r="H4">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2858,28 +3013,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5">
-        <v>114.92</v>
+        <v>115.22</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>113.76</v>
+        <v>116.54</v>
       </c>
       <c r="G5">
-        <v>0.477</v>
+        <v>0.46</v>
       </c>
       <c r="H5">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2887,28 +3042,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D6">
-        <v>117.78</v>
+        <v>124.29</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>113.5</v>
+        <v>118.22</v>
       </c>
       <c r="G6">
-        <v>0.477</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H6">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2916,28 +3071,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7">
+        <v>87.98</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>118.22</v>
+      </c>
+      <c r="G7">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7">
-        <v>117.27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>113.54</v>
-      </c>
-      <c r="G7">
-        <v>0.5</v>
-      </c>
-      <c r="H7">
-        <v>-0.1</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2945,28 +3100,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D8">
-        <v>123.66</v>
+        <v>133.64</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
       </c>
       <c r="F8">
-        <v>112.96</v>
+        <v>114.21</v>
       </c>
       <c r="G8">
-        <v>0.477</v>
+        <v>0.48</v>
       </c>
       <c r="H8">
-        <v>-0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2974,28 +3129,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9">
-        <v>118.4</v>
+        <v>118.68</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9">
-        <v>113.44</v>
+        <v>114.21</v>
       </c>
       <c r="G9">
-        <v>0.477</v>
+        <v>0.48</v>
       </c>
       <c r="H9">
         <v>-0.5</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3003,28 +3158,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D10">
-        <v>132.06</v>
+        <v>104.66</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F10">
-        <v>112.2</v>
+        <v>116.89</v>
       </c>
       <c r="G10">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="H10">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3032,28 +3187,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D11">
-        <v>116.47</v>
+        <v>120.86</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>113.62</v>
+        <v>116.89</v>
       </c>
       <c r="G11">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="H11">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3061,28 +3216,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D12">
-        <v>105.77</v>
+        <v>131.37</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>114.59</v>
+        <v>113.74</v>
       </c>
       <c r="G12">
-        <v>0.523</v>
+        <v>0.48</v>
       </c>
       <c r="H12">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="I12">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3090,28 +3245,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13">
-        <v>114.44</v>
+        <v>125.69</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>113.8</v>
+        <v>113.74</v>
       </c>
       <c r="G13">
-        <v>0.523</v>
+        <v>0.48</v>
       </c>
       <c r="H13">
-        <v>-0.9</v>
+        <v>-1.1</v>
       </c>
       <c r="I13">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3126,31 +3281,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3158,28 +3313,28 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D2">
-        <v>132.055</v>
+        <v>133.644</v>
       </c>
       <c r="E2">
-        <v>528.22</v>
+        <v>668.22</v>
       </c>
       <c r="F2">
-        <v>81.69999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3187,57 +3342,57 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D3">
-        <v>123.655</v>
+        <v>131.372</v>
       </c>
       <c r="E3">
-        <v>494.62</v>
+        <v>656.86</v>
       </c>
       <c r="F3">
-        <v>76.2</v>
+        <v>78.7</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D4">
-        <v>118.4</v>
+        <v>125.688</v>
       </c>
       <c r="E4">
-        <v>473.6</v>
+        <v>628.4400000000001</v>
       </c>
       <c r="F4">
-        <v>56.39999999999999</v>
+        <v>60.6</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3245,202 +3400,202 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C5">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D5">
-        <v>117.78</v>
+        <v>115.224</v>
       </c>
       <c r="E5">
-        <v>471.12</v>
+        <v>576.12</v>
       </c>
       <c r="F5">
-        <v>54.40000000000001</v>
+        <v>42.3</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D6">
-        <v>114.92</v>
+        <v>120.856</v>
       </c>
       <c r="E6">
-        <v>459.68</v>
+        <v>604.28</v>
       </c>
       <c r="F6">
-        <v>38.1</v>
+        <v>38.7</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D7">
-        <v>117.27</v>
+        <v>118.684</v>
       </c>
       <c r="E7">
-        <v>469.08</v>
+        <v>593.4200000000001</v>
       </c>
       <c r="F7">
-        <v>30.8</v>
+        <v>38.5</v>
       </c>
       <c r="G7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D8">
-        <v>116.465</v>
+        <v>124.292</v>
       </c>
       <c r="E8">
-        <v>465.8600000000001</v>
+        <v>621.46</v>
       </c>
       <c r="F8">
-        <v>24.5</v>
+        <v>26.1</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D9">
-        <v>114.99</v>
+        <v>113.816</v>
       </c>
       <c r="E9">
-        <v>459.96</v>
+        <v>569.08</v>
       </c>
       <c r="F9">
-        <v>23.5</v>
+        <v>16.5</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
       </c>
       <c r="C10">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="D10">
-        <v>114.445</v>
+        <v>107.028</v>
       </c>
       <c r="E10">
-        <v>457.78</v>
+        <v>535.14</v>
       </c>
       <c r="F10">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="G10">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D11">
-        <v>105.3</v>
+        <v>111.184</v>
       </c>
       <c r="E11">
-        <v>421.2</v>
+        <v>555.9200000000001</v>
       </c>
       <c r="F11">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="G11">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3448,28 +3603,28 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C12">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D12">
-        <v>105.765</v>
+        <v>104.664</v>
       </c>
       <c r="E12">
-        <v>423.06</v>
+        <v>523.3200000000001</v>
       </c>
       <c r="F12">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="H12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3477,28 +3632,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>85.19999999999999</v>
+        <v>87.98399999999999</v>
       </c>
       <c r="E13">
-        <v>340.8</v>
+        <v>439.92</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>97</v>
+        <v>95.7</v>
       </c>
       <c r="H13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -3513,19 +3668,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3536,16 +3691,16 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3553,19 +3708,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3573,19 +3728,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3593,19 +3748,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3613,19 +3768,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3633,19 +3788,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3653,19 +3808,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3673,19 +3828,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3693,19 +3848,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3713,19 +3868,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D11">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3733,19 +3888,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D12">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3753,19 +3908,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D13">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -3775,27 +3930,30 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>108</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3811,228 +3969,264 @@
       <c r="E2">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="F2">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>-1</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
         <v>7</v>
       </c>
-      <c r="E4">
+      <c r="G5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
       </c>
       <c r="B6">
         <v>-1</v>
       </c>
       <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>-7</v>
+      </c>
+      <c r="D7">
+        <v>-4</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D6">
+      <c r="B8">
         <v>6</v>
       </c>
-      <c r="E6">
+      <c r="C8">
+        <v>-2</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>-9</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
         <v>5</v>
       </c>
-      <c r="F6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>-1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>-6</v>
+      </c>
+      <c r="C10">
         <v>-2</v>
       </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>-3</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
+      <c r="D10">
         <v>1</v>
-      </c>
-      <c r="C8">
-        <v>-7</v>
-      </c>
-      <c r="D8">
-        <v>-4</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>-6</v>
-      </c>
-      <c r="C9">
-        <v>-2</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>-6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>-6</v>
-      </c>
-      <c r="D10">
-        <v>-5</v>
       </c>
       <c r="E10">
         <v>-6</v>
       </c>
-      <c r="F10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10">
+        <v>-4</v>
+      </c>
+      <c r="G10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>-6</v>
+      </c>
+      <c r="D11">
+        <v>-5</v>
+      </c>
+      <c r="E11">
+        <v>-6</v>
+      </c>
+      <c r="F11">
+        <v>-11</v>
+      </c>
+      <c r="G11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>-8</v>
+      </c>
+      <c r="C12">
+        <v>-7</v>
+      </c>
+      <c r="D12">
+        <v>-9</v>
+      </c>
+      <c r="E12">
+        <v>-12</v>
+      </c>
+      <c r="F12">
+        <v>-12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B11">
+      <c r="B13">
         <v>2</v>
       </c>
-      <c r="C11">
+      <c r="C13">
         <v>-8</v>
       </c>
-      <c r="D11">
+      <c r="D13">
         <v>-15</v>
       </c>
-      <c r="E11">
+      <c r="E13">
         <v>-8</v>
       </c>
-      <c r="F11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>-2</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>-9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>-8</v>
-      </c>
-      <c r="C13">
-        <v>-7</v>
-      </c>
-      <c r="D13">
-        <v>-9</v>
-      </c>
-      <c r="E13">
-        <v>-12</v>
-      </c>
-      <c r="F13" t="s">
-        <v>100</v>
+      <c r="F13">
+        <v>-13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/The Girl's Room 💞🏈 2026.xlsx
+++ b/data/leagues/The Girl's Room 💞🏈 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="123">
   <si>
     <t>Tush Push Director 🍑</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Sacks and the City</t>
   </si>
   <si>
-    <t>Hurts Locker Room Talk</t>
+    <t>RIP Jalen 😭</t>
   </si>
   <si>
     <t>Say Cheese 🧀💚🧀</t>
@@ -61,22 +61,25 @@
     <t xml:space="preserve">michelle’s boy toys </t>
   </si>
   <si>
-    <t>3-2-0</t>
-  </si>
-  <si>
-    <t>2-3-0</t>
-  </si>
-  <si>
-    <t>4-1-0</t>
-  </si>
-  <si>
-    <t>0-5-0</t>
-  </si>
-  <si>
-    <t>5-0-0</t>
-  </si>
-  <si>
-    <t>1-4-0</t>
+    <t>3-3-0</t>
+  </si>
+  <si>
+    <t>4-2-0</t>
+  </si>
+  <si>
+    <t>2-4-0</t>
+  </si>
+  <si>
+    <t>0-6-0</t>
+  </si>
+  <si>
+    <t>5-1-0</t>
+  </si>
+  <si>
+    <t>6-0-0</t>
+  </si>
+  <si>
+    <t>1-5-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -154,6 +157,9 @@
     <t>Week_6</t>
   </si>
   <si>
+    <t>Week_7</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -175,42 +181,42 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Kiana McIntosh</t>
+  </si>
+  <si>
+    <t>Michelle Nocitra</t>
+  </si>
+  <si>
+    <t>Allie Kardon</t>
+  </si>
+  <si>
+    <t>nidhi shah</t>
+  </si>
+  <si>
+    <t>Grace Stockbower</t>
+  </si>
+  <si>
     <t>Sumita Gangwani</t>
   </si>
   <si>
-    <t>Kiana McIntosh</t>
-  </si>
-  <si>
     <t>Amanda Pasquale</t>
   </si>
   <si>
-    <t>nidhi shah</t>
-  </si>
-  <si>
-    <t>Grace Stockbower</t>
-  </si>
-  <si>
-    <t>Michelle Nocitra</t>
-  </si>
-  <si>
-    <t>Allie Kardon</t>
+    <t>Bianca Magsino</t>
+  </si>
+  <si>
+    <t>Hannah Miller</t>
+  </si>
+  <si>
+    <t>Emily Carey</t>
+  </si>
+  <si>
+    <t>Hillary Dale</t>
   </si>
   <si>
     <t>Malini Ragoopath</t>
   </si>
   <si>
-    <t>Hillary Dale</t>
-  </si>
-  <si>
-    <t>Bianca Magsino</t>
-  </si>
-  <si>
-    <t>Emily Carey</t>
-  </si>
-  <si>
-    <t>Hannah Miller</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -235,52 +241,55 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>0-5</t>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>0-6</t>
   </si>
   <si>
     <t>10.2-4.7-0.1</t>
   </si>
   <si>
-    <t>9.8-5.1-0.1</t>
-  </si>
-  <si>
-    <t>9.1-5.8-0.1</t>
-  </si>
-  <si>
-    <t>8.9-6.0-0.1</t>
-  </si>
-  <si>
-    <t>8.4-6.4-0.1</t>
-  </si>
-  <si>
-    <t>8.6-6.3-0.1</t>
-  </si>
-  <si>
-    <t>7.7-7.2-0.1</t>
-  </si>
-  <si>
-    <t>6.9-8.0-0.1</t>
-  </si>
-  <si>
-    <t>6.1-8.7-0.1</t>
-  </si>
-  <si>
-    <t>4.4-10.5-0.1</t>
-  </si>
-  <si>
-    <t>1.5-13.4-0.1</t>
+    <t>9.7-5.2-0.1</t>
+  </si>
+  <si>
+    <t>8.9-6.1-0.1</t>
+  </si>
+  <si>
+    <t>8.8-6.1-0.1</t>
+  </si>
+  <si>
+    <t>8.3-6.6-0.1</t>
+  </si>
+  <si>
+    <t>8.2-6.6-0.1</t>
+  </si>
+  <si>
+    <t>8.0-6.9-0.1</t>
+  </si>
+  <si>
+    <t>7.6-7.4-0.1</t>
+  </si>
+  <si>
+    <t>7.0-7.9-0.1</t>
+  </si>
+  <si>
+    <t>5.9-9.0-0.1</t>
+  </si>
+  <si>
+    <t>5.7-9.2-0.1</t>
+  </si>
+  <si>
+    <t>1.1-13.9-0.1</t>
   </si>
   <si>
     <t>11-4</t>
@@ -295,12 +304,15 @@
     <t>8-7</t>
   </si>
   <si>
+    <t>7-8</t>
+  </si>
+  <si>
+    <t>5-10</t>
+  </si>
+  <si>
     <t>6-9</t>
   </si>
   <si>
-    <t>4-11</t>
-  </si>
-  <si>
     <t>1-14</t>
   </si>
   <si>
@@ -313,28 +325,34 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑5</t>
+  </si>
+  <si>
     <t>↑2</t>
   </si>
   <si>
-    <t>↑8</t>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↓2</t>
   </si>
   <si>
     <t>↑4</t>
   </si>
   <si>
-    <t>↓2</t>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↓5</t>
   </si>
   <si>
     <t>↓7</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↑10</t>
-  </si>
-  <si>
-    <t>↓5</t>
+    <t>↓4</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -350,6 +368,9 @@
   </si>
   <si>
     <t>Week 5</t>
+  </si>
+  <si>
+    <t>Week 6</t>
   </si>
   <si>
     <t>Week</t>
@@ -777,37 +798,37 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2" t="s">
         <v>12</v>
       </c>
       <c r="L2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -818,37 +839,37 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -856,40 +877,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" t="s">
-        <v>14</v>
-      </c>
       <c r="L4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -900,10 +921,10 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -912,7 +933,7 @@
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
         <v>12</v>
@@ -921,13 +942,13 @@
         <v>16</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K5" t="s">
         <v>16</v>
       </c>
       <c r="L5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M5" t="s">
         <v>12</v>
@@ -938,40 +959,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" t="s">
         <v>16</v>
       </c>
-      <c r="J6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L6" t="s">
-        <v>14</v>
-      </c>
       <c r="M6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -979,40 +1000,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1023,19 +1044,19 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
         <v>12</v>
@@ -1044,7 +1065,7 @@
         <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K8" t="s">
         <v>16</v>
@@ -1061,40 +1082,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" t="s">
         <v>17</v>
       </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" t="s">
-        <v>13</v>
-      </c>
-      <c r="K9" t="s">
-        <v>16</v>
-      </c>
       <c r="L9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1102,16 +1123,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -1120,19 +1141,19 @@
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" t="s">
         <v>12</v>
       </c>
       <c r="J10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M10" t="s">
         <v>15</v>
@@ -1146,37 +1167,37 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" t="s">
         <v>16</v>
       </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" t="s">
-        <v>14</v>
-      </c>
       <c r="L11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1184,25 +1205,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I12" t="s">
         <v>12</v>
@@ -1211,13 +1232,13 @@
         <v>12</v>
       </c>
       <c r="K12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1228,7 +1249,7 @@
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -1237,13 +1258,13 @@
         <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
@@ -1252,10 +1273,10 @@
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M13" t="s">
         <v>15</v>
@@ -1273,25 +1294,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1299,25 +1320,25 @@
         <v>0</v>
       </c>
       <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
       <c r="E2">
-        <v>11</v>
+        <v>-11</v>
       </c>
       <c r="F2">
-        <v>-4</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1325,25 +1346,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>-13</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="G3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1354,22 +1375,22 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>-13</v>
       </c>
       <c r="F4">
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1380,22 +1401,22 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F5">
+        <v>-11</v>
+      </c>
+      <c r="G5">
         <v>10</v>
       </c>
-      <c r="G5">
+      <c r="H5" t="s">
         <v>9</v>
-      </c>
-      <c r="H5" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1429,25 +1450,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
         <v>4</v>
       </c>
-      <c r="D7" t="s">
-        <v>2</v>
-      </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>10</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1455,22 +1476,22 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
         <v>4</v>
@@ -1481,25 +1502,25 @@
         <v>7</v>
       </c>
       <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
         <v>5</v>
       </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
       <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+      <c r="G9">
         <v>7</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
-      </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1533,25 +1554,25 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11">
         <v>7</v>
-      </c>
-      <c r="E11">
-        <v>5</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1559,25 +1580,25 @@
         <v>10</v>
       </c>
       <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
         <v>4</v>
       </c>
-      <c r="C12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12">
-        <v>10</v>
-      </c>
-      <c r="F12">
-        <v>8</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
       <c r="H12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1592,13 +1613,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1609,10 +1630,10 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>1.166666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1620,13 +1641,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1.75</v>
-      </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1637,7 +1658,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>1.75</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -1648,13 +1669,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>1.916666666666667</v>
+        <v>2.5</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1662,10 +1683,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>2.5</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -1676,13 +1697,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>2.583333333333333</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1690,10 +1711,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -1704,10 +1725,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>2.75</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -1721,7 +1742,7 @@
         <v>6</v>
       </c>
       <c r="C10">
-        <v>2.833333333333333</v>
+        <v>3.5</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1732,13 +1753,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>2.916666666666667</v>
+        <v>3.583333333333333</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1749,10 +1770,10 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>3.333333333333333</v>
+        <v>4.25</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1763,10 +1784,10 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>3.75</v>
+        <v>4.416666666666667</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1781,16 +1802,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1798,16 +1819,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>3.333333333333333</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="D2">
-        <v>0.3333333333333335</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1815,13 +1836,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>3.333333333333333</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="D3">
-        <v>0.3333333333333335</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1832,13 +1853,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>2.916666666666667</v>
+        <v>3.583333333333333</v>
       </c>
       <c r="D4">
-        <v>-0.08333333333333348</v>
+        <v>0.5833333333333335</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
@@ -1852,13 +1873,13 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>2.833333333333333</v>
+        <v>3.5</v>
       </c>
       <c r="D5">
-        <v>-1.166666666666667</v>
+        <v>-1.5</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1869,13 +1890,13 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>2.833333333333333</v>
+        <v>3.25</v>
       </c>
       <c r="D6">
-        <v>-0.1666666666666665</v>
+        <v>-0.75</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1883,16 +1904,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>2.75</v>
+        <v>3.083333333333333</v>
       </c>
       <c r="D7">
-        <v>0.75</v>
+        <v>0.08333333333333348</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1900,16 +1921,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>2.666666666666667</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>-0.3333333333333335</v>
+        <v>-1</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1917,13 +1938,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>2.583333333333333</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>-0.4166666666666665</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -1934,13 +1955,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>2.25</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="D10">
-        <v>-0.75</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -1951,16 +1972,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1968,16 +1989,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>1.75</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="D12">
-        <v>0.75</v>
+        <v>0.4166666666666665</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2009,84 +2030,84 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
-        <v>38.4</v>
+        <v>46.9</v>
       </c>
       <c r="C2">
-        <v>23.4</v>
+        <v>20.3</v>
       </c>
       <c r="D2">
-        <v>16.7</v>
+        <v>13.1</v>
       </c>
       <c r="E2">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="F2">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="G2">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="H2">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="I2">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J2">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -2097,37 +2118,37 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>29.2</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>21.1</v>
+        <v>17.9</v>
       </c>
       <c r="D3">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>14.8</v>
       </c>
       <c r="F3">
-        <v>9.699999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="G3">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="H3">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J3">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="K3">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -2136,21 +2157,21 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>78.7</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="C4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="D4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="E4">
         <v>15.1</v>
@@ -2159,22 +2180,22 @@
         <v>12.5</v>
       </c>
       <c r="G4">
-        <v>8.800000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="L4">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -2185,37 +2206,37 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="C5">
-        <v>10.3</v>
+        <v>11.9</v>
       </c>
       <c r="D5">
-        <v>10.6</v>
+        <v>14.1</v>
       </c>
       <c r="E5">
-        <v>13.7</v>
+        <v>14.9</v>
       </c>
       <c r="F5">
-        <v>13.7</v>
+        <v>12.8</v>
       </c>
       <c r="G5">
-        <v>13.4</v>
+        <v>14.3</v>
       </c>
       <c r="H5">
-        <v>13.1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="K5">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="L5">
         <v>0.6</v>
@@ -2224,51 +2245,51 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>42.3</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B6">
-        <v>4.7</v>
+        <v>7.1</v>
       </c>
       <c r="C6">
-        <v>8.6</v>
+        <v>11.3</v>
       </c>
       <c r="D6">
-        <v>10.9</v>
+        <v>12.9</v>
       </c>
       <c r="E6">
-        <v>14.5</v>
+        <v>12.7</v>
       </c>
       <c r="F6">
-        <v>15.1</v>
+        <v>13.8</v>
       </c>
       <c r="G6">
-        <v>13.8</v>
+        <v>11</v>
       </c>
       <c r="H6">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="I6">
-        <v>11.3</v>
+        <v>8.9</v>
       </c>
       <c r="J6">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="K6">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="L6">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>38.7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -2276,175 +2297,175 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="C7">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="E7">
-        <v>13.6</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>15.2</v>
+        <v>14.6</v>
       </c>
       <c r="G7">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="H7">
-        <v>12.1</v>
+        <v>13</v>
       </c>
       <c r="I7">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="K7">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="L7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7">
-        <v>38.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B8">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="C8">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="D8">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E8">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="F8">
-        <v>11.6</v>
+        <v>10.1</v>
       </c>
       <c r="G8">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="H8">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="I8">
-        <v>15.5</v>
+        <v>10.1</v>
       </c>
       <c r="J8">
-        <v>9.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K8">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="L8">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8">
-        <v>26.1</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="C9">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="D9">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="E9">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>10.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G9">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="H9">
-        <v>16.1</v>
+        <v>12.8</v>
       </c>
       <c r="I9">
-        <v>19</v>
+        <v>17.4</v>
       </c>
       <c r="J9">
-        <v>14.8</v>
+        <v>16.8</v>
       </c>
       <c r="K9">
-        <v>8.199999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="L9">
-        <v>1.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
-        <v>16.5</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B10">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="D10">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="E10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F10">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="G10">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H10">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="I10">
-        <v>12.9</v>
+        <v>15.2</v>
       </c>
       <c r="J10">
-        <v>22.2</v>
+        <v>18.8</v>
       </c>
       <c r="K10">
-        <v>24.4</v>
+        <v>16.5</v>
       </c>
       <c r="L10">
-        <v>8.699999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="M10">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2452,43 +2473,43 @@
         <v>8</v>
       </c>
       <c r="B11">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C11">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="D11">
         <v>0.8</v>
       </c>
       <c r="E11">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F11">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="G11">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="H11">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="I11">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="J11">
-        <v>23.1</v>
+        <v>17.4</v>
       </c>
       <c r="K11">
-        <v>34.1</v>
+        <v>26.5</v>
       </c>
       <c r="L11">
-        <v>12.2</v>
+        <v>30.2</v>
       </c>
       <c r="M11">
         <v>0.2</v>
       </c>
       <c r="N11">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2496,43 +2517,43 @@
         <v>5</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F12">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="G12">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="H12">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="I12">
-        <v>2.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12">
-        <v>7</v>
+        <v>15.6</v>
       </c>
       <c r="K12">
-        <v>15.2</v>
+        <v>26</v>
       </c>
       <c r="L12">
-        <v>69.59999999999999</v>
+        <v>39.2</v>
       </c>
       <c r="M12">
-        <v>3.9</v>
+        <v>0.2</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2567,13 +2588,13 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="M13">
-        <v>95.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2586,237 +2607,267 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>43</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>20.6</v>
+      </c>
+      <c r="D2">
+        <v>23.6</v>
+      </c>
+      <c r="E2">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="F2">
+        <v>80.10000000000001</v>
+      </c>
+      <c r="G2">
+        <v>89.60000000000001</v>
+      </c>
+      <c r="H2">
+        <v>88.59999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>81.89999999999999</v>
+      </c>
+      <c r="C3">
+        <v>48.2</v>
+      </c>
+      <c r="D3">
+        <v>25.5</v>
+      </c>
+      <c r="E3">
+        <v>59.7</v>
+      </c>
+      <c r="F3">
+        <v>39.1</v>
+      </c>
+      <c r="G3">
+        <v>64.7</v>
+      </c>
+      <c r="H3">
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>1.8</v>
-      </c>
-      <c r="C2">
+      <c r="B4">
+        <v>1.9</v>
+      </c>
+      <c r="C4">
+        <v>98.3</v>
+      </c>
+      <c r="D4">
         <v>98.40000000000001</v>
       </c>
-      <c r="D2">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="E2">
-        <v>84.8</v>
-      </c>
-      <c r="F2">
-        <v>85.7</v>
-      </c>
-      <c r="G2">
-        <v>87.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>23.7</v>
-      </c>
-      <c r="D3">
-        <v>22</v>
-      </c>
-      <c r="E3">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="F3">
-        <v>79.80000000000001</v>
-      </c>
-      <c r="G3">
-        <v>80.30000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>16.4</v>
-      </c>
-      <c r="C4">
+      <c r="E4">
+        <v>86.3</v>
+      </c>
+      <c r="F4">
+        <v>87.2</v>
+      </c>
+      <c r="G4">
+        <v>61.3</v>
+      </c>
+      <c r="H4">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4">
-        <v>74.2</v>
-      </c>
-      <c r="E4">
-        <v>22.1</v>
-      </c>
-      <c r="F4">
-        <v>59.3</v>
-      </c>
-      <c r="G4">
-        <v>64.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="B5">
-        <v>82.39999999999999</v>
+        <v>26.6</v>
       </c>
       <c r="C5">
-        <v>45.4</v>
+        <v>9.4</v>
       </c>
       <c r="D5">
-        <v>28.6</v>
+        <v>45.9</v>
       </c>
       <c r="E5">
-        <v>58.7</v>
+        <v>31.9</v>
       </c>
       <c r="F5">
-        <v>39.90000000000001</v>
+        <v>42.4</v>
       </c>
       <c r="G5">
-        <v>39.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>47</v>
+      </c>
+      <c r="H5">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B6">
-        <v>23.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="C6">
-        <v>8.9</v>
+        <v>77.60000000000001</v>
       </c>
       <c r="D6">
-        <v>47.59999999999999</v>
+        <v>21.4</v>
       </c>
       <c r="E6">
-        <v>29.7</v>
+        <v>8.799999999999999</v>
       </c>
       <c r="F6">
-        <v>42.6</v>
+        <v>31.1</v>
       </c>
       <c r="G6">
-        <v>38.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>46.6</v>
+      </c>
+      <c r="H6">
+        <v>40.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="C7">
-        <v>14.5</v>
+        <v>13.9</v>
       </c>
       <c r="D7">
-        <v>46.40000000000001</v>
+        <v>51.4</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>35.7</v>
       </c>
       <c r="F7">
-        <v>33.8</v>
+        <v>35.2</v>
       </c>
       <c r="G7">
-        <v>37.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>30.5</v>
+      </c>
+      <c r="H7">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B8">
-        <v>98.3</v>
+        <v>16</v>
       </c>
       <c r="C8">
-        <v>76.2</v>
+        <v>9.1</v>
       </c>
       <c r="D8">
-        <v>21.7</v>
+        <v>74.7</v>
       </c>
       <c r="E8">
-        <v>7.399999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="F8">
-        <v>32.8</v>
+        <v>56.99999999999999</v>
       </c>
       <c r="G8">
-        <v>25.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>32.1</v>
+      </c>
+      <c r="H8">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9">
-        <v>91.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="C9">
+        <v>14.3</v>
+      </c>
+      <c r="D9">
+        <v>0.2</v>
+      </c>
+      <c r="E9">
+        <v>4.399999999999999</v>
+      </c>
+      <c r="F9">
+        <v>6.7</v>
+      </c>
+      <c r="G9">
+        <v>17.5</v>
+      </c>
+      <c r="H9">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
         <v>93.10000000000001</v>
       </c>
-      <c r="D9">
-        <v>46.40000000000001</v>
-      </c>
-      <c r="E9">
-        <v>50.8</v>
-      </c>
-      <c r="F9">
-        <v>17.2</v>
-      </c>
-      <c r="G9">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>82.39999999999999</v>
-      </c>
       <c r="C10">
-        <v>12.4</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D10">
-        <v>0.1</v>
+        <v>44.5</v>
       </c>
       <c r="E10">
-        <v>4.9</v>
+        <v>50.7</v>
       </c>
       <c r="F10">
-        <v>5.600000000000001</v>
+        <v>16.6</v>
       </c>
       <c r="G10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>7.6</v>
+      </c>
+      <c r="H10">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -2824,45 +2875,51 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="D11">
-        <v>14.7</v>
+        <v>13.6</v>
       </c>
       <c r="E11">
-        <v>27.5</v>
+        <v>26.8</v>
       </c>
       <c r="F11">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="G11">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>2.1</v>
+      </c>
+      <c r="H11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>14.8</v>
+      </c>
+      <c r="D12">
+        <v>0.8</v>
+      </c>
+      <c r="E12">
+        <v>0.6</v>
+      </c>
+      <c r="F12">
         <v>0.3</v>
       </c>
-      <c r="C12">
-        <v>16.6</v>
-      </c>
-      <c r="D12">
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
         <v>1.2</v>
       </c>
-      <c r="E12">
-        <v>0.7000000000000001</v>
-      </c>
-      <c r="F12">
-        <v>0.2</v>
-      </c>
-      <c r="G12">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -2882,6 +2939,9 @@
         <v>0</v>
       </c>
       <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>0</v>
       </c>
     </row>
@@ -2897,28 +2957,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2926,28 +2986,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2">
-        <v>113.82</v>
+        <v>108.48</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>116.54</v>
+        <v>118.32</v>
       </c>
       <c r="G2">
-        <v>0.46</v>
+        <v>0.556</v>
       </c>
       <c r="H2">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2955,28 +3015,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D3">
-        <v>107.03</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>117.62</v>
+        <v>116.86</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>0.537</v>
       </c>
       <c r="H3">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2984,28 +3044,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D4">
-        <v>111.18</v>
+        <v>126.59</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>117.62</v>
+        <v>111.85</v>
       </c>
       <c r="G4">
-        <v>0.5</v>
+        <v>0.463</v>
       </c>
       <c r="H4">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3016,25 +3076,25 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D5">
-        <v>115.22</v>
+        <v>115.21</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>116.54</v>
+        <v>112.72</v>
       </c>
       <c r="G5">
-        <v>0.46</v>
+        <v>0.463</v>
       </c>
       <c r="H5">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3045,25 +3105,25 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D6">
-        <v>124.29</v>
+        <v>123.96</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>118.22</v>
+        <v>116.78</v>
       </c>
       <c r="G6">
-        <v>0.5600000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3071,28 +3131,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>87.98</v>
+        <v>109.2</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>118.22</v>
+        <v>113.01</v>
       </c>
       <c r="G7">
-        <v>0.5600000000000001</v>
+        <v>0.463</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3100,28 +3160,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D8">
-        <v>133.64</v>
+        <v>110.78</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>114.21</v>
+        <v>115.31</v>
       </c>
       <c r="G8">
-        <v>0.48</v>
+        <v>0.519</v>
       </c>
       <c r="H8">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3129,28 +3189,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D9">
-        <v>118.68</v>
+        <v>117.06</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>114.21</v>
+        <v>113.57</v>
       </c>
       <c r="G9">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="H9">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3158,28 +3218,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D10">
-        <v>104.66</v>
+        <v>117.88</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>116.89</v>
+        <v>111.23</v>
       </c>
       <c r="G10">
-        <v>0.52</v>
+        <v>0.463</v>
       </c>
       <c r="H10">
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3187,28 +3247,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D11">
-        <v>120.86</v>
+        <v>129.51</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>116.89</v>
+        <v>111.23</v>
       </c>
       <c r="G11">
-        <v>0.52</v>
+        <v>0.481</v>
       </c>
       <c r="H11">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3216,28 +3276,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D12">
-        <v>131.37</v>
+        <v>108.45</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F12">
-        <v>113.74</v>
+        <v>114.36</v>
       </c>
       <c r="G12">
-        <v>0.48</v>
+        <v>0.519</v>
       </c>
       <c r="H12">
-        <v>-1.1</v>
+        <v>-1.6</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3245,28 +3305,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D13">
-        <v>125.69</v>
+        <v>117.06</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
       </c>
       <c r="F13">
-        <v>113.74</v>
+        <v>110.26</v>
       </c>
       <c r="G13">
-        <v>0.48</v>
+        <v>0.481</v>
       </c>
       <c r="H13">
-        <v>-1.1</v>
+        <v>-2.3</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3281,48 +3341,48 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C2">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D2">
-        <v>133.644</v>
+        <v>129.5133333333333</v>
       </c>
       <c r="E2">
-        <v>668.22</v>
+        <v>777.08</v>
       </c>
       <c r="F2">
         <v>87.7</v>
@@ -3331,56 +3391,56 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C3">
-        <v>0.6</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D3">
-        <v>131.372</v>
+        <v>115.2066666666667</v>
       </c>
       <c r="E3">
-        <v>656.86</v>
+        <v>691.24</v>
       </c>
       <c r="F3">
-        <v>78.7</v>
+        <v>66.3</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C4">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D4">
-        <v>125.688</v>
+        <v>126.5866666666667</v>
       </c>
       <c r="E4">
-        <v>628.4400000000001</v>
+        <v>759.52</v>
       </c>
       <c r="F4">
         <v>60.6</v>
@@ -3389,68 +3449,68 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>115.224</v>
+        <v>117.06</v>
       </c>
       <c r="E5">
-        <v>576.12</v>
+        <v>702.36</v>
       </c>
       <c r="F5">
-        <v>42.3</v>
+        <v>47.7</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C6">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>120.856</v>
+        <v>123.96</v>
       </c>
       <c r="E6">
-        <v>604.28</v>
+        <v>743.76</v>
       </c>
       <c r="F6">
-        <v>38.7</v>
+        <v>44</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3458,115 +3518,115 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C7">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>118.684</v>
+        <v>117.0566666666667</v>
       </c>
       <c r="E7">
-        <v>593.4200000000001</v>
+        <v>702.34</v>
       </c>
       <c r="F7">
-        <v>38.5</v>
+        <v>34.5</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C8">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>124.292</v>
+        <v>117.88</v>
       </c>
       <c r="E8">
-        <v>621.46</v>
+        <v>707.2800000000001</v>
       </c>
       <c r="F8">
-        <v>26.1</v>
+        <v>31.3</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D9">
-        <v>113.816</v>
+        <v>108.48</v>
       </c>
       <c r="E9">
-        <v>569.08</v>
+        <v>650.88</v>
       </c>
       <c r="F9">
-        <v>16.5</v>
+        <v>15.8</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C10">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>107.028</v>
+        <v>109.2033333333333</v>
       </c>
       <c r="E10">
-        <v>535.14</v>
+        <v>655.22</v>
       </c>
       <c r="F10">
-        <v>7.5</v>
+        <v>8.200000000000001</v>
       </c>
       <c r="G10">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3574,28 +3634,28 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C11">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D11">
-        <v>111.184</v>
+        <v>110.78</v>
       </c>
       <c r="E11">
-        <v>555.9200000000001</v>
+        <v>664.6800000000001</v>
       </c>
       <c r="F11">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="G11">
         <v>0.2</v>
       </c>
       <c r="H11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3603,28 +3663,28 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C12">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D12">
+        <v>108.4533333333333</v>
+      </c>
+      <c r="E12">
+        <v>650.72</v>
+      </c>
+      <c r="F12">
+        <v>1.2</v>
+      </c>
+      <c r="G12">
         <v>0.2</v>
       </c>
-      <c r="D12">
-        <v>104.664</v>
-      </c>
-      <c r="E12">
-        <v>523.3200000000001</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>3.9</v>
-      </c>
       <c r="H12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I12" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3632,28 +3692,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>87.98399999999999</v>
+        <v>81.31666666666666</v>
       </c>
       <c r="E13">
-        <v>439.92</v>
+        <v>487.9</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>95.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I13" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3668,19 +3728,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3688,19 +3748,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3708,19 +3768,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3728,19 +3788,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3748,19 +3808,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D5">
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3771,16 +3831,16 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3788,19 +3848,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3808,19 +3868,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3828,19 +3888,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3848,19 +3908,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D10">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3871,16 +3931,16 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11">
         <v>-11</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3888,19 +3948,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D12">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3908,19 +3968,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13">
-        <v>-13</v>
+        <v>-16</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3930,81 +3990,90 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>115</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>-2</v>
+      </c>
+      <c r="C2">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="D2">
+        <v>-3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
         <v>8</v>
       </c>
-      <c r="C2">
+      <c r="C3">
         <v>10</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>11</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>10</v>
       </c>
-      <c r="F2">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>-2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>-3</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
       <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -4013,21 +4082,24 @@
         <v>6</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -4036,16 +4108,19 @@
         <v>6</v>
       </c>
       <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
         <v>9</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>7</v>
       </c>
-      <c r="G5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -4064,103 +4139,118 @@
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>-1</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="C8">
         <v>-2</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>-4</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>-4</v>
+      </c>
+      <c r="H9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F9">
-        <v>-1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="B10">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <v>-2</v>
       </c>
       <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>-9</v>
+      </c>
+      <c r="F10">
         <v>1</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>-6</v>
       </c>
-      <c r="F10">
-        <v>-4</v>
-      </c>
-      <c r="G10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -4179,54 +4269,63 @@
       <c r="F11">
         <v>-11</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11">
+        <v>-11</v>
+      </c>
+      <c r="H11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>-8</v>
+      </c>
+      <c r="D12">
+        <v>-15</v>
+      </c>
+      <c r="E12">
+        <v>-8</v>
+      </c>
+      <c r="F12">
+        <v>-13</v>
+      </c>
+      <c r="G12">
+        <v>-15</v>
+      </c>
+      <c r="H12" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1" t="s">
+    <row r="13" spans="1:8">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>-8</v>
       </c>
-      <c r="C12">
+      <c r="C13">
         <v>-7</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>-9</v>
       </c>
-      <c r="E12">
+      <c r="E13">
         <v>-12</v>
       </c>
-      <c r="F12">
+      <c r="F13">
         <v>-12</v>
       </c>
-      <c r="G12" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13">
-        <v>-8</v>
-      </c>
-      <c r="D13">
-        <v>-15</v>
-      </c>
-      <c r="E13">
-        <v>-8</v>
-      </c>
-      <c r="F13">
-        <v>-13</v>
-      </c>
-      <c r="G13" t="s">
-        <v>103</v>
+      <c r="G13">
+        <v>-16</v>
+      </c>
+      <c r="H13" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/The Girl's Room 💞🏈 2026.xlsx
+++ b/data/leagues/The Girl's Room 💞🏈 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="126">
   <si>
     <t>Tush Push Director 🍑</t>
   </si>
@@ -61,25 +61,28 @@
     <t xml:space="preserve">michelle’s boy toys </t>
   </si>
   <si>
-    <t>3-3-0</t>
-  </si>
-  <si>
-    <t>4-2-0</t>
-  </si>
-  <si>
-    <t>2-4-0</t>
-  </si>
-  <si>
-    <t>0-6-0</t>
-  </si>
-  <si>
-    <t>5-1-0</t>
-  </si>
-  <si>
-    <t>6-0-0</t>
-  </si>
-  <si>
-    <t>1-5-0</t>
+    <t>4-3-0</t>
+  </si>
+  <si>
+    <t>3-4-0</t>
+  </si>
+  <si>
+    <t>5-2-0</t>
+  </si>
+  <si>
+    <t>2-5-0</t>
+  </si>
+  <si>
+    <t>0-7-0</t>
+  </si>
+  <si>
+    <t>6-1-0</t>
+  </si>
+  <si>
+    <t>7-0-0</t>
+  </si>
+  <si>
+    <t>1-6-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -160,6 +163,9 @@
     <t>Week_7</t>
   </si>
   <si>
+    <t>Week_8</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -184,39 +190,39 @@
     <t>Kiana McIntosh</t>
   </si>
   <si>
+    <t>Sumita Gangwani</t>
+  </si>
+  <si>
+    <t>Amanda Pasquale</t>
+  </si>
+  <si>
     <t>Michelle Nocitra</t>
   </si>
   <si>
+    <t>Hillary Dale</t>
+  </si>
+  <si>
+    <t>nidhi shah</t>
+  </si>
+  <si>
+    <t>Grace Stockbower</t>
+  </si>
+  <si>
+    <t>Hannah Miller</t>
+  </si>
+  <si>
+    <t>Emily Carey</t>
+  </si>
+  <si>
     <t>Allie Kardon</t>
   </si>
   <si>
-    <t>nidhi shah</t>
-  </si>
-  <si>
-    <t>Grace Stockbower</t>
-  </si>
-  <si>
-    <t>Sumita Gangwani</t>
-  </si>
-  <si>
-    <t>Amanda Pasquale</t>
+    <t>Malini Ragoopath</t>
   </si>
   <si>
     <t>Bianca Magsino</t>
   </si>
   <si>
-    <t>Hannah Miller</t>
-  </si>
-  <si>
-    <t>Emily Carey</t>
-  </si>
-  <si>
-    <t>Hillary Dale</t>
-  </si>
-  <si>
-    <t>Malini Ragoopath</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -241,58 +247,55 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>0-6</t>
-  </si>
-  <si>
-    <t>10.2-4.7-0.1</t>
-  </si>
-  <si>
-    <t>9.7-5.2-0.1</t>
-  </si>
-  <si>
-    <t>8.9-6.1-0.1</t>
-  </si>
-  <si>
-    <t>8.8-6.1-0.1</t>
-  </si>
-  <si>
-    <t>8.3-6.6-0.1</t>
-  </si>
-  <si>
-    <t>8.2-6.6-0.1</t>
-  </si>
-  <si>
-    <t>8.0-6.9-0.1</t>
-  </si>
-  <si>
-    <t>7.6-7.4-0.1</t>
-  </si>
-  <si>
-    <t>7.0-7.9-0.1</t>
-  </si>
-  <si>
-    <t>5.9-9.0-0.1</t>
-  </si>
-  <si>
-    <t>5.7-9.2-0.1</t>
-  </si>
-  <si>
-    <t>1.1-13.9-0.1</t>
-  </si>
-  <si>
-    <t>11-4</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>0-7</t>
+  </si>
+  <si>
+    <t>10.0-4.9-0.1</t>
+  </si>
+  <si>
+    <t>9.6-5.4-0.1</t>
+  </si>
+  <si>
+    <t>9.4-5.6-0.1</t>
+  </si>
+  <si>
+    <t>8.9-6.0-0.1</t>
+  </si>
+  <si>
+    <t>9.0-5.9-0.1</t>
+  </si>
+  <si>
+    <t>8.6-6.3-0.1</t>
+  </si>
+  <si>
+    <t>7.7-7.2-0.1</t>
+  </si>
+  <si>
+    <t>7.2-7.7-0.1</t>
+  </si>
+  <si>
+    <t>6.4-8.5-0.1</t>
+  </si>
+  <si>
+    <t>6.7-8.3-0.1</t>
+  </si>
+  <si>
+    <t>5.1-9.8-0.1</t>
+  </si>
+  <si>
+    <t>0.9-14.1</t>
   </si>
   <si>
     <t>10-5</t>
@@ -307,12 +310,12 @@
     <t>7-8</t>
   </si>
   <si>
+    <t>6-9</t>
+  </si>
+  <si>
     <t>5-10</t>
   </si>
   <si>
-    <t>6-9</t>
-  </si>
-  <si>
     <t>1-14</t>
   </si>
   <si>
@@ -325,36 +328,39 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↓4</t>
+  </si>
+  <si>
     <t>↑5</t>
   </si>
   <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↑6</t>
+    <t>↓5</t>
   </si>
   <si>
     <t>↓2</t>
   </si>
   <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↓5</t>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↓3</t>
   </si>
   <si>
     <t>↓7</t>
   </si>
   <si>
-    <t>↓4</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -371,6 +377,9 @@
   </si>
   <si>
     <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
   </si>
   <si>
     <t>Week</t>
@@ -798,37 +807,37 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" t="s">
-        <v>12</v>
-      </c>
       <c r="L2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -836,40 +845,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" t="s">
         <v>13</v>
-      </c>
-      <c r="L3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -880,37 +889,37 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
       <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
       <c r="G4" t="s">
         <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" t="s">
         <v>13</v>
-      </c>
-      <c r="J4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -921,7 +930,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
@@ -930,25 +939,25 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
         <v>14</v>
       </c>
-      <c r="H5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" t="s">
-        <v>13</v>
-      </c>
       <c r="K5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M5" t="s">
         <v>12</v>
@@ -959,40 +968,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
       </c>
       <c r="J6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" t="s">
         <v>14</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>13</v>
-      </c>
-      <c r="L6" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1006,34 +1015,34 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>13</v>
       </c>
-      <c r="J7" t="s">
-        <v>14</v>
-      </c>
       <c r="K7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1044,37 +1053,37 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" t="s">
-        <v>16</v>
-      </c>
       <c r="L8" t="s">
         <v>12</v>
       </c>
       <c r="M8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1082,40 +1091,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
         <v>14</v>
       </c>
-      <c r="E9" t="s">
+      <c r="I9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" t="s">
         <v>14</v>
       </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" t="s">
-        <v>13</v>
-      </c>
       <c r="M9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1123,40 +1132,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
         <v>13</v>
       </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
       <c r="G10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" t="s">
         <v>15</v>
       </c>
-      <c r="H10" t="s">
+      <c r="K10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L10" t="s">
         <v>13</v>
       </c>
-      <c r="I10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" t="s">
-        <v>13</v>
-      </c>
-      <c r="L10" t="s">
-        <v>12</v>
-      </c>
       <c r="M10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1167,37 +1176,37 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" t="s">
         <v>17</v>
       </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" t="s">
-        <v>16</v>
-      </c>
-      <c r="L11" t="s">
-        <v>16</v>
-      </c>
       <c r="M11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1205,40 +1214,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" t="s">
         <v>13</v>
       </c>
-      <c r="C12" t="s">
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" t="s">
         <v>13</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" t="s">
-        <v>12</v>
-      </c>
-      <c r="K12" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12" t="s">
-        <v>13</v>
-      </c>
-      <c r="M12" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1246,40 +1255,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
         <v>15</v>
       </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
       <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" t="s">
         <v>15</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" t="s">
         <v>15</v>
       </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="I13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" t="s">
         <v>15</v>
       </c>
-      <c r="H13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" t="s">
-        <v>14</v>
-      </c>
       <c r="L13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1289,30 +1298,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1346,22 +1355,22 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
         <v>10</v>
@@ -1372,25 +1381,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>-13</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="G4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1401,22 +1410,22 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>-13</v>
       </c>
       <c r="F5">
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1424,25 +1433,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>-1</v>
+      </c>
+      <c r="F6">
+        <v>-11</v>
+      </c>
+      <c r="G6">
         <v>10</v>
       </c>
-      <c r="D6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>-8</v>
-      </c>
-      <c r="G6">
+      <c r="H6" t="s">
         <v>9</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1450,25 +1459,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>-8</v>
       </c>
       <c r="G7">
         <v>9</v>
       </c>
       <c r="H7" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1476,25 +1485,25 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
         <v>4</v>
       </c>
-      <c r="D8" t="s">
-        <v>2</v>
-      </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>10</v>
       </c>
       <c r="G8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1502,25 +1511,25 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
         <v>9</v>
       </c>
-      <c r="G9">
-        <v>7</v>
-      </c>
       <c r="H9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1528,25 +1537,25 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1554,25 +1563,25 @@
         <v>9</v>
       </c>
       <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
         <v>5</v>
       </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
       <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>9</v>
+      </c>
+      <c r="G11">
         <v>7</v>
       </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>6</v>
-      </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1583,21 +1592,99 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>6</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>6</v>
+      </c>
+      <c r="H12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13">
         <v>7</v>
       </c>
-      <c r="E12">
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>6</v>
+      </c>
+      <c r="H13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>13</v>
+      </c>
+      <c r="F14">
+        <v>18</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
-      <c r="F12">
+      <c r="H14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15">
         <v>1</v>
       </c>
-      <c r="G12">
+      <c r="G15">
         <v>4</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H15" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1613,13 +1700,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1627,13 +1714,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>1.666666666666667</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1644,10 +1731,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1655,13 +1742,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>2.083333333333333</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1672,10 +1759,10 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>2.5</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1683,10 +1770,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>2.916666666666667</v>
+        <v>3</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -1697,13 +1784,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>2.916666666666667</v>
+        <v>3.416666666666667</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1711,10 +1798,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -1728,7 +1815,7 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>3.166666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -1739,13 +1826,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>3.5</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1753,13 +1840,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>3.583333333333333</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1767,13 +1854,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1781,13 +1868,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>4.416666666666667</v>
+        <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1802,16 +1889,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1819,16 +1906,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4.166666666666667</v>
+        <v>4.5</v>
       </c>
       <c r="D2">
-        <v>0.166666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1836,13 +1923,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>3.666666666666667</v>
+        <v>4.5</v>
       </c>
       <c r="D3">
-        <v>0.6666666666666665</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1853,16 +1940,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>3.583333333333333</v>
+        <v>4.25</v>
       </c>
       <c r="D4">
-        <v>0.5833333333333335</v>
+        <v>-0.75</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1870,16 +1957,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>3.5</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="D5">
-        <v>-1.5</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1887,16 +1974,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>3.25</v>
+        <v>3.916666666666667</v>
       </c>
       <c r="D6">
-        <v>-0.75</v>
+        <v>-1.083333333333333</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1907,10 +1994,10 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>3.083333333333333</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="D7">
-        <v>0.08333333333333348</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -1921,16 +2008,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1938,16 +2025,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>3.583333333333333</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.5833333333333335</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1958,10 +2045,10 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>2.833333333333333</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="D10">
-        <v>-0.1666666666666665</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -1972,16 +2059,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>2.75</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="D11">
-        <v>0.75</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1992,13 +2079,13 @@
         <v>8</v>
       </c>
       <c r="C12">
-        <v>2.416666666666667</v>
+        <v>2.5</v>
       </c>
       <c r="D12">
-        <v>0.4166666666666665</v>
+        <v>0.5</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2015,7 +2102,7 @@
         <v>0.75</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2030,530 +2117,530 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>46.9</v>
+        <v>29.9</v>
       </c>
       <c r="C2">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="D2">
-        <v>13.1</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>7.4</v>
+        <v>13.3</v>
       </c>
       <c r="F2">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="H2">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="I2">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J2">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K2">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>87.7</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>25.1</v>
       </c>
       <c r="C3">
-        <v>17.9</v>
+        <v>21.9</v>
       </c>
       <c r="D3">
-        <v>14.6</v>
+        <v>17.3</v>
       </c>
       <c r="E3">
-        <v>14.8</v>
+        <v>12.3</v>
       </c>
       <c r="F3">
-        <v>11.9</v>
+        <v>10.6</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="I3">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
-        <v>66.3</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>20.1</v>
+      </c>
+      <c r="C4">
+        <v>18.9</v>
+      </c>
+      <c r="D4">
+        <v>17.2</v>
+      </c>
+      <c r="E4">
+        <v>14</v>
+      </c>
+      <c r="F4">
+        <v>10.8</v>
+      </c>
+      <c r="G4">
+        <v>7.6</v>
+      </c>
+      <c r="H4">
+        <v>5.5</v>
+      </c>
+      <c r="I4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>10.5</v>
-      </c>
-      <c r="C4">
-        <v>17.5</v>
-      </c>
-      <c r="D4">
-        <v>17.5</v>
-      </c>
-      <c r="E4">
-        <v>15.1</v>
-      </c>
-      <c r="F4">
-        <v>12.5</v>
-      </c>
-      <c r="G4">
-        <v>10.4</v>
-      </c>
-      <c r="H4">
-        <v>6.2</v>
-      </c>
-      <c r="I4">
-        <v>4.9</v>
-      </c>
       <c r="J4">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="K4">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="L4">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>60.6</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="C5">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>14.1</v>
+        <v>13.4</v>
       </c>
       <c r="E5">
-        <v>14.9</v>
+        <v>16.3</v>
       </c>
       <c r="F5">
-        <v>12.8</v>
+        <v>15.4</v>
       </c>
       <c r="G5">
         <v>14.3</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I5">
-        <v>8.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="J5">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="L5">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>47.7</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="C6">
         <v>11.3</v>
       </c>
       <c r="D6">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="E6">
-        <v>12.7</v>
+        <v>15.3</v>
       </c>
       <c r="F6">
-        <v>13.8</v>
+        <v>13.3</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>15.9</v>
       </c>
       <c r="H6">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="I6">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="L6">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>44</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>2.7</v>
+        <v>6.9</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D7">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="F7">
-        <v>14.6</v>
+        <v>12.6</v>
       </c>
       <c r="G7">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="H7">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7">
-        <v>7.9</v>
+        <v>5.1</v>
       </c>
       <c r="K7">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7">
-        <v>34.5</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B8">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>3.3</v>
       </c>
       <c r="D8">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="E8">
-        <v>10.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F8">
-        <v>10.1</v>
+        <v>14.7</v>
       </c>
       <c r="G8">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="H8">
-        <v>14.4</v>
+        <v>16.8</v>
       </c>
       <c r="I8">
-        <v>10.1</v>
+        <v>13.1</v>
       </c>
       <c r="J8">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="L8">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8">
-        <v>31.3</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="C9">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="D9">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="F9">
+        <v>6.2</v>
+      </c>
+      <c r="G9">
+        <v>7.8</v>
+      </c>
+      <c r="H9">
+        <v>13.9</v>
+      </c>
+      <c r="I9">
+        <v>19.9</v>
+      </c>
+      <c r="J9">
+        <v>20.1</v>
+      </c>
+      <c r="K9">
+        <v>17.2</v>
+      </c>
+      <c r="L9">
         <v>8.699999999999999</v>
       </c>
-      <c r="G9">
-        <v>9.4</v>
-      </c>
-      <c r="H9">
-        <v>12.8</v>
-      </c>
-      <c r="I9">
-        <v>17.4</v>
-      </c>
-      <c r="J9">
-        <v>16.8</v>
-      </c>
-      <c r="K9">
-        <v>10.8</v>
-      </c>
-      <c r="L9">
-        <v>8.300000000000001</v>
-      </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
-        <v>15.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B10">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="C10">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="D10">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="E10">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>8.300000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="H10">
-        <v>13.4</v>
+        <v>9.9</v>
       </c>
       <c r="I10">
-        <v>15.2</v>
+        <v>16.7</v>
       </c>
       <c r="J10">
-        <v>18.8</v>
+        <v>22.5</v>
       </c>
       <c r="K10">
-        <v>16.5</v>
+        <v>23.4</v>
       </c>
       <c r="L10">
-        <v>13.8</v>
+        <v>15.1</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
       <c r="N10">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B11">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="C11">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D11">
         <v>0.8</v>
       </c>
       <c r="E11">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F11">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="H11">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="I11">
-        <v>11.8</v>
+        <v>15.9</v>
       </c>
       <c r="J11">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="K11">
-        <v>26.5</v>
+        <v>24.5</v>
       </c>
       <c r="L11">
-        <v>30.2</v>
+        <v>16.3</v>
       </c>
       <c r="M11">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B12">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
         <v>0.2</v>
       </c>
-      <c r="D12">
+      <c r="F12">
+        <v>0.4</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>2.5</v>
+      </c>
+      <c r="I12">
+        <v>6.8</v>
+      </c>
+      <c r="J12">
+        <v>11.3</v>
+      </c>
+      <c r="K12">
+        <v>21.8</v>
+      </c>
+      <c r="L12">
+        <v>55.7</v>
+      </c>
+      <c r="M12">
+        <v>0.3</v>
+      </c>
+      <c r="N12">
         <v>0.2</v>
-      </c>
-      <c r="E12">
-        <v>0.7</v>
-      </c>
-      <c r="F12">
-        <v>2.5</v>
-      </c>
-      <c r="G12">
-        <v>2.2</v>
-      </c>
-      <c r="H12">
-        <v>4.4</v>
-      </c>
-      <c r="I12">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J12">
-        <v>15.6</v>
-      </c>
-      <c r="K12">
-        <v>26</v>
-      </c>
-      <c r="L12">
-        <v>39.2</v>
-      </c>
-      <c r="M12">
-        <v>0.2</v>
-      </c>
-      <c r="N12">
-        <v>1.2</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2591,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="M13">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2607,319 +2694,355 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>1.3</v>
+      </c>
+      <c r="C2">
+        <v>98.3</v>
+      </c>
+      <c r="D2">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="E2">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="F2">
+        <v>88</v>
+      </c>
+      <c r="G2">
+        <v>64.7</v>
+      </c>
+      <c r="H2">
+        <v>77.7</v>
+      </c>
+      <c r="I2">
+        <v>77.10000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>23.1</v>
+      </c>
+      <c r="C3">
+        <v>8.6</v>
+      </c>
+      <c r="D3">
+        <v>45</v>
+      </c>
+      <c r="E3">
+        <v>30.2</v>
+      </c>
+      <c r="F3">
+        <v>43.6</v>
+      </c>
+      <c r="G3">
+        <v>48.1</v>
+      </c>
+      <c r="H3">
+        <v>74.7</v>
+      </c>
+      <c r="I3">
+        <v>77.10000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.1</v>
+      </c>
+      <c r="C4">
+        <v>19.1</v>
+      </c>
+      <c r="D4">
+        <v>23</v>
+      </c>
+      <c r="E4">
+        <v>78.3</v>
+      </c>
+      <c r="F4">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="G4">
+        <v>90.5</v>
+      </c>
+      <c r="H4">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="I4">
+        <v>70.89999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>3.3</v>
+      </c>
+      <c r="C5">
+        <v>12.7</v>
+      </c>
+      <c r="D5">
+        <v>51.6</v>
+      </c>
+      <c r="E5">
+        <v>36.8</v>
+      </c>
+      <c r="F5">
+        <v>34.1</v>
+      </c>
+      <c r="G5">
+        <v>29.4</v>
+      </c>
+      <c r="H5">
+        <v>47.59999999999999</v>
+      </c>
+      <c r="I5">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>83.7</v>
+      </c>
+      <c r="C6">
+        <v>48.2</v>
+      </c>
+      <c r="D6">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>61.3</v>
+      </c>
+      <c r="F6">
+        <v>39.5</v>
+      </c>
+      <c r="G6">
+        <v>62.5</v>
+      </c>
+      <c r="H6">
+        <v>43.8</v>
+      </c>
+      <c r="I6">
+        <v>45.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>14.9</v>
+      </c>
+      <c r="C7">
+        <v>11.9</v>
+      </c>
+      <c r="D7">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="E7">
+        <v>20.7</v>
+      </c>
+      <c r="F7">
+        <v>56.2</v>
+      </c>
+      <c r="G7">
+        <v>32.3</v>
+      </c>
+      <c r="H7">
+        <v>46.9</v>
+      </c>
+      <c r="I7">
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>20.6</v>
-      </c>
-      <c r="D2">
-        <v>23.6</v>
-      </c>
-      <c r="E2">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="F2">
-        <v>80.10000000000001</v>
-      </c>
-      <c r="G2">
-        <v>89.60000000000001</v>
-      </c>
-      <c r="H2">
-        <v>88.59999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>81.89999999999999</v>
-      </c>
-      <c r="C3">
-        <v>48.2</v>
-      </c>
-      <c r="D3">
-        <v>25.5</v>
-      </c>
-      <c r="E3">
-        <v>59.7</v>
-      </c>
-      <c r="F3">
-        <v>39.1</v>
-      </c>
-      <c r="G3">
-        <v>64.7</v>
-      </c>
-      <c r="H3">
-        <v>68.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1.9</v>
-      </c>
-      <c r="C4">
-        <v>98.3</v>
-      </c>
-      <c r="D4">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="E4">
-        <v>86.3</v>
-      </c>
-      <c r="F4">
-        <v>87.2</v>
-      </c>
-      <c r="G4">
-        <v>61.3</v>
-      </c>
-      <c r="H4">
-        <v>60.6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
-        <v>26.6</v>
-      </c>
-      <c r="C5">
-        <v>9.4</v>
-      </c>
-      <c r="D5">
-        <v>45.9</v>
-      </c>
-      <c r="E5">
-        <v>31.9</v>
-      </c>
-      <c r="F5">
-        <v>42.4</v>
-      </c>
-      <c r="G5">
-        <v>47</v>
-      </c>
-      <c r="H5">
-        <v>48.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B6">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="C6">
-        <v>77.60000000000001</v>
-      </c>
-      <c r="D6">
-        <v>21.4</v>
-      </c>
-      <c r="E6">
-        <v>8.799999999999999</v>
-      </c>
-      <c r="F6">
-        <v>31.1</v>
-      </c>
-      <c r="G6">
-        <v>46.6</v>
-      </c>
-      <c r="H6">
-        <v>40.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>2.5</v>
-      </c>
-      <c r="C7">
-        <v>13.9</v>
-      </c>
-      <c r="D7">
-        <v>51.4</v>
-      </c>
-      <c r="E7">
-        <v>35.7</v>
-      </c>
-      <c r="F7">
-        <v>35.2</v>
-      </c>
-      <c r="G7">
-        <v>30.5</v>
-      </c>
-      <c r="H7">
-        <v>31.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="B8">
-        <v>16</v>
+        <v>98.8</v>
       </c>
       <c r="C8">
-        <v>9.1</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D8">
-        <v>74.7</v>
+        <v>21.7</v>
       </c>
       <c r="E8">
-        <v>19.5</v>
+        <v>8.200000000000001</v>
       </c>
       <c r="F8">
-        <v>56.99999999999999</v>
+        <v>33.90000000000001</v>
       </c>
       <c r="G8">
-        <v>32.1</v>
+        <v>45.3</v>
       </c>
       <c r="H8">
-        <v>31.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>20</v>
+      </c>
+      <c r="I8">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="C9">
+        <v>94.5</v>
+      </c>
+      <c r="D9">
+        <v>46.7</v>
+      </c>
+      <c r="E9">
+        <v>51.7</v>
+      </c>
+      <c r="F9">
+        <v>16.1</v>
+      </c>
+      <c r="G9">
+        <v>5.3</v>
+      </c>
+      <c r="H9">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B9">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="C9">
-        <v>14.3</v>
-      </c>
-      <c r="D9">
+      <c r="B10">
+        <v>81.8</v>
+      </c>
+      <c r="C10">
+        <v>14.7</v>
+      </c>
+      <c r="D10">
         <v>0.2</v>
       </c>
-      <c r="E9">
-        <v>4.399999999999999</v>
-      </c>
-      <c r="F9">
-        <v>6.7</v>
-      </c>
-      <c r="G9">
-        <v>17.5</v>
-      </c>
-      <c r="H9">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10">
-        <v>93.10000000000001</v>
-      </c>
-      <c r="C10">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="D10">
-        <v>44.5</v>
-      </c>
       <c r="E10">
-        <v>50.7</v>
+        <v>5.5</v>
       </c>
       <c r="F10">
-        <v>16.6</v>
+        <v>6.4</v>
       </c>
       <c r="G10">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="H10">
-        <v>9.199999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>5.2</v>
+      </c>
+      <c r="I10">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>14.7</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>0.5</v>
+      </c>
+      <c r="F11">
+        <v>0.1</v>
+      </c>
+      <c r="G11">
+        <v>1.8</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
+      <c r="B12">
+        <v>0.1</v>
+      </c>
+      <c r="C12">
         <v>0.4</v>
       </c>
-      <c r="D11">
-        <v>13.6</v>
-      </c>
-      <c r="E11">
-        <v>26.8</v>
-      </c>
-      <c r="F11">
-        <v>4.3</v>
-      </c>
-      <c r="G11">
+      <c r="D12">
+        <v>14.1</v>
+      </c>
+      <c r="E12">
+        <v>25.2</v>
+      </c>
+      <c r="F12">
+        <v>3.2</v>
+      </c>
+      <c r="G12">
         <v>2.1</v>
       </c>
-      <c r="H11">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>14.8</v>
-      </c>
-      <c r="D12">
-        <v>0.8</v>
-      </c>
-      <c r="E12">
-        <v>0.6</v>
-      </c>
-      <c r="F12">
-        <v>0.3</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
       <c r="H12">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>0.2</v>
+      </c>
+      <c r="I12">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -2942,6 +3065,9 @@
         <v>0</v>
       </c>
       <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>0</v>
       </c>
     </row>
@@ -2957,28 +3083,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2989,25 +3115,25 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D2">
-        <v>108.48</v>
+        <v>105.33</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>118.32</v>
+        <v>119.82</v>
       </c>
       <c r="G2">
-        <v>0.556</v>
+        <v>0.571</v>
       </c>
       <c r="H2">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3015,28 +3141,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D3">
-        <v>81.31999999999999</v>
+        <v>106.32</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>116.86</v>
+        <v>113.81</v>
       </c>
       <c r="G3">
-        <v>0.537</v>
+        <v>0.464</v>
       </c>
       <c r="H3">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3044,28 +3170,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>126.59</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>111.85</v>
+        <v>114.37</v>
       </c>
       <c r="G4">
-        <v>0.463</v>
+        <v>0.518</v>
       </c>
       <c r="H4">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3073,28 +3199,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D5">
-        <v>115.21</v>
+        <v>80.3</v>
       </c>
       <c r="E5" t="s">
         <v>16</v>
       </c>
       <c r="F5">
-        <v>112.72</v>
+        <v>117.33</v>
       </c>
       <c r="G5">
-        <v>0.463</v>
+        <v>0.571</v>
       </c>
       <c r="H5">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3102,28 +3228,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D6">
-        <v>123.96</v>
+        <v>111.32</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>116.78</v>
+        <v>117.21</v>
       </c>
       <c r="G6">
-        <v>0.556</v>
+        <v>0.571</v>
       </c>
       <c r="H6">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3131,28 +3257,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D7">
-        <v>109.2</v>
+        <v>113.47</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7">
-        <v>113.01</v>
+        <v>111.46</v>
       </c>
       <c r="G7">
-        <v>0.463</v>
+        <v>0.446</v>
       </c>
       <c r="H7">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3160,28 +3286,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8">
+        <v>121.95</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>115.18</v>
+      </c>
+      <c r="G8">
+        <v>0.554</v>
+      </c>
+      <c r="H8">
+        <v>-0.8</v>
+      </c>
+      <c r="I8">
         <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8">
-        <v>110.78</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8">
-        <v>115.31</v>
-      </c>
-      <c r="G8">
-        <v>0.519</v>
-      </c>
-      <c r="H8">
-        <v>-0.3</v>
-      </c>
-      <c r="I8">
-        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3189,28 +3315,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D9">
-        <v>117.06</v>
+        <v>118.95</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>113.57</v>
+        <v>110.59</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.482</v>
       </c>
       <c r="H9">
-        <v>-0.3</v>
+        <v>-1.5</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3218,28 +3344,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D10">
-        <v>117.88</v>
+        <v>125.61</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
       <c r="F10">
-        <v>111.23</v>
+        <v>109.16</v>
       </c>
       <c r="G10">
-        <v>0.463</v>
+        <v>0.446</v>
       </c>
       <c r="H10">
-        <v>-0.6</v>
+        <v>-1.6</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3247,28 +3373,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D11">
-        <v>129.51</v>
+        <v>127.57</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>111.23</v>
+        <v>109.51</v>
       </c>
       <c r="G11">
-        <v>0.481</v>
+        <v>0.464</v>
       </c>
       <c r="H11">
-        <v>-0.9</v>
+        <v>-2.9</v>
       </c>
       <c r="I11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3276,28 +3402,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D12">
-        <v>108.45</v>
+        <v>118.46</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>114.36</v>
+        <v>109.05</v>
       </c>
       <c r="G12">
-        <v>0.519</v>
+        <v>0.446</v>
       </c>
       <c r="H12">
-        <v>-1.6</v>
+        <v>-2.9</v>
       </c>
       <c r="I12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3305,28 +3431,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D13">
-        <v>117.06</v>
+        <v>121.25</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13">
-        <v>110.26</v>
+        <v>110.05</v>
       </c>
       <c r="G13">
-        <v>0.481</v>
+        <v>0.464</v>
       </c>
       <c r="H13">
-        <v>-2.3</v>
+        <v>-2.9</v>
       </c>
       <c r="I13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3341,115 +3467,115 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C2">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D2">
-        <v>129.5133333333333</v>
+        <v>121.2485714285714</v>
       </c>
       <c r="E2">
-        <v>777.08</v>
+        <v>848.74</v>
       </c>
       <c r="F2">
-        <v>87.7</v>
+        <v>78.5</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D3">
-        <v>115.2066666666667</v>
+        <v>127.5742857142857</v>
       </c>
       <c r="E3">
-        <v>691.24</v>
+        <v>893.02</v>
       </c>
       <c r="F3">
-        <v>66.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D4">
-        <v>126.5866666666667</v>
+        <v>125.6142857142857</v>
       </c>
       <c r="E4">
-        <v>759.52</v>
+        <v>879.3000000000001</v>
       </c>
       <c r="F4">
-        <v>60.6</v>
+        <v>70.19999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I4" t="s">
         <v>91</v>
@@ -3457,57 +3583,57 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D5">
-        <v>117.06</v>
+        <v>118.4628571428571</v>
       </c>
       <c r="E5">
-        <v>702.36</v>
+        <v>829.24</v>
       </c>
       <c r="F5">
-        <v>47.7</v>
+        <v>48.4</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>74</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D6">
-        <v>123.96</v>
+        <v>113.4742857142857</v>
       </c>
       <c r="E6">
-        <v>743.76</v>
+        <v>794.3200000000001</v>
       </c>
       <c r="F6">
-        <v>44</v>
+        <v>46.8</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I6" t="s">
         <v>92</v>
@@ -3515,28 +3641,28 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D7">
-        <v>117.0566666666667</v>
+        <v>118.9485714285714</v>
       </c>
       <c r="E7">
-        <v>702.34</v>
+        <v>832.6400000000001</v>
       </c>
       <c r="F7">
-        <v>34.5</v>
+        <v>43.1</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I7" t="s">
         <v>92</v>
@@ -3544,115 +3670,115 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D8">
-        <v>117.88</v>
+        <v>121.9542857142857</v>
       </c>
       <c r="E8">
-        <v>707.2800000000001</v>
+        <v>853.6799999999999</v>
       </c>
       <c r="F8">
-        <v>31.3</v>
+        <v>22.4</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C9">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D9">
-        <v>108.48</v>
+        <v>106.32</v>
       </c>
       <c r="E9">
-        <v>650.88</v>
+        <v>744.24</v>
       </c>
       <c r="F9">
-        <v>15.8</v>
+        <v>6.2</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D10">
-        <v>109.2033333333333</v>
+        <v>111.3228571428571</v>
       </c>
       <c r="E10">
-        <v>655.22</v>
+        <v>779.26</v>
       </c>
       <c r="F10">
-        <v>8.200000000000001</v>
+        <v>4</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
         <v>75</v>
       </c>
       <c r="C11">
-        <v>0.3333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D11">
-        <v>110.78</v>
+        <v>105.3285714285714</v>
       </c>
       <c r="E11">
-        <v>664.6800000000001</v>
+        <v>737.3</v>
       </c>
       <c r="F11">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="G11">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s">
         <v>94</v>
@@ -3660,31 +3786,31 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C12">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D12">
-        <v>108.4533333333333</v>
+        <v>107</v>
       </c>
       <c r="E12">
-        <v>650.72</v>
+        <v>749</v>
       </c>
       <c r="F12">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="G12">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3692,28 +3818,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>81.31666666666666</v>
+        <v>80.30285714285715</v>
       </c>
       <c r="E13">
-        <v>487.9</v>
+        <v>562.12</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="H13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3728,19 +3854,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3751,16 +3877,16 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3771,16 +3897,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3788,19 +3914,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4">
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3808,19 +3934,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3828,19 +3954,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3848,16 +3974,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
         <v>105</v>
@@ -3868,16 +3994,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
         <v>106</v>
@@ -3888,16 +4014,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D9">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
         <v>107</v>
@@ -3911,10 +4037,10 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D10">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -3931,16 +4057,16 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D11">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3948,19 +4074,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D12">
-        <v>-15</v>
+        <v>-19</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3968,19 +4094,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13">
-        <v>-16</v>
+        <v>-22</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -3990,33 +4116,36 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>118</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -4038,11 +4167,14 @@
       <c r="G2">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -4064,16 +4196,19 @@
       <c r="G3">
         <v>14</v>
       </c>
-      <c r="H3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="H3">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -4082,24 +4217,27 @@
         <v>6</v>
       </c>
       <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
         <v>9</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>7</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>13</v>
       </c>
-      <c r="H4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -4108,123 +4246,138 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>12</v>
+      </c>
+      <c r="I5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
+      <c r="B6">
+        <v>-6</v>
+      </c>
+      <c r="C6">
+        <v>-2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>-6</v>
+      </c>
+      <c r="F6">
+        <v>-4</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>-1</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
       </c>
       <c r="C7">
         <v>4</v>
       </c>
       <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
         <v>5</v>
       </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>-1</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="D8">
+        <v>-4</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="E8">
-        <v>-6</v>
-      </c>
       <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
         <v>-4</v>
       </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G9">
-        <v>-4</v>
-      </c>
-      <c r="H9" t="s">
+        <v>-1</v>
+      </c>
+      <c r="H9">
+        <v>-6</v>
+      </c>
+      <c r="I9" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4246,11 +4399,14 @@
       <c r="G10">
         <v>-6</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10">
+        <v>-8</v>
+      </c>
+      <c r="I10" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -4272,60 +4428,69 @@
       <c r="G11">
         <v>-11</v>
       </c>
-      <c r="H11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="H11">
+        <v>-10</v>
+      </c>
+      <c r="I11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>-8</v>
+      </c>
+      <c r="C12">
+        <v>-7</v>
+      </c>
+      <c r="D12">
+        <v>-9</v>
+      </c>
+      <c r="E12">
+        <v>-12</v>
+      </c>
+      <c r="F12">
+        <v>-12</v>
+      </c>
+      <c r="G12">
+        <v>-16</v>
+      </c>
+      <c r="H12">
+        <v>-19</v>
+      </c>
+      <c r="I12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>2</v>
       </c>
-      <c r="C12">
+      <c r="C13">
         <v>-8</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>-15</v>
       </c>
-      <c r="E12">
+      <c r="E13">
         <v>-8</v>
       </c>
-      <c r="F12">
+      <c r="F13">
         <v>-13</v>
       </c>
-      <c r="G12">
+      <c r="G13">
         <v>-15</v>
       </c>
-      <c r="H12" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>-8</v>
-      </c>
-      <c r="C13">
-        <v>-7</v>
-      </c>
-      <c r="D13">
-        <v>-9</v>
-      </c>
-      <c r="E13">
-        <v>-12</v>
-      </c>
-      <c r="F13">
-        <v>-12</v>
-      </c>
-      <c r="G13">
-        <v>-16</v>
-      </c>
-      <c r="H13" t="s">
-        <v>109</v>
+      <c r="H13">
+        <v>-22</v>
+      </c>
+      <c r="I13" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/The Girl's Room 💞🏈 2026.xlsx
+++ b/data/leagues/The Girl's Room 💞🏈 2026.xlsx
@@ -247,12 +247,12 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
+    <t>4-3</t>
+  </si>
+  <si>
     <t>5-2</t>
   </si>
   <si>
-    <t>4-3</t>
-  </si>
-  <si>
     <t>3-4</t>
   </si>
   <si>
@@ -262,37 +262,37 @@
     <t>0-7</t>
   </si>
   <si>
+    <t>9.6-5.4-0.1</t>
+  </si>
+  <si>
     <t>10.0-4.9-0.1</t>
   </si>
   <si>
-    <t>9.6-5.4-0.1</t>
-  </si>
-  <si>
-    <t>9.4-5.6-0.1</t>
+    <t>9.4-5.5-0.1</t>
   </si>
   <si>
     <t>8.9-6.0-0.1</t>
   </si>
   <si>
-    <t>9.0-5.9-0.1</t>
-  </si>
-  <si>
-    <t>8.6-6.3-0.1</t>
-  </si>
-  <si>
-    <t>7.7-7.2-0.1</t>
+    <t>9.1-5.8-0.1</t>
+  </si>
+  <si>
+    <t>8.7-6.2-0.1</t>
+  </si>
+  <si>
+    <t>7.6-7.3-0.1</t>
   </si>
   <si>
     <t>7.2-7.7-0.1</t>
   </si>
   <si>
-    <t>6.4-8.5-0.1</t>
-  </si>
-  <si>
-    <t>6.7-8.3-0.1</t>
-  </si>
-  <si>
-    <t>5.1-9.8-0.1</t>
+    <t>6.7-8.2-0.1</t>
+  </si>
+  <si>
+    <t>6.3-8.6-0.1</t>
+  </si>
+  <si>
+    <t>5.1-9.7-0.1</t>
   </si>
   <si>
     <t>0.9-14.1</t>
@@ -328,10 +328,10 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑4</t>
+  </si>
+  <si>
     <t>↑3</t>
-  </si>
-  <si>
-    <t>↑4</t>
   </si>
   <si>
     <t>↑6</t>
@@ -2161,37 +2161,37 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>29.9</v>
+        <v>24.7</v>
       </c>
       <c r="C2">
-        <v>18.3</v>
+        <v>19.4</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>18.9</v>
       </c>
       <c r="E2">
-        <v>13.3</v>
+        <v>15.7</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I2">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J2">
         <v>0.5</v>
       </c>
       <c r="K2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2200,51 +2200,51 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>78.5</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>25.1</v>
+        <v>28.9</v>
       </c>
       <c r="C3">
-        <v>21.9</v>
+        <v>21</v>
       </c>
       <c r="D3">
-        <v>17.3</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>12.3</v>
+        <v>11.7</v>
       </c>
       <c r="F3">
-        <v>10.6</v>
+        <v>9.4</v>
       </c>
       <c r="G3">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="H3">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J3">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K3">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
-        <v>76.59999999999999</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -2252,43 +2252,43 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="C4">
-        <v>18.9</v>
+        <v>20.5</v>
       </c>
       <c r="D4">
-        <v>17.2</v>
+        <v>16.5</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="F4">
-        <v>10.8</v>
+        <v>12.3</v>
       </c>
       <c r="G4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H4">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J4">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="K4">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="L4">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>70.2</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -2299,40 +2299,40 @@
         <v>6.7</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="D5">
-        <v>13.4</v>
+        <v>12.8</v>
       </c>
       <c r="E5">
-        <v>16.3</v>
+        <v>15.8</v>
       </c>
       <c r="F5">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="G5">
-        <v>14.3</v>
+        <v>13.7</v>
       </c>
       <c r="H5">
-        <v>9.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="I5">
         <v>5.8</v>
       </c>
       <c r="J5">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="K5">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="L5">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>48.4</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -2340,43 +2340,43 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C6">
-        <v>11.3</v>
+        <v>10.6</v>
       </c>
       <c r="D6">
-        <v>12.3</v>
+        <v>11.9</v>
       </c>
       <c r="E6">
-        <v>15.3</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="G6">
-        <v>15.9</v>
+        <v>14.1</v>
       </c>
       <c r="H6">
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="I6">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="J6">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L6">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
-        <v>46.8</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -2384,43 +2384,43 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>6.9</v>
+        <v>8.6</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>10.4</v>
       </c>
       <c r="D7">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="E7">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="F7">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="G7">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="H7">
-        <v>12.8</v>
+        <v>11.7</v>
       </c>
       <c r="I7">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J7">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="K7">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="L7">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7">
-        <v>43.1</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -2428,43 +2428,43 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="C8">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="D8">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="E8">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F8">
+        <v>12.6</v>
+      </c>
+      <c r="G8">
+        <v>15.5</v>
+      </c>
+      <c r="H8">
         <v>14.7</v>
       </c>
-      <c r="G8">
-        <v>14.9</v>
-      </c>
-      <c r="H8">
-        <v>16.8</v>
-      </c>
       <c r="I8">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="J8">
-        <v>9</v>
+        <v>10.7</v>
       </c>
       <c r="K8">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="L8">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8">
-        <v>22.4</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -2472,48 +2472,48 @@
         <v>0</v>
       </c>
       <c r="B9">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="C9">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="D9">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="E9">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="F9">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="G9">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="H9">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="I9">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="J9">
-        <v>20.1</v>
+        <v>19.6</v>
       </c>
       <c r="K9">
-        <v>17.2</v>
+        <v>16</v>
       </c>
       <c r="L9">
-        <v>8.699999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B10">
         <v>0.2</v>
@@ -2525,78 +2525,78 @@
         <v>1.4</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G10">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="H10">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="I10">
-        <v>16.7</v>
+        <v>18</v>
       </c>
       <c r="J10">
-        <v>22.5</v>
+        <v>23.3</v>
       </c>
       <c r="K10">
-        <v>23.4</v>
+        <v>21</v>
       </c>
       <c r="L10">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>0.2</v>
+      </c>
+      <c r="C11">
+        <v>0.5</v>
+      </c>
+      <c r="D11">
         <v>1</v>
       </c>
-      <c r="B11">
-        <v>0.4</v>
-      </c>
-      <c r="C11">
-        <v>0.8</v>
-      </c>
-      <c r="D11">
-        <v>0.8</v>
-      </c>
       <c r="E11">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="H11">
-        <v>9.6</v>
+        <v>10.9</v>
       </c>
       <c r="I11">
-        <v>15.9</v>
+        <v>16.6</v>
       </c>
       <c r="J11">
-        <v>20.1</v>
+        <v>22.7</v>
       </c>
       <c r="K11">
-        <v>24.5</v>
+        <v>25.8</v>
       </c>
       <c r="L11">
-        <v>16.3</v>
+        <v>12.9</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
       <c r="N11">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2610,37 +2610,37 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E12">
         <v>0.2</v>
       </c>
       <c r="F12">
+        <v>0.2</v>
+      </c>
+      <c r="G12">
+        <v>1.5</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>6.1</v>
+      </c>
+      <c r="J12">
+        <v>11.4</v>
+      </c>
+      <c r="K12">
+        <v>22</v>
+      </c>
+      <c r="L12">
+        <v>56.1</v>
+      </c>
+      <c r="M12">
         <v>0.4</v>
       </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>2.5</v>
-      </c>
-      <c r="I12">
-        <v>6.8</v>
-      </c>
-      <c r="J12">
-        <v>11.3</v>
-      </c>
-      <c r="K12">
-        <v>21.8</v>
-      </c>
-      <c r="L12">
-        <v>55.7</v>
-      </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.3</v>
-      </c>
-      <c r="N12">
-        <v>0.2</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="M13">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2725,60 +2725,60 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>1.3</v>
+        <v>22.3</v>
       </c>
       <c r="C2">
-        <v>98.3</v>
+        <v>8.4</v>
       </c>
       <c r="D2">
-        <v>98.59999999999999</v>
+        <v>44.9</v>
       </c>
       <c r="E2">
-        <v>81.59999999999999</v>
+        <v>30.8</v>
       </c>
       <c r="F2">
-        <v>88</v>
+        <v>42.8</v>
       </c>
       <c r="G2">
-        <v>64.7</v>
+        <v>46.7</v>
       </c>
       <c r="H2">
-        <v>77.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I2">
-        <v>77.10000000000001</v>
+        <v>78.60000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>23.1</v>
+        <v>1.3</v>
       </c>
       <c r="C3">
-        <v>8.6</v>
+        <v>97.8</v>
       </c>
       <c r="D3">
-        <v>45</v>
+        <v>98.5</v>
       </c>
       <c r="E3">
-        <v>30.2</v>
+        <v>84.39999999999999</v>
       </c>
       <c r="F3">
-        <v>43.6</v>
+        <v>87</v>
       </c>
       <c r="G3">
-        <v>48.1</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="H3">
-        <v>74.7</v>
+        <v>76</v>
       </c>
       <c r="I3">
-        <v>77.10000000000001</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2786,86 +2786,86 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>21.1</v>
       </c>
       <c r="E4">
-        <v>78.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F4">
-        <v>78.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="G4">
-        <v>90.5</v>
+        <v>89.5</v>
       </c>
       <c r="H4">
-        <v>69.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="I4">
-        <v>70.89999999999999</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>3.3</v>
+        <v>83</v>
       </c>
       <c r="C5">
-        <v>12.7</v>
+        <v>49.8</v>
       </c>
       <c r="D5">
-        <v>51.6</v>
+        <v>27.5</v>
       </c>
       <c r="E5">
-        <v>36.8</v>
+        <v>61.7</v>
       </c>
       <c r="F5">
-        <v>34.1</v>
+        <v>39.7</v>
       </c>
       <c r="G5">
-        <v>29.4</v>
+        <v>60.4</v>
       </c>
       <c r="H5">
-        <v>47.59999999999999</v>
+        <v>46.3</v>
       </c>
       <c r="I5">
-        <v>50.4</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>83.7</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>48.2</v>
+        <v>14.1</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>46.1</v>
       </c>
       <c r="E6">
-        <v>61.3</v>
+        <v>35.5</v>
       </c>
       <c r="F6">
-        <v>39.5</v>
+        <v>31.5</v>
       </c>
       <c r="G6">
-        <v>62.5</v>
+        <v>29.4</v>
       </c>
       <c r="H6">
-        <v>43.8</v>
+        <v>52</v>
       </c>
       <c r="I6">
-        <v>45.9</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2873,28 +2873,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>14.9</v>
+        <v>17.6</v>
       </c>
       <c r="C7">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="D7">
-        <v>73.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E7">
-        <v>20.7</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>56.2</v>
+        <v>56.99999999999999</v>
       </c>
       <c r="G7">
-        <v>32.3</v>
+        <v>33.90000000000001</v>
       </c>
       <c r="H7">
-        <v>46.9</v>
+        <v>43.8</v>
       </c>
       <c r="I7">
-        <v>44</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2902,28 +2902,28 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <v>98.8</v>
+        <v>98.2</v>
       </c>
       <c r="C8">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="D8">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="E8">
-        <v>8.200000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="F8">
-        <v>33.90000000000001</v>
+        <v>34.2</v>
       </c>
       <c r="G8">
-        <v>45.3</v>
+        <v>44.7</v>
       </c>
       <c r="H8">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="I8">
-        <v>23.2</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2931,28 +2931,28 @@
         <v>0</v>
       </c>
       <c r="B9">
-        <v>92.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="C9">
-        <v>94.5</v>
+        <v>94.3</v>
       </c>
       <c r="D9">
-        <v>46.7</v>
+        <v>50.2</v>
       </c>
       <c r="E9">
-        <v>51.7</v>
+        <v>50.2</v>
       </c>
       <c r="F9">
-        <v>16.1</v>
+        <v>17.3</v>
       </c>
       <c r="G9">
-        <v>5.3</v>
+        <v>5.899999999999999</v>
       </c>
       <c r="H9">
-        <v>9.300000000000001</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2960,28 +2960,28 @@
         <v>1</v>
       </c>
       <c r="B10">
-        <v>81.8</v>
+        <v>81.69999999999999</v>
       </c>
       <c r="C10">
-        <v>14.7</v>
+        <v>12.6</v>
       </c>
       <c r="D10">
         <v>0.2</v>
       </c>
       <c r="E10">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="F10">
-        <v>6.4</v>
+        <v>5.899999999999999</v>
       </c>
       <c r="G10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H10">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I10">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2989,28 +2989,28 @@
         <v>5</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C11">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E11">
-        <v>0.5</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="F11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I11">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3018,28 +3018,28 @@
         <v>8</v>
       </c>
       <c r="B12">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C12">
         <v>0.4</v>
       </c>
       <c r="D12">
-        <v>14.1</v>
+        <v>14.9</v>
       </c>
       <c r="E12">
-        <v>25.2</v>
+        <v>24.9</v>
       </c>
       <c r="F12">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G12">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="H12">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I12">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3496,22 +3496,22 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
       </c>
       <c r="C2">
-        <v>0.7142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D2">
-        <v>121.2485714285714</v>
+        <v>127.5742857142857</v>
       </c>
       <c r="E2">
-        <v>848.74</v>
+        <v>893.02</v>
       </c>
       <c r="F2">
-        <v>78.5</v>
+        <v>78.7</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -3525,22 +3525,22 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D3">
-        <v>127.5742857142857</v>
+        <v>121.2485714285714</v>
       </c>
       <c r="E3">
-        <v>893.02</v>
+        <v>848.74</v>
       </c>
       <c r="F3">
-        <v>76.59999999999999</v>
+        <v>78.60000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -3557,7 +3557,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4">
         <v>0.5714285714285714</v>
@@ -3569,7 +3569,7 @@
         <v>879.3000000000001</v>
       </c>
       <c r="F4">
-        <v>70.19999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5">
         <v>0.5714285714285714</v>
@@ -3598,7 +3598,7 @@
         <v>829.24</v>
       </c>
       <c r="F5">
-        <v>48.4</v>
+        <v>47.59999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -3615,7 +3615,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6">
         <v>0.7142857142857143</v>
@@ -3627,7 +3627,7 @@
         <v>794.3200000000001</v>
       </c>
       <c r="F6">
-        <v>46.8</v>
+        <v>45.8</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -3644,7 +3644,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C7">
         <v>0.5714285714285714</v>
@@ -3656,7 +3656,7 @@
         <v>832.6400000000001</v>
       </c>
       <c r="F7">
-        <v>43.1</v>
+        <v>42.8</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -3685,7 +3685,7 @@
         <v>853.6799999999999</v>
       </c>
       <c r="F8">
-        <v>22.4</v>
+        <v>21.8</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9">
         <v>0.5714285714285714</v>
@@ -3714,7 +3714,7 @@
         <v>744.24</v>
       </c>
       <c r="F9">
-        <v>6.2</v>
+        <v>7.399999999999999</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3728,22 +3728,22 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C10">
-        <v>0.4285714285714285</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D10">
-        <v>111.3228571428571</v>
+        <v>105.3285714285714</v>
       </c>
       <c r="E10">
-        <v>779.26</v>
+        <v>737.3</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3752,27 +3752,27 @@
         <v>87</v>
       </c>
       <c r="I10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11">
-        <v>0.5714285714285714</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D11">
-        <v>105.3285714285714</v>
+        <v>111.3228571428571</v>
       </c>
       <c r="E11">
-        <v>737.3</v>
+        <v>779.26</v>
       </c>
       <c r="F11">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -3781,7 +3781,7 @@
         <v>88</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3801,10 +3801,10 @@
         <v>749</v>
       </c>
       <c r="F12">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G12">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H12" t="s">
         <v>89</v>
@@ -3833,7 +3833,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H13" t="s">
         <v>90</v>
@@ -3874,16 +3874,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D2">
         <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
         <v>101</v>
@@ -3894,16 +3894,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D3">
         <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
         <v>102</v>
@@ -3966,7 +3966,7 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4147,25 +4147,25 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>-2</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>-3</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2">
         <v>18</v>
@@ -4176,25 +4176,25 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>-2</v>
+      </c>
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>8</v>
-      </c>
-      <c r="C3">
+      <c r="D3">
+        <v>-3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
         <v>10</v>
       </c>
-      <c r="D3">
-        <v>11</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>12</v>
-      </c>
       <c r="G3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3">
         <v>18</v>
@@ -4287,7 +4287,7 @@
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:9">
